--- a/rosters/.versions/2026-10/previous.xlsx
+++ b/rosters/.versions/2026-10/previous.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\80235\OneDrive - Oman Air\Desktop\Rosters\STAFF OPERATION SCHEDULE\Roster 5 x 3\2026\OPS\10 October 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://omanair-my.sharepoint.com/personal/8715_hq_omanair_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8685B1CC-5234-4032-83AD-36DA364E9C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD1553C5-25A3-468F-BADD-6AD1EB0C0E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting " sheetId="1" state="hidden" r:id="rId1"/>
@@ -4140,13 +4140,13 @@
     <t>Export Load Control Roster for the Month of OCTOBER 2026</t>
   </si>
   <si>
-    <t>Rashid Shayai</t>
-  </si>
-  <si>
     <t>LV</t>
   </si>
   <si>
     <t>Off</t>
+  </si>
+  <si>
+    <t>Rashid AL Shayai - 82677</t>
   </si>
 </sst>
 </file>
@@ -5517,17 +5517,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5538,86 +5544,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5703,6 +5634,75 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5757,6 +5757,45 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5787,9 +5826,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5798,54 +5834,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5865,17 +5853,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5885,6 +5879,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5908,586 +5908,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="240">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="175">
     <dxf>
       <font>
         <color auto="1"/>
@@ -7410,14 +6831,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7428,27 +6844,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7469,13 +6864,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7516,6 +6904,32 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -7528,19 +6942,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7623,6 +7027,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -7631,13 +7042,6 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7670,12 +7074,19 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
-        <color auto="1"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7786,6 +7197,23 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
@@ -7843,9 +7271,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7884,24 +7315,25 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7921,8 +7353,14 @@
       </font>
       <fill>
         <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7934,19 +7372,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8487,91 +7932,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="144"/>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
-      <c r="AG1" s="144"/>
-      <c r="AH1" s="144"/>
-      <c r="AI1" s="144"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
     </row>
     <row r="2" spans="2:40" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="142"/>
+      <c r="C2" s="144"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="143" t="s">
+      <c r="E2" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143" t="s">
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="145"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="145"/>
+      <c r="W2" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
-      <c r="Z2" s="143"/>
-      <c r="AA2" s="143"/>
-      <c r="AB2" s="143"/>
-      <c r="AC2" s="143">
+      <c r="X2" s="145"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="145"/>
+      <c r="AA2" s="145"/>
+      <c r="AB2" s="145"/>
+      <c r="AC2" s="145">
         <v>2025</v>
       </c>
-      <c r="AD2" s="143"/>
-      <c r="AE2" s="143"/>
-      <c r="AF2" s="143"/>
+      <c r="AD2" s="145"/>
+      <c r="AE2" s="145"/>
+      <c r="AF2" s="145"/>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AK2" s="137" t="s">
+      <c r="AK2" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="AL2" s="137"/>
-      <c r="AM2" s="137"/>
-      <c r="AN2" s="137"/>
+      <c r="AL2" s="141"/>
+      <c r="AM2" s="141"/>
+      <c r="AN2" s="141"/>
     </row>
     <row r="3" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B3" s="142"/>
-      <c r="C3" s="142"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
       <c r="D3" s="11"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -8604,14 +8049,14 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AK3" s="137"/>
-      <c r="AL3" s="137"/>
-      <c r="AM3" s="137"/>
-      <c r="AN3" s="137"/>
+      <c r="AK3" s="141"/>
+      <c r="AL3" s="141"/>
+      <c r="AM3" s="141"/>
+      <c r="AN3" s="141"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
       <c r="D4" s="11"/>
       <c r="E4" s="138" t="s">
         <v>34</v>
@@ -8625,37 +8070,37 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="140" t="s">
+      <c r="M4" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="140"/>
-      <c r="O4" s="140"/>
-      <c r="P4" s="145">
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="140">
         <f>IFERROR(DATEVALUE(J4&amp;W2&amp;AC2),"")</f>
         <v>45901</v>
       </c>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="Q4" s="140"/>
+      <c r="R4" s="140"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="140" t="s">
+      <c r="U4" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="140"/>
-      <c r="W4" s="140"/>
-      <c r="X4" s="145">
+      <c r="V4" s="139"/>
+      <c r="W4" s="139"/>
+      <c r="X4" s="140">
         <f>IFERROR(EOMONTH(P4,0)+J4-1,"")</f>
         <v>45930</v>
       </c>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="145"/>
+      <c r="Y4" s="140"/>
+      <c r="Z4" s="140"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="140" t="s">
+      <c r="AC4" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="AD4" s="140"/>
-      <c r="AE4" s="140"/>
+      <c r="AD4" s="139"/>
+      <c r="AE4" s="139"/>
       <c r="AF4" s="3">
         <f>COUNTIF(E6:AI6,"*?")</f>
         <v>30</v>
@@ -8663,10 +8108,10 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AK4" s="137"/>
-      <c r="AL4" s="137"/>
-      <c r="AM4" s="137"/>
-      <c r="AN4" s="137"/>
+      <c r="AK4" s="141"/>
+      <c r="AL4" s="141"/>
+      <c r="AM4" s="141"/>
+      <c r="AN4" s="141"/>
     </row>
     <row r="5" spans="2:40" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
@@ -8705,10 +8150,10 @@
       <c r="AI5" s="3"/>
     </row>
     <row r="6" spans="2:40" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="141" t="s">
+      <c r="B6" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="141" t="s">
+      <c r="C6" s="143" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="14"/>
@@ -8837,22 +8282,22 @@
         <v/>
       </c>
       <c r="AJ6" s="16"/>
-      <c r="AK6" s="139" t="s">
+      <c r="AK6" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="AL6" s="139" t="s">
+      <c r="AL6" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="AM6" s="139" t="s">
+      <c r="AM6" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="AN6" s="139" t="s">
+      <c r="AN6" s="142" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
+      <c r="B7" s="143"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="14"/>
       <c r="E7" s="17">
         <f>P4</f>
@@ -8979,10 +8424,10 @@
         <v/>
       </c>
       <c r="AJ7" s="16"/>
-      <c r="AK7" s="139"/>
-      <c r="AL7" s="139"/>
-      <c r="AM7" s="139"/>
-      <c r="AN7" s="139"/>
+      <c r="AK7" s="142"/>
+      <c r="AL7" s="142"/>
+      <c r="AM7" s="142"/>
+      <c r="AN7" s="142"/>
     </row>
     <row r="8" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
@@ -13962,12 +13407,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E1:AI1"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AK2:AN4"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
@@ -13984,28 +13423,34 @@
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="W2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="E1:AI1"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
-    <cfRule type="expression" dxfId="239" priority="4">
+    <cfRule type="expression" dxfId="174" priority="4">
       <formula>LEFT(E8,1)="N"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="238" priority="5">
+    <cfRule type="expression" dxfId="173" priority="5">
       <formula>LEFT(E8,1)="A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="237" priority="7">
+    <cfRule type="expression" dxfId="172" priority="7">
       <formula>LEFT(E8,1)="M"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="236" priority="8">
+    <cfRule type="expression" dxfId="171" priority="8">
       <formula>LEFT(E8,1)="D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42 E8:AI37 AK8:AN37">
-    <cfRule type="expression" dxfId="235" priority="3">
+    <cfRule type="expression" dxfId="170" priority="3">
       <formula>LEFT(E8,1)="O"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42">
-    <cfRule type="expression" dxfId="234" priority="1">
+    <cfRule type="expression" dxfId="169" priority="1">
       <formula>ISEVEN(ROW($E39))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14047,61 +13492,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="192" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="149"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="193"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="193"/>
+      <c r="Q2" s="193"/>
+      <c r="R2" s="193"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="W2" s="193"/>
+      <c r="X2" s="193"/>
+      <c r="Y2" s="193"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="193"/>
+      <c r="AB2" s="193"/>
+      <c r="AC2" s="193"/>
+      <c r="AD2" s="193"/>
+      <c r="AE2" s="193"/>
+      <c r="AF2" s="193"/>
+      <c r="AG2" s="193"/>
+      <c r="AH2" s="193"/>
+      <c r="AI2" s="193"/>
+      <c r="AJ2" s="194"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
       <c r="F3" s="46" t="s">
         <v>96</v>
       </c>
@@ -14195,16 +13640,16 @@
       <c r="AJ3" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
       <c r="F4" s="43">
         <v>1</v>
       </c>
@@ -14298,22 +13743,22 @@
       <c r="AJ4" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="176" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="176"/>
       <c r="F5" s="127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G5" s="127" t="s">
         <v>219</v>
@@ -14430,10 +13875,10 @@
       <c r="B6" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="176" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="146"/>
+      <c r="D6" s="176"/>
       <c r="F6" s="128" t="s">
         <v>202</v>
       </c>
@@ -14552,10 +13997,10 @@
       <c r="B7" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C7" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="D7" s="154"/>
+      <c r="D7" s="147"/>
       <c r="F7" s="128" t="s">
         <v>194</v>
       </c>
@@ -14659,10 +14104,10 @@
       <c r="B8" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="176" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="146"/>
+      <c r="D8" s="176"/>
       <c r="F8" s="128" t="s">
         <v>195</v>
       </c>
@@ -14781,10 +14226,10 @@
       <c r="B9" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="176" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="146"/>
+      <c r="D9" s="176"/>
       <c r="F9" s="42" t="s">
         <v>194</v>
       </c>
@@ -14855,22 +14300,22 @@
         <v>219</v>
       </c>
       <c r="AC9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH9" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI9" s="42" t="s">
         <v>219</v>
@@ -14903,10 +14348,10 @@
       <c r="B10" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="176" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="146"/>
+      <c r="D10" s="176"/>
       <c r="F10" s="49" t="s">
         <v>218</v>
       </c>
@@ -15025,10 +14470,10 @@
       <c r="B11" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="176" t="s">
         <v>157</v>
       </c>
-      <c r="D11" s="146"/>
+      <c r="D11" s="176"/>
       <c r="F11" s="49" t="s">
         <v>219</v>
       </c>
@@ -15147,10 +14592,10 @@
       <c r="B12" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="176" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="146"/>
+      <c r="D12" s="176"/>
       <c r="F12" s="49" t="s">
         <v>195</v>
       </c>
@@ -15269,10 +14714,10 @@
       <c r="B13" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="176" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="146"/>
+      <c r="D13" s="176"/>
       <c r="F13" s="49" t="s">
         <v>219</v>
       </c>
@@ -15301,22 +14746,22 @@
         <v>219</v>
       </c>
       <c r="O13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T13" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U13" s="49" t="s">
         <v>219</v>
@@ -15392,10 +14837,10 @@
       <c r="B14" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C14" s="146" t="s">
+      <c r="C14" s="176" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="146"/>
+      <c r="D14" s="176"/>
       <c r="F14" s="56" t="s">
         <v>194</v>
       </c>
@@ -15514,10 +14959,10 @@
       <c r="B15" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="156" t="s">
+      <c r="C15" s="185" t="s">
         <v>190</v>
       </c>
-      <c r="D15" s="157"/>
+      <c r="D15" s="186"/>
       <c r="E15" s="77"/>
       <c r="F15" s="99" t="s">
         <v>194</v>
@@ -15637,10 +15082,10 @@
       <c r="B16" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="146" t="s">
+      <c r="C16" s="176" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="153"/>
+      <c r="D16" s="146"/>
       <c r="E16" s="77"/>
       <c r="F16" s="96" t="s">
         <v>194</v>
@@ -15664,10 +15109,10 @@
         <v>219</v>
       </c>
       <c r="M16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O16" s="96" t="s">
         <v>195</v>
@@ -15712,22 +15157,22 @@
         <v>219</v>
       </c>
       <c r="AC16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI16" s="96" t="s">
         <v>219</v>
@@ -15760,10 +15205,10 @@
       <c r="B17" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C17" s="176" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="153"/>
+      <c r="D17" s="146"/>
       <c r="E17" s="77"/>
       <c r="F17" s="96" t="s">
         <v>195</v>
@@ -15883,10 +15328,10 @@
       <c r="B18" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="176" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="153"/>
+      <c r="D18" s="146"/>
       <c r="E18" s="77"/>
       <c r="F18" s="96" t="s">
         <v>218</v>
@@ -16006,64 +15451,64 @@
       <c r="B19" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="176" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="153"/>
+      <c r="D19" s="146"/>
       <c r="E19" s="77"/>
       <c r="F19" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N19" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V19" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W19" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X19" s="96" t="s">
         <v>219</v>
@@ -16129,10 +15574,10 @@
       <c r="B20" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="176" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="153"/>
+      <c r="D20" s="146"/>
       <c r="E20" s="77"/>
       <c r="F20" s="96" t="s">
         <v>219</v>
@@ -16252,10 +15697,10 @@
       <c r="B21" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C21" s="146" t="s">
+      <c r="C21" s="176" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="153"/>
+      <c r="D21" s="146"/>
       <c r="E21" s="77"/>
       <c r="F21" s="96" t="s">
         <v>219</v>
@@ -16285,22 +15730,22 @@
         <v>219</v>
       </c>
       <c r="O21" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P21" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q21" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R21" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S21" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T21" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U21" s="96" t="s">
         <v>219</v>
@@ -16375,10 +15820,10 @@
       <c r="B22" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C22" s="146" t="s">
+      <c r="C22" s="176" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="153"/>
+      <c r="D22" s="146"/>
       <c r="E22" s="77"/>
       <c r="F22" s="96" t="s">
         <v>194</v>
@@ -16429,22 +15874,22 @@
         <v>219</v>
       </c>
       <c r="V22" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W22" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X22" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y22" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z22" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA22" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB22" s="96" t="s">
         <v>219</v>
@@ -16498,10 +15943,10 @@
       <c r="B23" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="146" t="s">
+      <c r="C23" s="176" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="153"/>
+      <c r="D23" s="146"/>
       <c r="E23" s="77"/>
       <c r="F23" s="96" t="s">
         <v>195</v>
@@ -16621,10 +16066,10 @@
       <c r="B24" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C24" s="146" t="s">
+      <c r="C24" s="176" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="153"/>
+      <c r="D24" s="146"/>
       <c r="E24" s="77"/>
       <c r="F24" s="96" t="s">
         <v>195</v>
@@ -16744,10 +16189,10 @@
       <c r="B25" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="146" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="162"/>
+      <c r="D25" s="191"/>
       <c r="E25" s="77"/>
       <c r="F25" s="96" t="s">
         <v>218</v>
@@ -16867,10 +16312,10 @@
       <c r="B26" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="146" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="162"/>
+      <c r="D26" s="191"/>
       <c r="E26" s="77"/>
       <c r="F26" s="96" t="s">
         <v>218</v>
@@ -16933,37 +16378,37 @@
         <v>219</v>
       </c>
       <c r="Z26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ26" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AL26" s="48">
         <f t="shared" si="10"/>
@@ -16990,10 +16435,10 @@
       <c r="B27" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="146" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="162"/>
+      <c r="D27" s="191"/>
       <c r="E27" s="77"/>
       <c r="F27" s="101" t="s">
         <v>219</v>
@@ -17005,22 +16450,22 @@
         <v>219</v>
       </c>
       <c r="I27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N27" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O27" s="96" t="s">
         <v>219</v>
@@ -17113,10 +16558,10 @@
       <c r="B28" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C28" s="158" t="s">
+      <c r="C28" s="187" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="159"/>
+      <c r="D28" s="188"/>
       <c r="E28" s="77"/>
       <c r="F28" s="106" t="s">
         <v>219</v>
@@ -17170,22 +16615,22 @@
         <v>219</v>
       </c>
       <c r="W28" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X28" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y28" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z28" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA28" s="125" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB28" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC28" s="106" t="s">
         <v>219</v>
@@ -17236,10 +16681,10 @@
       <c r="B29" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C29" s="160" t="s">
+      <c r="C29" s="189" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="161"/>
+      <c r="D29" s="190"/>
       <c r="E29" s="66"/>
       <c r="F29" s="98" t="s">
         <v>219</v>
@@ -17296,43 +16741,43 @@
         <v>219</v>
       </c>
       <c r="X29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB29" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC29" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI29" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ29" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AL29" s="48">
         <f t="shared" si="10"/>
@@ -17359,10 +16804,10 @@
       <c r="B30" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="176" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="146"/>
+      <c r="D30" s="176"/>
       <c r="F30" s="99" t="s">
         <v>194</v>
       </c>
@@ -17481,10 +16926,10 @@
       <c r="B31" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="176" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="146"/>
+      <c r="D31" s="176"/>
       <c r="F31" s="96" t="s">
         <v>195</v>
       </c>
@@ -17603,10 +17048,10 @@
       <c r="B32" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="146" t="s">
+      <c r="C32" s="176" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="146"/>
+      <c r="D32" s="176"/>
       <c r="F32" s="96" t="s">
         <v>195</v>
       </c>
@@ -17725,10 +17170,10 @@
       <c r="B33" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C33" s="146" t="s">
+      <c r="C33" s="176" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="146"/>
+      <c r="D33" s="176"/>
       <c r="F33" s="96" t="s">
         <v>218</v>
       </c>
@@ -17847,10 +17292,10 @@
       <c r="B34" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="146" t="s">
+      <c r="C34" s="176" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="146"/>
+      <c r="D34" s="176"/>
       <c r="F34" s="96" t="s">
         <v>219</v>
       </c>
@@ -17969,10 +17414,10 @@
       <c r="B35" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C35" s="146" t="s">
+      <c r="C35" s="176" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="146"/>
+      <c r="D35" s="176"/>
       <c r="F35" s="96" t="s">
         <v>218</v>
       </c>
@@ -18091,10 +17536,10 @@
       <c r="B36" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C36" s="146" t="s">
+      <c r="C36" s="176" t="s">
         <v>135</v>
       </c>
-      <c r="D36" s="146"/>
+      <c r="D36" s="176"/>
       <c r="F36" s="96" t="s">
         <v>194</v>
       </c>
@@ -18213,10 +17658,10 @@
       <c r="B37" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C37" s="146" t="s">
+      <c r="C37" s="176" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="146"/>
+      <c r="D37" s="176"/>
       <c r="F37" s="96" t="s">
         <v>195</v>
       </c>
@@ -18335,10 +17780,10 @@
       <c r="B38" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="146" t="s">
+      <c r="C38" s="176" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="146"/>
+      <c r="D38" s="176"/>
       <c r="F38" s="96" t="s">
         <v>218</v>
       </c>
@@ -18400,22 +17845,22 @@
         <v>219</v>
       </c>
       <c r="Z38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE38" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF38" s="96" t="s">
         <v>219</v>
@@ -18457,10 +17902,10 @@
       <c r="B39" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C39" s="176" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="146"/>
+      <c r="D39" s="176"/>
       <c r="F39" s="96" t="s">
         <v>219</v>
       </c>
@@ -18468,85 +17913,85 @@
         <v>219</v>
       </c>
       <c r="H39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH39" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI39" s="96" t="s">
         <v>218</v>
@@ -18579,10 +18024,10 @@
       <c r="B40" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="146" t="s">
+      <c r="C40" s="176" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="146"/>
+      <c r="D40" s="176"/>
       <c r="F40" s="96" t="s">
         <v>194</v>
       </c>
@@ -18701,10 +18146,10 @@
       <c r="B41" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="176" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="146"/>
+      <c r="D41" s="176"/>
       <c r="F41" s="96" t="s">
         <v>194</v>
       </c>
@@ -18823,10 +18268,10 @@
       <c r="B42" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C42" s="146" t="s">
+      <c r="C42" s="176" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="146"/>
+      <c r="D42" s="176"/>
       <c r="F42" s="96" t="s">
         <v>195</v>
       </c>
@@ -18906,7 +18351,7 @@
         <v>218</v>
       </c>
       <c r="AF42" s="96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG42" s="96" t="s">
         <v>126</v>
@@ -18945,10 +18390,10 @@
       <c r="B43" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C43" s="146" t="s">
+      <c r="C43" s="176" t="s">
         <v>142</v>
       </c>
-      <c r="D43" s="146"/>
+      <c r="D43" s="176"/>
       <c r="F43" s="96" t="s">
         <v>218</v>
       </c>
@@ -19067,10 +18512,10 @@
       <c r="B44" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C44" s="146" t="s">
+      <c r="C44" s="176" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="146"/>
+      <c r="D44" s="176"/>
       <c r="F44" s="96" t="s">
         <v>219</v>
       </c>
@@ -19189,10 +18634,10 @@
       <c r="B45" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C45" s="146" t="s">
+      <c r="C45" s="176" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="146"/>
+      <c r="D45" s="176"/>
       <c r="F45" s="96" t="s">
         <v>219</v>
       </c>
@@ -19311,10 +18756,10 @@
       <c r="B46" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="146" t="s">
+      <c r="C46" s="176" t="s">
         <v>146</v>
       </c>
-      <c r="D46" s="146"/>
+      <c r="D46" s="176"/>
       <c r="F46" s="96" t="s">
         <v>219</v>
       </c>
@@ -19433,10 +18878,10 @@
       <c r="B47" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C47" s="146" t="s">
+      <c r="C47" s="176" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="146"/>
+      <c r="D47" s="176"/>
       <c r="F47" s="96" t="s">
         <v>194</v>
       </c>
@@ -19555,10 +19000,10 @@
       <c r="B48" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="153" t="s">
+      <c r="C48" s="146" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="154"/>
+      <c r="D48" s="147"/>
       <c r="F48" s="96" t="s">
         <v>194</v>
       </c>
@@ -19581,10 +19026,10 @@
         <v>219</v>
       </c>
       <c r="M48" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N48" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O48" s="96" t="s">
         <v>195</v>
@@ -19677,10 +19122,10 @@
       <c r="B49" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C49" s="146" t="s">
+      <c r="C49" s="176" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="146"/>
+      <c r="D49" s="176"/>
       <c r="F49" s="96" t="s">
         <v>195</v>
       </c>
@@ -19799,10 +19244,10 @@
       <c r="B50" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C50" s="146" t="s">
+      <c r="C50" s="176" t="s">
         <v>149</v>
       </c>
-      <c r="D50" s="146"/>
+      <c r="D50" s="176"/>
       <c r="F50" s="96" t="s">
         <v>218</v>
       </c>
@@ -19921,10 +19366,10 @@
       <c r="B51" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C51" s="146" t="s">
+      <c r="C51" s="176" t="s">
         <v>151</v>
       </c>
-      <c r="D51" s="146"/>
+      <c r="D51" s="176"/>
       <c r="F51" s="96" t="s">
         <v>218</v>
       </c>
@@ -20043,10 +19488,10 @@
       <c r="B52" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C52" s="153" t="s">
+      <c r="C52" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="154"/>
+      <c r="D52" s="147"/>
       <c r="F52" s="96" t="s">
         <v>219</v>
       </c>
@@ -20054,22 +19499,22 @@
         <v>219</v>
       </c>
       <c r="H52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M52" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N52" s="96" t="s">
         <v>219</v>
@@ -20165,10 +19610,10 @@
       <c r="B53" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C53" s="153" t="s">
+      <c r="C53" s="146" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="154"/>
+      <c r="D53" s="147"/>
       <c r="F53" s="96" t="s">
         <v>219</v>
       </c>
@@ -20287,12 +19732,12 @@
       <c r="B54" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C54" s="153" t="s">
+      <c r="C54" s="146" t="s">
         <v>177</v>
       </c>
-      <c r="D54" s="154"/>
+      <c r="D54" s="147"/>
       <c r="F54" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G54" s="96" t="s">
         <v>195</v>
@@ -20409,10 +19854,10 @@
       <c r="B55" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C55" s="146" t="s">
+      <c r="C55" s="176" t="s">
         <v>223</v>
       </c>
-      <c r="D55" s="146"/>
+      <c r="D55" s="176"/>
       <c r="F55" s="96" t="s">
         <v>218</v>
       </c>
@@ -20517,7 +19962,7 @@
         <v>213</v>
       </c>
       <c r="C56" s="133" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D56" s="134"/>
       <c r="F56" s="96" t="s">
@@ -20623,10 +20068,10 @@
       <c r="B57" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C57" s="153" t="s">
+      <c r="C57" s="146" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="154"/>
+      <c r="D57" s="147"/>
       <c r="F57" s="96" t="s">
         <v>195</v>
       </c>
@@ -20745,10 +20190,10 @@
       <c r="B58" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C58" s="153" t="s">
+      <c r="C58" s="146" t="s">
         <v>224</v>
       </c>
-      <c r="D58" s="154"/>
+      <c r="D58" s="147"/>
       <c r="F58" s="96" t="s">
         <v>195</v>
       </c>
@@ -20867,10 +20312,10 @@
       <c r="B59" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C59" s="146" t="s">
+      <c r="C59" s="176" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="146"/>
+      <c r="D59" s="176"/>
       <c r="F59" s="96" t="s">
         <v>218</v>
       </c>
@@ -20989,10 +20434,10 @@
       <c r="B60" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C60" s="163" t="s">
+      <c r="C60" s="177" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="163"/>
+      <c r="D60" s="177"/>
       <c r="F60" s="98" t="s">
         <v>194</v>
       </c>
@@ -21111,10 +20556,10 @@
       <c r="B61" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C61" s="153" t="s">
+      <c r="C61" s="146" t="s">
         <v>174</v>
       </c>
-      <c r="D61" s="154"/>
+      <c r="D61" s="147"/>
       <c r="F61" s="94" t="s">
         <v>194</v>
       </c>
@@ -21233,10 +20678,10 @@
       <c r="B62" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C62" s="153" t="s">
+      <c r="C62" s="146" t="s">
         <v>165</v>
       </c>
-      <c r="D62" s="154"/>
+      <c r="D62" s="147"/>
       <c r="F62" s="94" t="s">
         <v>194</v>
       </c>
@@ -21355,10 +20800,10 @@
       <c r="B63" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C63" s="153" t="s">
+      <c r="C63" s="146" t="s">
         <v>221</v>
       </c>
-      <c r="D63" s="154"/>
+      <c r="D63" s="147"/>
       <c r="F63" s="95" t="s">
         <v>195</v>
       </c>
@@ -21477,10 +20922,10 @@
       <c r="B64" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C64" s="153" t="s">
+      <c r="C64" s="146" t="s">
         <v>166</v>
       </c>
-      <c r="D64" s="154"/>
+      <c r="D64" s="147"/>
       <c r="F64" s="96" t="s">
         <v>218</v>
       </c>
@@ -21599,10 +21044,10 @@
       <c r="B65" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C65" s="153" t="s">
+      <c r="C65" s="146" t="s">
         <v>167</v>
       </c>
-      <c r="D65" s="154"/>
+      <c r="D65" s="147"/>
       <c r="F65" s="96" t="s">
         <v>218</v>
       </c>
@@ -21721,10 +21166,10 @@
       <c r="B66" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C66" s="153" t="s">
+      <c r="C66" s="146" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="154"/>
+      <c r="D66" s="147"/>
       <c r="F66" s="96" t="s">
         <v>219</v>
       </c>
@@ -21843,10 +21288,10 @@
       <c r="B67" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C67" s="153" t="s">
+      <c r="C67" s="146" t="s">
         <v>169</v>
       </c>
-      <c r="D67" s="154"/>
+      <c r="D67" s="147"/>
       <c r="F67" s="94" t="s">
         <v>219</v>
       </c>
@@ -21965,10 +21410,10 @@
       <c r="B68" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="153" t="s">
+      <c r="C68" s="146" t="s">
         <v>170</v>
       </c>
-      <c r="D68" s="154"/>
+      <c r="D68" s="147"/>
       <c r="F68" s="94" t="s">
         <v>194</v>
       </c>
@@ -22087,10 +21532,10 @@
       <c r="B69" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="C69" s="153" t="s">
+      <c r="C69" s="146" t="s">
         <v>175</v>
       </c>
-      <c r="D69" s="154"/>
+      <c r="D69" s="147"/>
       <c r="F69" s="94" t="s">
         <v>195</v>
       </c>
@@ -22209,10 +21654,10 @@
       <c r="B70" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="153" t="s">
+      <c r="C70" s="146" t="s">
         <v>171</v>
       </c>
-      <c r="D70" s="154"/>
+      <c r="D70" s="147"/>
       <c r="F70" s="94" t="s">
         <v>195</v>
       </c>
@@ -22331,10 +21776,10 @@
       <c r="B71" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="C71" s="153" t="s">
+      <c r="C71" s="146" t="s">
         <v>172</v>
       </c>
-      <c r="D71" s="154"/>
+      <c r="D71" s="147"/>
       <c r="F71" s="95" t="s">
         <v>219</v>
       </c>
@@ -22453,10 +21898,10 @@
       <c r="B72" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="C72" s="153" t="s">
+      <c r="C72" s="146" t="s">
         <v>173</v>
       </c>
-      <c r="D72" s="154"/>
+      <c r="D72" s="147"/>
       <c r="F72" s="94" t="s">
         <v>219</v>
       </c>
@@ -22525,10 +21970,10 @@
       <c r="B73" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="C73" s="153" t="s">
+      <c r="C73" s="146" t="s">
         <v>176</v>
       </c>
-      <c r="D73" s="154"/>
+      <c r="D73" s="147"/>
       <c r="F73" s="94" t="s">
         <v>194</v>
       </c>
@@ -22820,10 +22265,10 @@
       </c>
     </row>
     <row r="76" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C76" s="170" t="s">
+      <c r="C76" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="D76" s="170"/>
+      <c r="D76" s="184"/>
       <c r="E76" s="36"/>
       <c r="F76" s="37">
         <f t="shared" ref="F76:AJ76" si="25">COUNTIF(F9:F74,"M*")</f>
@@ -22971,10 +22416,10 @@
       </c>
     </row>
     <row r="77" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C77" s="170" t="s">
+      <c r="C77" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="170"/>
+      <c r="D77" s="184"/>
       <c r="E77" s="36"/>
       <c r="F77" s="37">
         <f t="shared" ref="F77:AJ77" si="26">COUNTIF(F9:F74,"A*")</f>
@@ -23122,10 +22567,10 @@
       </c>
     </row>
     <row r="78" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C78" s="170" t="s">
+      <c r="C78" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D78" s="170"/>
+      <c r="D78" s="184"/>
       <c r="E78" s="36"/>
       <c r="F78" s="37">
         <f t="shared" ref="F78:AJ78" si="27">COUNTIF(F9:F74,"N*")</f>
@@ -23273,10 +22718,10 @@
       </c>
     </row>
     <row r="79" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C79" s="170" t="s">
+      <c r="C79" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D79" s="170"/>
+      <c r="D79" s="184"/>
       <c r="E79" s="36"/>
       <c r="F79" s="37">
         <f t="shared" ref="F79:AJ79" si="28">COUNTIF(F$30:F$74,"O*")</f>
@@ -23424,10 +22869,10 @@
       </c>
     </row>
     <row r="80" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C80" s="166" t="s">
+      <c r="C80" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D80" s="167"/>
+      <c r="D80" s="181"/>
       <c r="E80" s="36"/>
       <c r="F80" s="37">
         <f t="shared" ref="F80:AJ80" si="29">COUNTIF(F9:F74,"TR*")</f>
@@ -23575,10 +23020,10 @@
       </c>
     </row>
     <row r="81" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C81" s="166" t="s">
+      <c r="C81" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D81" s="167"/>
+      <c r="D81" s="181"/>
       <c r="E81" s="36"/>
       <c r="F81" s="37">
         <f>COUNTIF(F9:F74,"ST*")</f>
@@ -23726,10 +23171,10 @@
       </c>
     </row>
     <row r="82" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C82" s="168" t="s">
+      <c r="C82" s="182" t="s">
         <v>248</v>
       </c>
-      <c r="D82" s="168"/>
+      <c r="D82" s="182"/>
       <c r="E82" s="38"/>
       <c r="F82" s="51">
         <f t="shared" ref="F82:AJ82" si="31">COUNTIF(F$5:F$74,"OT*")</f>
@@ -23880,37 +23325,37 @@
       <c r="C83" s="40"/>
       <c r="D83" s="40"/>
       <c r="E83" s="36"/>
-      <c r="F83" s="169"/>
-      <c r="G83" s="169"/>
-      <c r="H83" s="169"/>
-      <c r="I83" s="169"/>
-      <c r="J83" s="169"/>
-      <c r="K83" s="169"/>
-      <c r="L83" s="169"/>
-      <c r="M83" s="169"/>
-      <c r="N83" s="169"/>
-      <c r="O83" s="169"/>
-      <c r="P83" s="169"/>
-      <c r="Q83" s="169"/>
-      <c r="R83" s="169"/>
-      <c r="S83" s="169"/>
-      <c r="T83" s="169"/>
-      <c r="U83" s="169"/>
-      <c r="V83" s="169"/>
-      <c r="W83" s="169"/>
-      <c r="X83" s="169"/>
-      <c r="Y83" s="169"/>
-      <c r="Z83" s="169"/>
-      <c r="AA83" s="169"/>
-      <c r="AB83" s="169"/>
-      <c r="AC83" s="169"/>
-      <c r="AD83" s="169"/>
-      <c r="AE83" s="169"/>
-      <c r="AF83" s="169"/>
-      <c r="AG83" s="169"/>
-      <c r="AH83" s="169"/>
-      <c r="AI83" s="169"/>
-      <c r="AJ83" s="169"/>
+      <c r="F83" s="183"/>
+      <c r="G83" s="183"/>
+      <c r="H83" s="183"/>
+      <c r="I83" s="183"/>
+      <c r="J83" s="183"/>
+      <c r="K83" s="183"/>
+      <c r="L83" s="183"/>
+      <c r="M83" s="183"/>
+      <c r="N83" s="183"/>
+      <c r="O83" s="183"/>
+      <c r="P83" s="183"/>
+      <c r="Q83" s="183"/>
+      <c r="R83" s="183"/>
+      <c r="S83" s="183"/>
+      <c r="T83" s="183"/>
+      <c r="U83" s="183"/>
+      <c r="V83" s="183"/>
+      <c r="W83" s="183"/>
+      <c r="X83" s="183"/>
+      <c r="Y83" s="183"/>
+      <c r="Z83" s="183"/>
+      <c r="AA83" s="183"/>
+      <c r="AB83" s="183"/>
+      <c r="AC83" s="183"/>
+      <c r="AD83" s="183"/>
+      <c r="AE83" s="183"/>
+      <c r="AF83" s="183"/>
+      <c r="AG83" s="183"/>
+      <c r="AH83" s="183"/>
+      <c r="AI83" s="183"/>
+      <c r="AJ83" s="183"/>
       <c r="AL83" s="48">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -23933,10 +23378,10 @@
       </c>
     </row>
     <row r="84" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C84" s="170" t="s">
+      <c r="C84" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="170"/>
+      <c r="D84" s="184"/>
       <c r="E84" s="36"/>
       <c r="F84" s="41">
         <f>SUM(F76:F78)</f>
@@ -24083,10 +23528,10 @@
       </c>
     </row>
     <row r="85" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C85" s="170" t="s">
+      <c r="C85" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D85" s="170"/>
+      <c r="D85" s="184"/>
       <c r="E85" s="36"/>
       <c r="F85" s="37">
         <v>45</v>
@@ -24203,10 +23648,10 @@
       </c>
     </row>
     <row r="86" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C86" s="170" t="s">
+      <c r="C86" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="D86" s="170"/>
+      <c r="D86" s="184"/>
       <c r="E86" s="36"/>
       <c r="F86" s="37">
         <f>SUM(F76,F77,F78,F79,F81)</f>
@@ -24375,14 +23820,14 @@
       </c>
     </row>
     <row r="88" spans="3:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F88" s="186" t="s">
+      <c r="F88" s="163" t="s">
         <v>197</v>
       </c>
-      <c r="G88" s="187"/>
-      <c r="H88" s="187"/>
-      <c r="I88" s="187"/>
-      <c r="J88" s="187"/>
-      <c r="K88" s="188"/>
+      <c r="G88" s="164"/>
+      <c r="H88" s="164"/>
+      <c r="I88" s="164"/>
+      <c r="J88" s="164"/>
+      <c r="K88" s="165"/>
       <c r="AL88" s="48" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -24408,17 +23853,17 @@
       <c r="F89" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="G89" s="189" t="s">
+      <c r="G89" s="166" t="s">
         <v>193</v>
       </c>
-      <c r="H89" s="190"/>
+      <c r="H89" s="167"/>
       <c r="I89" s="73" t="s">
         <v>194</v>
       </c>
-      <c r="J89" s="174" t="s">
+      <c r="J89" s="151" t="s">
         <v>205</v>
       </c>
-      <c r="K89" s="175"/>
+      <c r="K89" s="152"/>
       <c r="AL89" s="48" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -24444,17 +23889,17 @@
       <c r="F90" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="G90" s="191" t="s">
-        <v>194</v>
-      </c>
-      <c r="H90" s="192"/>
+      <c r="G90" s="168" t="s">
+        <v>194</v>
+      </c>
+      <c r="H90" s="169"/>
       <c r="I90" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="J90" s="193" t="s">
+      <c r="J90" s="170" t="s">
         <v>206</v>
       </c>
-      <c r="K90" s="194"/>
+      <c r="K90" s="171"/>
       <c r="AL90" s="48" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -24480,17 +23925,17 @@
       <c r="F91" s="69" t="s">
         <v>191</v>
       </c>
-      <c r="G91" s="195" t="s">
-        <v>195</v>
-      </c>
-      <c r="H91" s="196"/>
+      <c r="G91" s="172" t="s">
+        <v>195</v>
+      </c>
+      <c r="H91" s="173"/>
       <c r="I91" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="J91" s="197" t="s">
+      <c r="J91" s="174" t="s">
         <v>207</v>
       </c>
-      <c r="K91" s="198"/>
+      <c r="K91" s="175"/>
       <c r="AL91" s="48" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -24516,91 +23961,122 @@
       <c r="F92" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="G92" s="164" t="s">
+      <c r="G92" s="178" t="s">
         <v>196</v>
       </c>
-      <c r="H92" s="165"/>
+      <c r="H92" s="179"/>
       <c r="I92" s="75" t="s">
         <v>211</v>
       </c>
-      <c r="J92" s="176" t="s">
+      <c r="J92" s="153" t="s">
         <v>208</v>
       </c>
-      <c r="K92" s="177"/>
+      <c r="K92" s="154"/>
     </row>
     <row r="93" spans="3:42" x14ac:dyDescent="0.25">
       <c r="F93" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G93" s="178" t="s">
+      <c r="G93" s="155" t="s">
         <v>199</v>
       </c>
-      <c r="H93" s="179"/>
+      <c r="H93" s="156"/>
       <c r="I93" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="J93" s="180" t="s">
+      <c r="J93" s="157" t="s">
         <v>209</v>
       </c>
-      <c r="K93" s="181"/>
+      <c r="K93" s="158"/>
     </row>
     <row r="94" spans="3:42" x14ac:dyDescent="0.25">
       <c r="F94" s="72"/>
-      <c r="G94" s="182" t="s">
+      <c r="G94" s="159" t="s">
         <v>198</v>
       </c>
-      <c r="H94" s="183"/>
+      <c r="H94" s="160"/>
       <c r="I94" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="J94" s="184" t="s">
+      <c r="J94" s="161" t="s">
         <v>210</v>
       </c>
-      <c r="K94" s="185"/>
+      <c r="K94" s="162"/>
     </row>
     <row r="95" spans="3:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F95" s="79" t="s">
         <v>216</v>
       </c>
-      <c r="G95" s="171" t="s">
+      <c r="G95" s="148" t="s">
         <v>217</v>
       </c>
-      <c r="H95" s="172"/>
+      <c r="H95" s="149"/>
       <c r="I95" s="80" t="s">
         <v>214</v>
       </c>
-      <c r="J95" s="171" t="s">
+      <c r="J95" s="148" t="s">
         <v>215</v>
       </c>
-      <c r="K95" s="173"/>
+      <c r="K95" s="150"/>
     </row>
     <row r="100" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="F4:AJ82" xr:uid="{10A87D31-A428-49C7-B3CE-66B468A7BADA}"/>
   <mergeCells count="101">
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="J95:K95"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="J93:K93"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="J94:K94"/>
-    <mergeCell ref="F88:K88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="C51:D51"/>
@@ -24625,274 +24101,241 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C69:D69"/>
     <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="F88:K88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="J91:K91"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="F61:AJ74">
-    <cfRule type="containsText" dxfId="67" priority="55" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F61)))</formula>
+  <conditionalFormatting sqref="F5:AJ8">
+    <cfRule type="containsText" dxfId="168" priority="1" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="56" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F61)))</formula>
+    <cfRule type="containsText" dxfId="167" priority="2" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="57" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F61)))</formula>
+    <cfRule type="containsText" dxfId="166" priority="3" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="58" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F61)))</formula>
+    <cfRule type="containsText" dxfId="165" priority="4" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="59" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F61)))</formula>
+    <cfRule type="containsText" dxfId="164" priority="5" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="60" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F61)))</formula>
+    <cfRule type="containsText" dxfId="163" priority="6" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="61" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F61)))</formula>
+    <cfRule type="containsText" dxfId="162" priority="7" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="62" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F61)))</formula>
+    <cfRule type="containsText" dxfId="161" priority="8" operator="containsText" text="ME07">
+      <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="63" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F61)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:AJ14">
+    <cfRule type="containsText" dxfId="160" priority="9" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="64" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F61)))</formula>
+    <cfRule type="containsText" dxfId="159" priority="11" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="65" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F61)))</formula>
+    <cfRule type="containsText" dxfId="158" priority="12" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",F9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="66" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F61)))</formula>
+    <cfRule type="containsText" dxfId="157" priority="13" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="67" operator="containsText" text="NN13">
-      <formula>NOT(ISERROR(SEARCH("NN13",F61)))</formula>
+    <cfRule type="containsText" dxfId="156" priority="14" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="68" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F61)))</formula>
+    <cfRule type="containsText" dxfId="155" priority="15" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="154" priority="16" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="153" priority="17" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="152" priority="18" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="151" priority="19" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="150" priority="20" operator="containsText" text="MN12">
+      <formula>NOT(ISERROR(SEARCH("MN12",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="149" priority="21" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="148" priority="22" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:AJ29">
+    <cfRule type="containsText" dxfId="147" priority="10" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:AJ29">
+    <cfRule type="containsText" dxfId="146" priority="36" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="145" priority="24" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="144" priority="25" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="143" priority="26" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="142" priority="27" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="141" priority="28" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="140" priority="29" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="139" priority="30" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="138" priority="31" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="137" priority="32" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="136" priority="33" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="135" priority="34" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="134" priority="35" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:AJ60">
-    <cfRule type="containsText" dxfId="53" priority="37" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="133" priority="52" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="132" priority="37" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="38" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="131" priority="38" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="39" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="130" priority="39" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="40" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="129" priority="40" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="41" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="128" priority="41" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="42" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="127" priority="43" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="126" priority="44" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="125" priority="45" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="43" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="124" priority="46" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="44" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="45" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="46" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="47" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="123" priority="47" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="48" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="122" priority="48" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="49" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="121" priority="49" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="50" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="120" priority="50" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="119" priority="51" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="53" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="118" priority="53" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="54" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="117" priority="54" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:AJ29">
-    <cfRule type="containsText" dxfId="35" priority="23" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="24" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="25" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="26" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="27" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="28" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="31" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="32" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="33" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="34" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F15)))</formula>
+  <conditionalFormatting sqref="F30:AJ74">
+    <cfRule type="containsText" dxfId="116" priority="42" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9:AJ14">
-    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F9)))</formula>
+  <conditionalFormatting sqref="F61:AJ74">
+    <cfRule type="containsText" dxfId="115" priority="68" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="10" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F9)))</formula>
+    <cfRule type="containsText" dxfId="114" priority="56" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F9)))</formula>
+    <cfRule type="containsText" dxfId="113" priority="57" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="12" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F9)))</formula>
+    <cfRule type="containsText" dxfId="112" priority="58" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F9)))</formula>
+    <cfRule type="containsText" dxfId="111" priority="59" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="14" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F9)))</formula>
+    <cfRule type="containsText" dxfId="110" priority="60" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F9)))</formula>
+    <cfRule type="containsText" dxfId="109" priority="61" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F9)))</formula>
+    <cfRule type="containsText" dxfId="108" priority="62" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="17" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F9)))</formula>
+    <cfRule type="containsText" dxfId="107" priority="63" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="18" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F9)))</formula>
+    <cfRule type="containsText" dxfId="106" priority="64" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F9)))</formula>
+    <cfRule type="containsText" dxfId="105" priority="65" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="20" operator="containsText" text="MN12">
-      <formula>NOT(ISERROR(SEARCH("MN12",F9)))</formula>
+    <cfRule type="containsText" dxfId="104" priority="66" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F61)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F9)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="22" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ8">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="ME07">
-      <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
+    <cfRule type="containsText" dxfId="103" priority="67" operator="containsText" text="NN13">
+      <formula>NOT(ISERROR(SEARCH("NN13",F61)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24920,61 +24363,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="192" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="149"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="193"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="193"/>
+      <c r="Q2" s="193"/>
+      <c r="R2" s="193"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="W2" s="193"/>
+      <c r="X2" s="193"/>
+      <c r="Y2" s="193"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="193"/>
+      <c r="AB2" s="193"/>
+      <c r="AC2" s="193"/>
+      <c r="AD2" s="193"/>
+      <c r="AE2" s="193"/>
+      <c r="AF2" s="193"/>
+      <c r="AG2" s="193"/>
+      <c r="AH2" s="193"/>
+      <c r="AI2" s="193"/>
+      <c r="AJ2" s="194"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
       <c r="F3" s="46" t="s">
         <v>98</v>
       </c>
@@ -25068,16 +24511,16 @@
       <c r="AJ3" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
       <c r="F4" s="43">
         <v>1</v>
       </c>
@@ -25171,22 +24614,22 @@
       <c r="AJ4" s="82">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="37">
         <v>1</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="176" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="176"/>
       <c r="F5" s="127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G5" s="127" t="s">
         <v>219</v>
@@ -25303,10 +24746,10 @@
       <c r="B6" s="37">
         <v>2</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="176" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="146"/>
+      <c r="D6" s="176"/>
       <c r="F6" s="128" t="s">
         <v>202</v>
       </c>
@@ -25425,10 +24868,10 @@
       <c r="B7" s="37">
         <v>4</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C7" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="D7" s="154"/>
+      <c r="D7" s="147"/>
       <c r="F7" s="128" t="s">
         <v>194</v>
       </c>
@@ -25532,10 +24975,10 @@
       <c r="B8" s="37">
         <v>4</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="176" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="146"/>
+      <c r="D8" s="176"/>
       <c r="F8" s="128" t="s">
         <v>195</v>
       </c>
@@ -25685,10 +25128,10 @@
       <c r="AI9" s="20"/>
     </row>
     <row r="10" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C10" s="170" t="s">
+      <c r="C10" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="170"/>
+      <c r="D10" s="184"/>
       <c r="E10" s="36"/>
       <c r="F10" s="37">
         <f t="shared" ref="F10:AJ10" si="5">COUNTIF(F$5:F$8,"M*")</f>
@@ -25816,10 +25259,10 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C11" s="170" t="s">
+      <c r="C11" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="170"/>
+      <c r="D11" s="184"/>
       <c r="E11" s="36"/>
       <c r="F11" s="37">
         <f t="shared" ref="F11:AJ11" si="6">COUNTIF(F$5:F$8,"A*")</f>
@@ -25947,10 +25390,10 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C12" s="170" t="s">
+      <c r="C12" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="170"/>
+      <c r="D12" s="184"/>
       <c r="E12" s="36"/>
       <c r="F12" s="37">
         <f t="shared" ref="F12:AJ12" si="7">COUNTIF(F$5:F$8,"N*")</f>
@@ -26078,10 +25521,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C13" s="170" t="s">
+      <c r="C13" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="170"/>
+      <c r="D13" s="184"/>
       <c r="E13" s="36"/>
       <c r="F13" s="37">
         <f t="shared" ref="F13:AJ13" si="8">COUNTIF(F$5:F$8,"O*")</f>
@@ -26209,10 +25652,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="167"/>
+      <c r="D14" s="181"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37">
         <f t="shared" ref="F14:AJ14" si="9">COUNTIF(F$5:F$8,"TR*")</f>
@@ -26340,10 +25783,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C15" s="166" t="s">
+      <c r="C15" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="167"/>
+      <c r="D15" s="181"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37">
         <f t="shared" ref="F15:AJ15" si="10">COUNTIF(F$5:F$8,"ST*")</f>
@@ -26471,10 +25914,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="182" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="168"/>
+      <c r="D16" s="182"/>
       <c r="E16" s="38"/>
       <c r="F16" s="51">
         <f>F18-F19</f>
@@ -26605,43 +26048,43 @@
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
       <c r="E17" s="36"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="169"/>
-      <c r="M17" s="169"/>
-      <c r="N17" s="169"/>
-      <c r="O17" s="169"/>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="169"/>
-      <c r="R17" s="169"/>
-      <c r="S17" s="169"/>
-      <c r="T17" s="169"/>
-      <c r="U17" s="169"/>
-      <c r="V17" s="169"/>
-      <c r="W17" s="169"/>
-      <c r="X17" s="169"/>
-      <c r="Y17" s="169"/>
-      <c r="Z17" s="169"/>
-      <c r="AA17" s="169"/>
-      <c r="AB17" s="169"/>
-      <c r="AC17" s="169"/>
-      <c r="AD17" s="169"/>
-      <c r="AE17" s="169"/>
-      <c r="AF17" s="169"/>
-      <c r="AG17" s="169"/>
-      <c r="AH17" s="169"/>
-      <c r="AI17" s="169"/>
-      <c r="AJ17" s="169"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="183"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="183"/>
+      <c r="K17" s="183"/>
+      <c r="L17" s="183"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="183"/>
+      <c r="O17" s="183"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="183"/>
+      <c r="R17" s="183"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="183"/>
+      <c r="U17" s="183"/>
+      <c r="V17" s="183"/>
+      <c r="W17" s="183"/>
+      <c r="X17" s="183"/>
+      <c r="Y17" s="183"/>
+      <c r="Z17" s="183"/>
+      <c r="AA17" s="183"/>
+      <c r="AB17" s="183"/>
+      <c r="AC17" s="183"/>
+      <c r="AD17" s="183"/>
+      <c r="AE17" s="183"/>
+      <c r="AF17" s="183"/>
+      <c r="AG17" s="183"/>
+      <c r="AH17" s="183"/>
+      <c r="AI17" s="183"/>
+      <c r="AJ17" s="183"/>
     </row>
     <row r="18" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C18" s="170" t="s">
+      <c r="C18" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="170"/>
+      <c r="D18" s="184"/>
       <c r="E18" s="36"/>
       <c r="F18" s="41">
         <f>SUM(F10:F12)</f>
@@ -26768,10 +26211,10 @@
       </c>
     </row>
     <row r="19" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C19" s="170" t="s">
+      <c r="C19" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="170"/>
+      <c r="D19" s="184"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37">
         <v>2</v>
@@ -26868,10 +26311,10 @@
       </c>
     </row>
     <row r="20" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C20" s="170" t="s">
+      <c r="C20" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="170"/>
+      <c r="D20" s="184"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37">
         <f>SUM(F10,F11,F12,F13,F15)</f>
@@ -27082,17 +26525,15 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
     <mergeCell ref="F17:AJ17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -27104,40 +26545,42 @@
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
-    <cfRule type="containsText" dxfId="170" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="102" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="169" priority="2" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="101" priority="2" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="168" priority="3" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="100" priority="3" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="167" priority="4" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="99" priority="4" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="166" priority="5" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="98" priority="5" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="165" priority="7" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="164" priority="10" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="96" priority="10" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="163" priority="11" operator="containsText" text="ME07">
+    <cfRule type="containsText" dxfId="95" priority="11" operator="containsText" text="ME07">
       <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27165,61 +26608,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="192" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="149"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="193"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="193"/>
+      <c r="Q2" s="193"/>
+      <c r="R2" s="193"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="W2" s="193"/>
+      <c r="X2" s="193"/>
+      <c r="Y2" s="193"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="193"/>
+      <c r="AB2" s="193"/>
+      <c r="AC2" s="193"/>
+      <c r="AD2" s="193"/>
+      <c r="AE2" s="193"/>
+      <c r="AF2" s="193"/>
+      <c r="AG2" s="193"/>
+      <c r="AH2" s="193"/>
+      <c r="AI2" s="193"/>
+      <c r="AJ2" s="194"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
       <c r="F3" s="46" t="s">
         <v>98</v>
       </c>
@@ -27313,16 +26756,16 @@
       <c r="AJ3" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
       <c r="F4" s="43">
         <v>1</v>
       </c>
@@ -27416,20 +26859,20 @@
       <c r="AJ4" s="82">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="37">
         <v>1</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="176" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="176"/>
       <c r="F5" s="42" t="s">
         <v>194</v>
       </c>
@@ -27500,22 +26943,22 @@
         <v>219</v>
       </c>
       <c r="AC5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI5" s="42" t="s">
         <v>219</v>
@@ -27548,10 +26991,10 @@
       <c r="B6" s="37">
         <v>2</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="176" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="146"/>
+      <c r="D6" s="176"/>
       <c r="F6" s="49" t="s">
         <v>218</v>
       </c>
@@ -27670,10 +27113,10 @@
       <c r="B7" s="37">
         <v>3</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="176" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="146"/>
+      <c r="D7" s="176"/>
       <c r="F7" s="49" t="s">
         <v>219</v>
       </c>
@@ -27792,10 +27235,10 @@
       <c r="B8" s="37">
         <v>4</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="176" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="146"/>
+      <c r="D8" s="176"/>
       <c r="F8" s="49" t="s">
         <v>195</v>
       </c>
@@ -27914,10 +27357,10 @@
       <c r="B9" s="37">
         <v>5</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="176" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="146"/>
+      <c r="D9" s="176"/>
       <c r="F9" s="49" t="s">
         <v>219</v>
       </c>
@@ -27946,22 +27389,22 @@
         <v>219</v>
       </c>
       <c r="O9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T9" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U9" s="49" t="s">
         <v>219</v>
@@ -28037,10 +27480,10 @@
       <c r="B10" s="37">
         <v>6</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="176" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="146"/>
+      <c r="D10" s="176"/>
       <c r="F10" s="56" t="s">
         <v>194</v>
       </c>
@@ -28190,10 +27633,10 @@
       <c r="AI11" s="20"/>
     </row>
     <row r="12" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C12" s="170" t="s">
+      <c r="C12" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="170"/>
+      <c r="D12" s="184"/>
       <c r="E12" s="36"/>
       <c r="F12" s="37">
         <f>COUNTIF(F$5:F$9,"M*")</f>
@@ -28321,10 +27764,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C13" s="170" t="s">
+      <c r="C13" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="170"/>
+      <c r="D13" s="184"/>
       <c r="E13" s="36"/>
       <c r="F13" s="37">
         <f>COUNTIF(F$5:F$9,"A*")</f>
@@ -28452,10 +27895,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C14" s="170" t="s">
+      <c r="C14" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="170"/>
+      <c r="D14" s="184"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37">
         <f>COUNTIF(F$5:F$9,"N*")</f>
@@ -28583,10 +28026,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C15" s="170" t="s">
+      <c r="C15" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="170"/>
+      <c r="D15" s="184"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37">
         <f t="shared" ref="F15:AJ15" si="8">COUNTIF(F$5:F$10,"O*")</f>
@@ -28714,10 +28157,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C16" s="166" t="s">
+      <c r="C16" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="167"/>
+      <c r="D16" s="181"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37">
         <f t="shared" ref="F16:AJ16" si="9">COUNTIF(F$5:F$10,"TR*")</f>
@@ -28845,10 +28288,10 @@
       </c>
     </row>
     <row r="17" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C17" s="166" t="s">
+      <c r="C17" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="167"/>
+      <c r="D17" s="181"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37">
         <f t="shared" ref="F17:AJ17" si="10">COUNTIF(F$5:F$10,"ST*")</f>
@@ -28976,10 +28419,10 @@
       </c>
     </row>
     <row r="18" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C18" s="168" t="s">
+      <c r="C18" s="182" t="s">
         <v>249</v>
       </c>
-      <c r="D18" s="168"/>
+      <c r="D18" s="182"/>
       <c r="E18" s="38"/>
       <c r="F18" s="50">
         <f>COUNTIF(F$5:F$10,"OT*")</f>
@@ -29110,43 +28553,43 @@
       <c r="C19" s="40"/>
       <c r="D19" s="40"/>
       <c r="E19" s="36"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="169"/>
-      <c r="J19" s="169"/>
-      <c r="K19" s="169"/>
-      <c r="L19" s="169"/>
-      <c r="M19" s="169"/>
-      <c r="N19" s="169"/>
-      <c r="O19" s="169"/>
-      <c r="P19" s="169"/>
-      <c r="Q19" s="169"/>
-      <c r="R19" s="169"/>
-      <c r="S19" s="169"/>
-      <c r="T19" s="169"/>
-      <c r="U19" s="169"/>
-      <c r="V19" s="169"/>
-      <c r="W19" s="169"/>
-      <c r="X19" s="169"/>
-      <c r="Y19" s="169"/>
-      <c r="Z19" s="169"/>
-      <c r="AA19" s="169"/>
-      <c r="AB19" s="169"/>
-      <c r="AC19" s="169"/>
-      <c r="AD19" s="169"/>
-      <c r="AE19" s="169"/>
-      <c r="AF19" s="169"/>
-      <c r="AG19" s="169"/>
-      <c r="AH19" s="169"/>
-      <c r="AI19" s="169"/>
-      <c r="AJ19" s="169"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="183"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="183"/>
+      <c r="N19" s="183"/>
+      <c r="O19" s="183"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="183"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="183"/>
+      <c r="T19" s="183"/>
+      <c r="U19" s="183"/>
+      <c r="V19" s="183"/>
+      <c r="W19" s="183"/>
+      <c r="X19" s="183"/>
+      <c r="Y19" s="183"/>
+      <c r="Z19" s="183"/>
+      <c r="AA19" s="183"/>
+      <c r="AB19" s="183"/>
+      <c r="AC19" s="183"/>
+      <c r="AD19" s="183"/>
+      <c r="AE19" s="183"/>
+      <c r="AF19" s="183"/>
+      <c r="AG19" s="183"/>
+      <c r="AH19" s="183"/>
+      <c r="AI19" s="183"/>
+      <c r="AJ19" s="183"/>
     </row>
     <row r="20" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C20" s="170" t="s">
+      <c r="C20" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="170"/>
+      <c r="D20" s="184"/>
       <c r="E20" s="36"/>
       <c r="F20" s="41">
         <f>SUM(F12:F14)</f>
@@ -29273,10 +28716,10 @@
       </c>
     </row>
     <row r="21" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C21" s="170" t="s">
+      <c r="C21" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="170"/>
+      <c r="D21" s="184"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37">
         <v>3</v>
@@ -29373,10 +28816,10 @@
       </c>
     </row>
     <row r="22" spans="3:36" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C22" s="170" t="s">
+      <c r="C22" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="170"/>
+      <c r="D22" s="184"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37">
         <f>SUM(F12,F13,F14,F15,F17)</f>
@@ -29504,177 +28947,206 @@
     </row>
     <row r="23" spans="3:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="3:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F24" s="233" t="s">
+      <c r="F24" s="221" t="s">
         <v>197</v>
       </c>
-      <c r="G24" s="234"/>
-      <c r="H24" s="234"/>
-      <c r="I24" s="234"/>
-      <c r="J24" s="234"/>
-      <c r="K24" s="235"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="222"/>
+      <c r="I24" s="222"/>
+      <c r="J24" s="222"/>
+      <c r="K24" s="223"/>
     </row>
     <row r="25" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F25" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="G25" s="242" t="s">
+      <c r="G25" s="217" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="242"/>
+      <c r="H25" s="217"/>
       <c r="I25" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="J25" s="240" t="s">
+      <c r="J25" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="K25" s="241"/>
+      <c r="K25" s="229"/>
     </row>
     <row r="26" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F26" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="G26" s="231" t="s">
+      <c r="G26" s="218" t="s">
         <v>229</v>
       </c>
-      <c r="H26" s="231"/>
+      <c r="H26" s="218"/>
       <c r="I26" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="J26" s="231" t="s">
+      <c r="J26" s="218" t="s">
         <v>230</v>
       </c>
-      <c r="K26" s="236"/>
+      <c r="K26" s="224"/>
     </row>
     <row r="27" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F27" s="121" t="s">
         <v>231</v>
       </c>
-      <c r="G27" s="232" t="s">
+      <c r="G27" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="H27" s="232"/>
+      <c r="H27" s="219"/>
       <c r="I27" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="J27" s="232" t="s">
+      <c r="J27" s="219" t="s">
         <v>233</v>
       </c>
-      <c r="K27" s="237"/>
+      <c r="K27" s="225"/>
     </row>
     <row r="28" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F28" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="G28" s="227" t="s">
+      <c r="G28" s="220" t="s">
         <v>235</v>
       </c>
-      <c r="H28" s="227"/>
+      <c r="H28" s="220"/>
       <c r="I28" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="J28" s="238" t="s">
+      <c r="J28" s="226" t="s">
         <v>245</v>
       </c>
-      <c r="K28" s="239"/>
+      <c r="K28" s="227"/>
     </row>
     <row r="29" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F29" s="123" t="s">
         <v>218</v>
       </c>
-      <c r="G29" s="227" t="s">
+      <c r="G29" s="220" t="s">
         <v>236</v>
       </c>
-      <c r="H29" s="227"/>
+      <c r="H29" s="220"/>
       <c r="I29" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="J29" s="225" t="s">
+      <c r="J29" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="K29" s="226"/>
+      <c r="K29" s="239"/>
     </row>
     <row r="30" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F30" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="228" t="s">
+      <c r="G30" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="H30" s="228"/>
+      <c r="H30" s="240"/>
       <c r="I30" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="J30" s="225" t="s">
+      <c r="J30" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="K30" s="226"/>
+      <c r="K30" s="239"/>
     </row>
     <row r="31" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F31" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="G31" s="229" t="s">
+      <c r="G31" s="241" t="s">
         <v>198</v>
       </c>
-      <c r="H31" s="229"/>
+      <c r="H31" s="241"/>
       <c r="I31" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="J31" s="225" t="s">
+      <c r="J31" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="226"/>
+      <c r="K31" s="239"/>
     </row>
     <row r="32" spans="3:36" x14ac:dyDescent="0.25">
       <c r="F32" s="112" t="s">
         <v>216</v>
       </c>
-      <c r="G32" s="217" t="s">
+      <c r="G32" s="230" t="s">
         <v>217</v>
       </c>
-      <c r="H32" s="217"/>
+      <c r="H32" s="230"/>
       <c r="I32" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="J32" s="217" t="s">
+      <c r="J32" s="230" t="s">
         <v>215</v>
       </c>
-      <c r="K32" s="218"/>
+      <c r="K32" s="231"/>
     </row>
     <row r="33" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F33" s="114" t="s">
         <v>240</v>
       </c>
-      <c r="G33" s="219" t="s">
+      <c r="G33" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="H33" s="230"/>
+      <c r="H33" s="242"/>
       <c r="I33" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="J33" s="219" t="s">
+      <c r="J33" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="K33" s="220"/>
+      <c r="K33" s="233"/>
     </row>
     <row r="34" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F34" s="115" t="s">
         <v>239</v>
       </c>
-      <c r="G34" s="221" t="s">
+      <c r="G34" s="234" t="s">
         <v>244</v>
       </c>
-      <c r="H34" s="222"/>
+      <c r="H34" s="235"/>
       <c r="I34" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="223" t="s">
+      <c r="J34" s="236" t="s">
         <v>246</v>
       </c>
-      <c r="K34" s="224"/>
+      <c r="K34" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="F24:K24"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="F19:AJ19"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="B3:D4"/>
@@ -29691,78 +29163,49 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="F19:AJ19"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="F24:K24"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
-    <cfRule type="containsText" dxfId="162" priority="1" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="94" priority="1" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="161" priority="2" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="93" priority="2" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="160" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="92" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="159" priority="4" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="91" priority="4" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="158" priority="5" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="90" priority="5" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="157" priority="6" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="89" priority="6" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="156" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="88" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="155" priority="8" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="87" priority="8" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="154" priority="9" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="86" priority="9" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="153" priority="10" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="85" priority="10" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="152" priority="11" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="84" priority="11" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="151" priority="12" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="83" priority="12" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="150" priority="13" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="82" priority="13" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="149" priority="14" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="81" priority="14" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29788,61 +29231,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="253" t="s">
+      <c r="F2" s="250" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="253"/>
-      <c r="O2" s="253"/>
-      <c r="P2" s="253"/>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
-      <c r="AD2" s="253"/>
-      <c r="AE2" s="253"/>
-      <c r="AF2" s="253"/>
-      <c r="AG2" s="253"/>
-      <c r="AH2" s="253"/>
-      <c r="AI2" s="253"/>
-      <c r="AJ2" s="253"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="250"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="250"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="250"/>
+      <c r="W2" s="250"/>
+      <c r="X2" s="250"/>
+      <c r="Y2" s="250"/>
+      <c r="Z2" s="250"/>
+      <c r="AA2" s="250"/>
+      <c r="AB2" s="250"/>
+      <c r="AC2" s="250"/>
+      <c r="AD2" s="250"/>
+      <c r="AE2" s="250"/>
+      <c r="AF2" s="250"/>
+      <c r="AG2" s="250"/>
+      <c r="AH2" s="250"/>
+      <c r="AI2" s="250"/>
+      <c r="AJ2" s="250"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="247" t="s">
+      <c r="B3" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
+      <c r="C3" s="244"/>
+      <c r="D3" s="245"/>
       <c r="F3" s="86" t="s">
         <v>98</v>
       </c>
@@ -29936,16 +29379,16 @@
       <c r="AJ3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="250"/>
-      <c r="C4" s="251"/>
-      <c r="D4" s="252"/>
+      <c r="B4" s="246"/>
+      <c r="C4" s="247"/>
+      <c r="D4" s="248"/>
       <c r="F4" s="83">
         <v>1</v>
       </c>
@@ -30039,20 +29482,20 @@
       <c r="AJ4" s="85">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="57">
         <v>1</v>
       </c>
-      <c r="C5" s="156" t="s">
+      <c r="C5" s="185" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="254"/>
+      <c r="D5" s="251"/>
       <c r="F5" s="99" t="s">
         <v>194</v>
       </c>
@@ -30171,10 +29614,10 @@
       <c r="B6" s="54">
         <v>2</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="176" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="243"/>
+      <c r="D6" s="249"/>
       <c r="F6" s="96" t="s">
         <v>194</v>
       </c>
@@ -30197,10 +29640,10 @@
         <v>219</v>
       </c>
       <c r="M6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O6" s="96" t="s">
         <v>195</v>
@@ -30245,22 +29688,22 @@
         <v>219</v>
       </c>
       <c r="AC6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH6" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI6" s="96" t="s">
         <v>219</v>
@@ -30293,10 +29736,10 @@
       <c r="B7" s="54">
         <v>3</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="176" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="243"/>
+      <c r="D7" s="249"/>
       <c r="F7" s="96" t="s">
         <v>195</v>
       </c>
@@ -30415,10 +29858,10 @@
       <c r="B8" s="54">
         <v>4</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="176" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="243"/>
+      <c r="D8" s="249"/>
       <c r="F8" s="96" t="s">
         <v>218</v>
       </c>
@@ -30537,63 +29980,63 @@
       <c r="B9" s="54">
         <v>5</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="176" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="243"/>
+      <c r="D9" s="249"/>
       <c r="F9" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N9" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V9" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W9" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X9" s="96" t="s">
         <v>219</v>
@@ -30659,10 +30102,10 @@
       <c r="B10" s="54">
         <v>6</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="176" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="243"/>
+      <c r="D10" s="249"/>
       <c r="F10" s="96" t="s">
         <v>219</v>
       </c>
@@ -30781,10 +30224,10 @@
       <c r="B11" s="54">
         <v>7</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="176" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="243"/>
+      <c r="D11" s="249"/>
       <c r="F11" s="96" t="s">
         <v>219</v>
       </c>
@@ -30813,22 +30256,22 @@
         <v>219</v>
       </c>
       <c r="O11" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P11" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q11" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R11" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S11" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T11" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U11" s="96" t="s">
         <v>219</v>
@@ -30903,10 +30346,10 @@
       <c r="B12" s="54">
         <v>8</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="176" t="s">
         <v>185</v>
       </c>
-      <c r="D12" s="243"/>
+      <c r="D12" s="249"/>
       <c r="F12" s="96" t="s">
         <v>194</v>
       </c>
@@ -30956,22 +30399,22 @@
         <v>219</v>
       </c>
       <c r="V12" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W12" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X12" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y12" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z12" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA12" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB12" s="96" t="s">
         <v>219</v>
@@ -31025,10 +30468,10 @@
       <c r="B13" s="54">
         <v>9</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="176" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="243"/>
+      <c r="D13" s="249"/>
       <c r="F13" s="96" t="s">
         <v>195</v>
       </c>
@@ -31147,10 +30590,10 @@
       <c r="B14" s="54">
         <v>10</v>
       </c>
-      <c r="C14" s="146" t="s">
+      <c r="C14" s="176" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="243"/>
+      <c r="D14" s="249"/>
       <c r="F14" s="96" t="s">
         <v>195</v>
       </c>
@@ -31269,10 +30712,10 @@
       <c r="B15" s="54">
         <v>11</v>
       </c>
-      <c r="C15" s="153" t="s">
+      <c r="C15" s="146" t="s">
         <v>129</v>
       </c>
-      <c r="D15" s="244"/>
+      <c r="D15" s="252"/>
       <c r="F15" s="96" t="s">
         <v>218</v>
       </c>
@@ -31391,10 +30834,10 @@
       <c r="B16" s="54">
         <v>12</v>
       </c>
-      <c r="C16" s="153" t="s">
+      <c r="C16" s="146" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="244"/>
+      <c r="D16" s="252"/>
       <c r="F16" s="96" t="s">
         <v>218</v>
       </c>
@@ -31456,37 +30899,37 @@
         <v>219</v>
       </c>
       <c r="Z16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ16" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AL16" s="48">
         <f>COUNTIF($F16:$AJ16,"ST*")</f>
@@ -31513,10 +30956,10 @@
       <c r="B17" s="54">
         <v>13</v>
       </c>
-      <c r="C17" s="153" t="s">
+      <c r="C17" s="146" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="244"/>
+      <c r="D17" s="252"/>
       <c r="F17" s="101" t="s">
         <v>219</v>
       </c>
@@ -31527,22 +30970,22 @@
         <v>219</v>
       </c>
       <c r="I17" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J17" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K17" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L17" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M17" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N17" s="101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O17" s="96" t="s">
         <v>219</v>
@@ -31635,10 +31078,10 @@
       <c r="B18" s="124">
         <v>15</v>
       </c>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="187" t="s">
         <v>189</v>
       </c>
-      <c r="D18" s="245"/>
+      <c r="D18" s="253"/>
       <c r="F18" s="106" t="s">
         <v>219</v>
       </c>
@@ -31691,22 +31134,22 @@
         <v>219</v>
       </c>
       <c r="W18" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X18" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y18" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z18" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA18" s="125" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB18" s="106" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC18" s="106" t="s">
         <v>219</v>
@@ -31757,10 +31200,10 @@
       <c r="B19" s="55">
         <v>14</v>
       </c>
-      <c r="C19" s="160" t="s">
+      <c r="C19" s="189" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="246"/>
+      <c r="D19" s="254"/>
       <c r="E19" s="126"/>
       <c r="F19" s="98" t="s">
         <v>219</v>
@@ -31817,43 +31260,43 @@
         <v>219</v>
       </c>
       <c r="X19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB19" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC19" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI19" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ19" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AL19" s="48">
         <f t="shared" si="0"/>
@@ -31911,10 +31354,10 @@
       <c r="AI20" s="20"/>
     </row>
     <row r="21" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C21" s="170" t="s">
+      <c r="C21" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="170"/>
+      <c r="D21" s="184"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37">
         <f t="shared" ref="F21:AJ21" si="5">COUNTIF(F$5:F$19,"M*")</f>
@@ -32042,10 +31485,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C22" s="170" t="s">
+      <c r="C22" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="170"/>
+      <c r="D22" s="184"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37">
         <f t="shared" ref="F22:AJ22" si="6">COUNTIF(F$5:F$19,"A*")</f>
@@ -32173,10 +31616,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C23" s="170" t="s">
+      <c r="C23" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="170"/>
+      <c r="D23" s="184"/>
       <c r="E23" s="36"/>
       <c r="F23" s="37">
         <f t="shared" ref="F23:AJ23" si="7">COUNTIF(F$5:F$19,"N*")</f>
@@ -32304,10 +31747,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C24" s="170" t="s">
+      <c r="C24" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="170"/>
+      <c r="D24" s="184"/>
       <c r="E24" s="36"/>
       <c r="F24" s="37">
         <f t="shared" ref="F24:AJ24" si="8">COUNTIF(F$5:F$19,"O*")</f>
@@ -32435,10 +31878,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C25" s="166" t="s">
+      <c r="C25" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="167"/>
+      <c r="D25" s="181"/>
       <c r="E25" s="36"/>
       <c r="F25" s="37">
         <f t="shared" ref="F25:AJ25" si="9">COUNTIF(F$5:F$19,"ST*")</f>
@@ -32566,10 +32009,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C26" s="168" t="s">
+      <c r="C26" s="182" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="168"/>
+      <c r="D26" s="182"/>
       <c r="E26" s="38"/>
       <c r="F26" s="51">
         <f>COUNTIF(F$5:F$19,"OT*")</f>
@@ -32700,43 +32143,43 @@
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="169"/>
-      <c r="L27" s="169"/>
-      <c r="M27" s="169"/>
-      <c r="N27" s="169"/>
-      <c r="O27" s="169"/>
-      <c r="P27" s="169"/>
-      <c r="Q27" s="169"/>
-      <c r="R27" s="169"/>
-      <c r="S27" s="169"/>
-      <c r="T27" s="169"/>
-      <c r="U27" s="169"/>
-      <c r="V27" s="169"/>
-      <c r="W27" s="169"/>
-      <c r="X27" s="169"/>
-      <c r="Y27" s="169"/>
-      <c r="Z27" s="169"/>
-      <c r="AA27" s="169"/>
-      <c r="AB27" s="169"/>
-      <c r="AC27" s="169"/>
-      <c r="AD27" s="169"/>
-      <c r="AE27" s="169"/>
-      <c r="AF27" s="169"/>
-      <c r="AG27" s="169"/>
-      <c r="AH27" s="169"/>
-      <c r="AI27" s="169"/>
-      <c r="AJ27" s="169"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="183"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="183"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="183"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="183"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="183"/>
+      <c r="U27" s="183"/>
+      <c r="V27" s="183"/>
+      <c r="W27" s="183"/>
+      <c r="X27" s="183"/>
+      <c r="Y27" s="183"/>
+      <c r="Z27" s="183"/>
+      <c r="AA27" s="183"/>
+      <c r="AB27" s="183"/>
+      <c r="AC27" s="183"/>
+      <c r="AD27" s="183"/>
+      <c r="AE27" s="183"/>
+      <c r="AF27" s="183"/>
+      <c r="AG27" s="183"/>
+      <c r="AH27" s="183"/>
+      <c r="AI27" s="183"/>
+      <c r="AJ27" s="183"/>
     </row>
     <row r="28" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C28" s="170" t="s">
+      <c r="C28" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="170"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="36"/>
       <c r="F28" s="41">
         <f>SUM(F21:F23)</f>
@@ -32863,10 +32306,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C29" s="170" t="s">
+      <c r="C29" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="170"/>
+      <c r="D29" s="184"/>
       <c r="E29" s="36"/>
       <c r="F29" s="37">
         <v>6</v>
@@ -32963,10 +32406,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C30" s="170" t="s">
+      <c r="C30" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="170"/>
+      <c r="D30" s="184"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37">
         <f>SUM(F21,F22,F23,F24,F25)</f>
@@ -33094,198 +32537,193 @@
     </row>
     <row r="32" spans="2:42" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="233" t="s">
+      <c r="F33" s="221" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="234"/>
-      <c r="J33" s="234"/>
-      <c r="K33" s="235"/>
+      <c r="G33" s="222"/>
+      <c r="H33" s="222"/>
+      <c r="I33" s="222"/>
+      <c r="J33" s="222"/>
+      <c r="K33" s="223"/>
     </row>
     <row r="34" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F34" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="242" t="s">
+      <c r="G34" s="217" t="s">
         <v>193</v>
       </c>
-      <c r="H34" s="242"/>
+      <c r="H34" s="217"/>
       <c r="I34" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="J34" s="240" t="s">
+      <c r="J34" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="K34" s="241"/>
+      <c r="K34" s="229"/>
     </row>
     <row r="35" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F35" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="G35" s="231" t="s">
+      <c r="G35" s="218" t="s">
         <v>229</v>
       </c>
-      <c r="H35" s="231"/>
+      <c r="H35" s="218"/>
       <c r="I35" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="J35" s="231" t="s">
+      <c r="J35" s="218" t="s">
         <v>230</v>
       </c>
-      <c r="K35" s="236"/>
+      <c r="K35" s="224"/>
     </row>
     <row r="36" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F36" s="121" t="s">
         <v>231</v>
       </c>
-      <c r="G36" s="232" t="s">
+      <c r="G36" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="H36" s="232"/>
+      <c r="H36" s="219"/>
       <c r="I36" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="J36" s="232" t="s">
+      <c r="J36" s="219" t="s">
         <v>233</v>
       </c>
-      <c r="K36" s="237"/>
+      <c r="K36" s="225"/>
     </row>
     <row r="37" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F37" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="G37" s="227" t="s">
+      <c r="G37" s="220" t="s">
         <v>235</v>
       </c>
-      <c r="H37" s="227"/>
+      <c r="H37" s="220"/>
       <c r="I37" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="J37" s="238" t="s">
+      <c r="J37" s="226" t="s">
         <v>245</v>
       </c>
-      <c r="K37" s="239"/>
+      <c r="K37" s="227"/>
     </row>
     <row r="38" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F38" s="123" t="s">
         <v>218</v>
       </c>
-      <c r="G38" s="227" t="s">
+      <c r="G38" s="220" t="s">
         <v>236</v>
       </c>
-      <c r="H38" s="227"/>
+      <c r="H38" s="220"/>
       <c r="I38" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="J38" s="225" t="s">
+      <c r="J38" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="K38" s="226"/>
+      <c r="K38" s="239"/>
     </row>
     <row r="39" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F39" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G39" s="228" t="s">
+      <c r="G39" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="H39" s="228"/>
+      <c r="H39" s="240"/>
       <c r="I39" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="J39" s="225" t="s">
+      <c r="J39" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="K39" s="226"/>
+      <c r="K39" s="239"/>
     </row>
     <row r="40" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F40" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="G40" s="229" t="s">
+      <c r="G40" s="241" t="s">
         <v>198</v>
       </c>
-      <c r="H40" s="229"/>
+      <c r="H40" s="241"/>
       <c r="I40" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="J40" s="225" t="s">
+      <c r="J40" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="K40" s="226"/>
+      <c r="K40" s="239"/>
     </row>
     <row r="41" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F41" s="112" t="s">
         <v>216</v>
       </c>
-      <c r="G41" s="217" t="s">
+      <c r="G41" s="230" t="s">
         <v>217</v>
       </c>
-      <c r="H41" s="217"/>
+      <c r="H41" s="230"/>
       <c r="I41" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="J41" s="217" t="s">
+      <c r="J41" s="230" t="s">
         <v>215</v>
       </c>
-      <c r="K41" s="218"/>
+      <c r="K41" s="231"/>
     </row>
     <row r="42" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F42" s="114" t="s">
         <v>240</v>
       </c>
-      <c r="G42" s="219" t="s">
+      <c r="G42" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="H42" s="230"/>
+      <c r="H42" s="242"/>
       <c r="I42" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="J42" s="219" t="s">
+      <c r="J42" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="K42" s="220"/>
+      <c r="K42" s="233"/>
     </row>
     <row r="43" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F43" s="115" t="s">
         <v>239</v>
       </c>
-      <c r="G43" s="221" t="s">
+      <c r="G43" s="234" t="s">
         <v>244</v>
       </c>
-      <c r="H43" s="222"/>
+      <c r="H43" s="235"/>
       <c r="I43" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="J43" s="223" t="s">
+      <c r="J43" s="236" t="s">
         <v>246</v>
       </c>
-      <c r="K43" s="224"/>
+      <c r="K43" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="F27:AJ27"/>
     <mergeCell ref="C14:D14"/>
@@ -33302,65 +32740,70 @@
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
-    <cfRule type="containsText" dxfId="148" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="80" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="147" priority="2" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="79" priority="2" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="146" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="78" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="145" priority="5" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="77" priority="5" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="6" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="76" priority="6" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="143" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="75" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="8" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="74" priority="8" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="141" priority="9" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="73" priority="9" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="11" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="72" priority="11" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="139" priority="12" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="71" priority="12" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="13" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="70" priority="13" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="137" priority="18" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="69" priority="18" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="136" priority="19" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="68" priority="19" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="135" priority="21" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="67" priority="21" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33389,61 +32832,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="192" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="149"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="193"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="193"/>
+      <c r="Q2" s="193"/>
+      <c r="R2" s="193"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="W2" s="193"/>
+      <c r="X2" s="193"/>
+      <c r="Y2" s="193"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="193"/>
+      <c r="AB2" s="193"/>
+      <c r="AC2" s="193"/>
+      <c r="AD2" s="193"/>
+      <c r="AE2" s="193"/>
+      <c r="AF2" s="193"/>
+      <c r="AG2" s="193"/>
+      <c r="AH2" s="193"/>
+      <c r="AI2" s="193"/>
+      <c r="AJ2" s="194"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
       <c r="F3" s="46" t="s">
         <v>98</v>
       </c>
@@ -33537,16 +32980,16 @@
       <c r="AJ3" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
       <c r="F4" s="43">
         <v>1</v>
       </c>
@@ -33640,20 +33083,20 @@
       <c r="AJ4" s="82">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="129">
         <v>1</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="176" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="176"/>
       <c r="F5" s="99" t="s">
         <v>194</v>
       </c>
@@ -33772,10 +33215,10 @@
       <c r="B6" s="129">
         <v>2</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="176" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="146"/>
+      <c r="D6" s="176"/>
       <c r="F6" s="96" t="s">
         <v>195</v>
       </c>
@@ -33894,10 +33337,10 @@
       <c r="B7" s="129">
         <v>3</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="176" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="146"/>
+      <c r="D7" s="176"/>
       <c r="F7" s="96" t="s">
         <v>195</v>
       </c>
@@ -34016,10 +33459,10 @@
       <c r="B8" s="129">
         <v>4</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="176" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="146"/>
+      <c r="D8" s="176"/>
       <c r="F8" s="96" t="s">
         <v>218</v>
       </c>
@@ -34138,10 +33581,10 @@
       <c r="B9" s="129">
         <v>5</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="176" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="146"/>
+      <c r="D9" s="176"/>
       <c r="F9" s="96" t="s">
         <v>219</v>
       </c>
@@ -34260,10 +33703,10 @@
       <c r="B10" s="129">
         <v>6</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="176" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="146"/>
+      <c r="D10" s="176"/>
       <c r="F10" s="96" t="s">
         <v>218</v>
       </c>
@@ -34382,10 +33825,10 @@
       <c r="B11" s="129">
         <v>7</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="176" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="146"/>
+      <c r="D11" s="176"/>
       <c r="F11" s="96" t="s">
         <v>194</v>
       </c>
@@ -34504,10 +33947,10 @@
       <c r="B12" s="129">
         <v>8</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="176" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="146"/>
+      <c r="D12" s="176"/>
       <c r="F12" s="96" t="s">
         <v>195</v>
       </c>
@@ -34626,10 +34069,10 @@
       <c r="B13" s="129">
         <v>9</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="176" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="146"/>
+      <c r="D13" s="176"/>
       <c r="F13" s="96" t="s">
         <v>218</v>
       </c>
@@ -34691,22 +34134,22 @@
         <v>219</v>
       </c>
       <c r="Z13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE13" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF13" s="96" t="s">
         <v>219</v>
@@ -34748,10 +34191,10 @@
       <c r="B14" s="107">
         <v>10</v>
       </c>
-      <c r="C14" s="146" t="s">
+      <c r="C14" s="176" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="146"/>
+      <c r="D14" s="176"/>
       <c r="F14" s="96" t="s">
         <v>219</v>
       </c>
@@ -34759,85 +34202,85 @@
         <v>219</v>
       </c>
       <c r="H14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH14" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AI14" s="96" t="s">
         <v>218</v>
@@ -34870,10 +34313,10 @@
       <c r="B15" s="129">
         <v>11</v>
       </c>
-      <c r="C15" s="146" t="s">
+      <c r="C15" s="176" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="146"/>
+      <c r="D15" s="176"/>
       <c r="F15" s="96" t="s">
         <v>194</v>
       </c>
@@ -34992,10 +34435,10 @@
       <c r="B16" s="129">
         <v>12</v>
       </c>
-      <c r="C16" s="146" t="s">
+      <c r="C16" s="176" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="146"/>
+      <c r="D16" s="176"/>
       <c r="F16" s="96" t="s">
         <v>194</v>
       </c>
@@ -35114,10 +34557,10 @@
       <c r="B17" s="129">
         <v>13</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C17" s="176" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="146"/>
+      <c r="D17" s="176"/>
       <c r="F17" s="96" t="s">
         <v>195</v>
       </c>
@@ -35197,7 +34640,7 @@
         <v>218</v>
       </c>
       <c r="AF17" s="96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG17" s="96" t="s">
         <v>126</v>
@@ -35236,10 +34679,10 @@
       <c r="B18" s="129">
         <v>14</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="176" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="146"/>
+      <c r="D18" s="176"/>
       <c r="F18" s="96" t="s">
         <v>218</v>
       </c>
@@ -35358,10 +34801,10 @@
       <c r="B19" s="129">
         <v>15</v>
       </c>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="176" t="s">
         <v>143</v>
       </c>
-      <c r="D19" s="146"/>
+      <c r="D19" s="176"/>
       <c r="F19" s="96" t="s">
         <v>219</v>
       </c>
@@ -35480,10 +34923,10 @@
       <c r="B20" s="129">
         <v>16</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="176" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="146"/>
+      <c r="D20" s="176"/>
       <c r="F20" s="96" t="s">
         <v>219</v>
       </c>
@@ -35602,10 +35045,10 @@
       <c r="B21" s="129">
         <v>17</v>
       </c>
-      <c r="C21" s="146" t="s">
+      <c r="C21" s="176" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="146"/>
+      <c r="D21" s="176"/>
       <c r="F21" s="96" t="s">
         <v>219</v>
       </c>
@@ -35724,10 +35167,10 @@
       <c r="B22" s="129">
         <v>18</v>
       </c>
-      <c r="C22" s="146" t="s">
+      <c r="C22" s="176" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="146"/>
+      <c r="D22" s="176"/>
       <c r="F22" s="96" t="s">
         <v>194</v>
       </c>
@@ -35846,10 +35289,10 @@
       <c r="B23" s="129">
         <v>19</v>
       </c>
-      <c r="C23" s="153" t="s">
+      <c r="C23" s="146" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="154"/>
+      <c r="D23" s="147"/>
       <c r="F23" s="96" t="s">
         <v>194</v>
       </c>
@@ -35872,10 +35315,10 @@
         <v>219</v>
       </c>
       <c r="M23" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N23" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O23" s="96" t="s">
         <v>195</v>
@@ -35968,10 +35411,10 @@
       <c r="B24" s="129">
         <v>20</v>
       </c>
-      <c r="C24" s="146" t="s">
+      <c r="C24" s="176" t="s">
         <v>148</v>
       </c>
-      <c r="D24" s="146"/>
+      <c r="D24" s="176"/>
       <c r="F24" s="96" t="s">
         <v>195</v>
       </c>
@@ -36090,10 +35533,10 @@
       <c r="B25" s="129">
         <v>21</v>
       </c>
-      <c r="C25" s="146" t="s">
+      <c r="C25" s="176" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="146"/>
+      <c r="D25" s="176"/>
       <c r="F25" s="96" t="s">
         <v>218</v>
       </c>
@@ -36212,10 +35655,10 @@
       <c r="B26" s="129">
         <v>22</v>
       </c>
-      <c r="C26" s="146" t="s">
+      <c r="C26" s="176" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="146"/>
+      <c r="D26" s="176"/>
       <c r="F26" s="96" t="s">
         <v>218</v>
       </c>
@@ -36334,10 +35777,10 @@
       <c r="B27" s="129">
         <v>23</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="D27" s="154"/>
+      <c r="D27" s="147"/>
       <c r="F27" s="96" t="s">
         <v>219</v>
       </c>
@@ -36345,22 +35788,22 @@
         <v>219</v>
       </c>
       <c r="H27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M27" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N27" s="96" t="s">
         <v>219</v>
@@ -36456,10 +35899,10 @@
       <c r="B28" s="129">
         <v>24</v>
       </c>
-      <c r="C28" s="153" t="s">
+      <c r="C28" s="146" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="154"/>
+      <c r="D28" s="147"/>
       <c r="F28" s="96" t="s">
         <v>219</v>
       </c>
@@ -36578,12 +36021,12 @@
       <c r="B29" s="129">
         <v>25</v>
       </c>
-      <c r="C29" s="153" t="s">
+      <c r="C29" s="146" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="154"/>
+      <c r="D29" s="147"/>
       <c r="F29" s="96" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G29" s="96" t="s">
         <v>195</v>
@@ -36700,10 +36143,10 @@
       <c r="B30" s="129">
         <v>26</v>
       </c>
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="176" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="146"/>
+      <c r="D30" s="176"/>
       <c r="F30" s="96" t="s">
         <v>218</v>
       </c>
@@ -36823,7 +36266,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="130" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D31" s="131"/>
       <c r="F31" s="96" t="s">
@@ -36944,10 +36387,10 @@
       <c r="B32" s="129">
         <v>28</v>
       </c>
-      <c r="C32" s="153" t="s">
+      <c r="C32" s="146" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="154"/>
+      <c r="D32" s="147"/>
       <c r="F32" s="96" t="s">
         <v>195</v>
       </c>
@@ -37066,10 +36509,10 @@
       <c r="B33" s="129">
         <v>29</v>
       </c>
-      <c r="C33" s="153" t="s">
+      <c r="C33" s="146" t="s">
         <v>224</v>
       </c>
-      <c r="D33" s="154"/>
+      <c r="D33" s="147"/>
       <c r="F33" s="96" t="s">
         <v>195</v>
       </c>
@@ -37188,10 +36631,10 @@
       <c r="B34" s="129">
         <v>30</v>
       </c>
-      <c r="C34" s="146" t="s">
+      <c r="C34" s="176" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="146"/>
+      <c r="D34" s="176"/>
       <c r="F34" s="96" t="s">
         <v>218</v>
       </c>
@@ -37310,10 +36753,10 @@
       <c r="B35" s="129">
         <v>31</v>
       </c>
-      <c r="C35" s="163" t="s">
+      <c r="C35" s="177" t="s">
         <v>225</v>
       </c>
-      <c r="D35" s="163"/>
+      <c r="D35" s="177"/>
       <c r="F35" s="98" t="s">
         <v>194</v>
       </c>
@@ -37463,10 +36906,10 @@
       <c r="AI36" s="20"/>
     </row>
     <row r="37" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="170" t="s">
+      <c r="C37" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="170"/>
+      <c r="D37" s="184"/>
       <c r="E37" s="36"/>
       <c r="F37" s="37">
         <f t="shared" ref="F37:AJ37" si="5">COUNTIF(F$5:F$33,"M*")</f>
@@ -37594,10 +37037,10 @@
       </c>
     </row>
     <row r="38" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="170" t="s">
+      <c r="C38" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="170"/>
+      <c r="D38" s="184"/>
       <c r="E38" s="36"/>
       <c r="F38" s="37">
         <f t="shared" ref="F38:AJ38" si="6">COUNTIF(F$5:F$33,"A*")</f>
@@ -37725,10 +37168,10 @@
       </c>
     </row>
     <row r="39" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C39" s="170" t="s">
+      <c r="C39" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="170"/>
+      <c r="D39" s="184"/>
       <c r="E39" s="36"/>
       <c r="F39" s="37">
         <f t="shared" ref="F39:AJ39" si="7">COUNTIF(F$5:F$33,"N*")</f>
@@ -37856,10 +37299,10 @@
       </c>
     </row>
     <row r="40" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="170" t="s">
+      <c r="C40" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="170"/>
+      <c r="D40" s="184"/>
       <c r="E40" s="36"/>
       <c r="F40" s="37">
         <f t="shared" ref="F40:AJ40" si="8">COUNTIF(F$5:F$35,"O*")</f>
@@ -37987,10 +37430,10 @@
       </c>
     </row>
     <row r="41" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C41" s="166" t="s">
+      <c r="C41" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D41" s="167"/>
+      <c r="D41" s="181"/>
       <c r="E41" s="36"/>
       <c r="F41" s="37">
         <f t="shared" ref="F41:AJ41" si="9">COUNTIF(F$5:F$35,"TR*")</f>
@@ -38118,10 +37561,10 @@
       </c>
     </row>
     <row r="42" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C42" s="166" t="s">
+      <c r="C42" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="167"/>
+      <c r="D42" s="181"/>
       <c r="E42" s="36"/>
       <c r="F42" s="37">
         <f>COUNTIF(F$5:F$35,"ST*")</f>
@@ -38249,10 +37692,10 @@
       </c>
     </row>
     <row r="43" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C43" s="168" t="s">
+      <c r="C43" s="182" t="s">
         <v>248</v>
       </c>
-      <c r="D43" s="168"/>
+      <c r="D43" s="182"/>
       <c r="E43" s="38"/>
       <c r="F43" s="51">
         <f t="shared" ref="F43:AJ43" si="11">COUNTIF(F$5:F$35,"OT*")</f>
@@ -38383,43 +37826,43 @@
       <c r="C44" s="40"/>
       <c r="D44" s="40"/>
       <c r="E44" s="36"/>
-      <c r="F44" s="169"/>
-      <c r="G44" s="169"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="169"/>
-      <c r="J44" s="169"/>
-      <c r="K44" s="169"/>
-      <c r="L44" s="169"/>
-      <c r="M44" s="169"/>
-      <c r="N44" s="169"/>
-      <c r="O44" s="169"/>
-      <c r="P44" s="169"/>
-      <c r="Q44" s="169"/>
-      <c r="R44" s="169"/>
-      <c r="S44" s="169"/>
-      <c r="T44" s="169"/>
-      <c r="U44" s="169"/>
-      <c r="V44" s="169"/>
-      <c r="W44" s="169"/>
-      <c r="X44" s="169"/>
-      <c r="Y44" s="169"/>
-      <c r="Z44" s="169"/>
-      <c r="AA44" s="169"/>
-      <c r="AB44" s="169"/>
-      <c r="AC44" s="169"/>
-      <c r="AD44" s="169"/>
-      <c r="AE44" s="169"/>
-      <c r="AF44" s="169"/>
-      <c r="AG44" s="169"/>
-      <c r="AH44" s="169"/>
-      <c r="AI44" s="169"/>
-      <c r="AJ44" s="169"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="183"/>
+      <c r="I44" s="183"/>
+      <c r="J44" s="183"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="183"/>
+      <c r="M44" s="183"/>
+      <c r="N44" s="183"/>
+      <c r="O44" s="183"/>
+      <c r="P44" s="183"/>
+      <c r="Q44" s="183"/>
+      <c r="R44" s="183"/>
+      <c r="S44" s="183"/>
+      <c r="T44" s="183"/>
+      <c r="U44" s="183"/>
+      <c r="V44" s="183"/>
+      <c r="W44" s="183"/>
+      <c r="X44" s="183"/>
+      <c r="Y44" s="183"/>
+      <c r="Z44" s="183"/>
+      <c r="AA44" s="183"/>
+      <c r="AB44" s="183"/>
+      <c r="AC44" s="183"/>
+      <c r="AD44" s="183"/>
+      <c r="AE44" s="183"/>
+      <c r="AF44" s="183"/>
+      <c r="AG44" s="183"/>
+      <c r="AH44" s="183"/>
+      <c r="AI44" s="183"/>
+      <c r="AJ44" s="183"/>
     </row>
     <row r="45" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="170" t="s">
+      <c r="C45" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="170"/>
+      <c r="D45" s="184"/>
       <c r="E45" s="36"/>
       <c r="F45" s="41">
         <f>SUM(F37:F39)</f>
@@ -38546,10 +37989,10 @@
       </c>
     </row>
     <row r="46" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C46" s="170" t="s">
+      <c r="C46" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="170"/>
+      <c r="D46" s="184"/>
       <c r="E46" s="36"/>
       <c r="F46" s="37">
         <v>18</v>
@@ -38646,10 +38089,10 @@
       </c>
     </row>
     <row r="47" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C47" s="170" t="s">
+      <c r="C47" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="170"/>
+      <c r="D47" s="184"/>
       <c r="E47" s="36"/>
       <c r="F47" s="37">
         <f>SUM(F37,F38,F39,F40,F42)</f>
@@ -38777,197 +38220,212 @@
     </row>
     <row r="48" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="49" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F49" s="233" t="s">
+      <c r="F49" s="221" t="s">
         <v>197</v>
       </c>
-      <c r="G49" s="234"/>
-      <c r="H49" s="234"/>
-      <c r="I49" s="234"/>
-      <c r="J49" s="234"/>
-      <c r="K49" s="235"/>
+      <c r="G49" s="222"/>
+      <c r="H49" s="222"/>
+      <c r="I49" s="222"/>
+      <c r="J49" s="222"/>
+      <c r="K49" s="223"/>
     </row>
     <row r="50" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F50" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="G50" s="242" t="s">
+      <c r="G50" s="217" t="s">
         <v>193</v>
       </c>
-      <c r="H50" s="242"/>
+      <c r="H50" s="217"/>
       <c r="I50" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="J50" s="240" t="s">
+      <c r="J50" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="K50" s="241"/>
+      <c r="K50" s="229"/>
     </row>
     <row r="51" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F51" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="G51" s="231" t="s">
+      <c r="G51" s="218" t="s">
         <v>229</v>
       </c>
-      <c r="H51" s="231"/>
+      <c r="H51" s="218"/>
       <c r="I51" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="J51" s="231" t="s">
+      <c r="J51" s="218" t="s">
         <v>230</v>
       </c>
-      <c r="K51" s="236"/>
+      <c r="K51" s="224"/>
     </row>
     <row r="52" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F52" s="121" t="s">
         <v>231</v>
       </c>
-      <c r="G52" s="232" t="s">
+      <c r="G52" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="H52" s="232"/>
+      <c r="H52" s="219"/>
       <c r="I52" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="J52" s="232" t="s">
+      <c r="J52" s="219" t="s">
         <v>233</v>
       </c>
-      <c r="K52" s="237"/>
+      <c r="K52" s="225"/>
     </row>
     <row r="53" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F53" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="G53" s="227" t="s">
+      <c r="G53" s="220" t="s">
         <v>235</v>
       </c>
-      <c r="H53" s="227"/>
+      <c r="H53" s="220"/>
       <c r="I53" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="J53" s="238" t="s">
+      <c r="J53" s="226" t="s">
         <v>245</v>
       </c>
-      <c r="K53" s="239"/>
+      <c r="K53" s="227"/>
     </row>
     <row r="54" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F54" s="123" t="s">
         <v>218</v>
       </c>
-      <c r="G54" s="227" t="s">
+      <c r="G54" s="220" t="s">
         <v>236</v>
       </c>
-      <c r="H54" s="227"/>
+      <c r="H54" s="220"/>
       <c r="I54" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="J54" s="225" t="s">
+      <c r="J54" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="K54" s="226"/>
+      <c r="K54" s="239"/>
     </row>
     <row r="55" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F55" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G55" s="228" t="s">
+      <c r="G55" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="H55" s="228"/>
+      <c r="H55" s="240"/>
       <c r="I55" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="J55" s="225" t="s">
+      <c r="J55" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="K55" s="226"/>
+      <c r="K55" s="239"/>
     </row>
     <row r="56" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F56" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="G56" s="229" t="s">
+      <c r="G56" s="241" t="s">
         <v>198</v>
       </c>
-      <c r="H56" s="229"/>
+      <c r="H56" s="241"/>
       <c r="I56" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="J56" s="225" t="s">
+      <c r="J56" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="K56" s="226"/>
+      <c r="K56" s="239"/>
     </row>
     <row r="57" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F57" s="112" t="s">
         <v>216</v>
       </c>
-      <c r="G57" s="217" t="s">
+      <c r="G57" s="230" t="s">
         <v>217</v>
       </c>
-      <c r="H57" s="217"/>
+      <c r="H57" s="230"/>
       <c r="I57" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="J57" s="217" t="s">
+      <c r="J57" s="230" t="s">
         <v>215</v>
       </c>
-      <c r="K57" s="218"/>
+      <c r="K57" s="231"/>
     </row>
     <row r="58" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F58" s="114" t="s">
         <v>240</v>
       </c>
-      <c r="G58" s="219" t="s">
+      <c r="G58" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="H58" s="230"/>
+      <c r="H58" s="242"/>
       <c r="I58" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="J58" s="219" t="s">
+      <c r="J58" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="K58" s="220"/>
+      <c r="K58" s="233"/>
     </row>
     <row r="59" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F59" s="115" t="s">
         <v>239</v>
       </c>
-      <c r="G59" s="221" t="s">
+      <c r="G59" s="234" t="s">
         <v>244</v>
       </c>
-      <c r="H59" s="222"/>
+      <c r="H59" s="235"/>
       <c r="I59" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="J59" s="223" t="s">
+      <c r="J59" s="236" t="s">
         <v>246</v>
       </c>
-      <c r="K59" s="224"/>
+      <c r="K59" s="237"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="69">
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="F49:K49"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F44:AJ44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -38984,95 +38442,80 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F44:AJ44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="F49:K49"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ35">
-    <cfRule type="containsText" dxfId="134" priority="1" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="66" priority="1" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="133" priority="2" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="65" priority="2" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="64" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="4" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="63" priority="4" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="5" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="62" priority="5" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="6" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="61" priority="6" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="128" priority="7" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="60" priority="7" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="127" priority="8" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="59" priority="8" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="9" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="58" priority="9" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="125" priority="10" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="57" priority="10" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="124" priority="11" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="56" priority="11" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="123" priority="14" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="55" priority="14" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="122" priority="15" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="54" priority="15" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="121" priority="16" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="53" priority="16" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="120" priority="17" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="52" priority="17" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="119" priority="18" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="51" priority="18" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="118" priority="19" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="50" priority="19" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="117" priority="23" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39098,61 +38541,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="257" t="s">
+      <c r="F2" s="255" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="258"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="M2" s="258"/>
-      <c r="N2" s="258"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="258"/>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258"/>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
-      <c r="AD2" s="258"/>
-      <c r="AE2" s="258"/>
-      <c r="AF2" s="258"/>
-      <c r="AG2" s="258"/>
-      <c r="AH2" s="258"/>
-      <c r="AI2" s="258"/>
-      <c r="AJ2" s="259"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="256"/>
+      <c r="H2" s="256"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="M2" s="256"/>
+      <c r="N2" s="256"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="256"/>
+      <c r="Q2" s="256"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
+      <c r="AD2" s="256"/>
+      <c r="AE2" s="256"/>
+      <c r="AF2" s="256"/>
+      <c r="AG2" s="256"/>
+      <c r="AH2" s="256"/>
+      <c r="AI2" s="256"/>
+      <c r="AJ2" s="257"/>
+      <c r="AL2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
       <c r="F3" s="88" t="s">
         <v>98</v>
       </c>
@@ -39246,16 +38689,16 @@
       <c r="AJ3" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
       <c r="F4" s="32">
         <v>1</v>
       </c>
@@ -39349,20 +38792,20 @@
       <c r="AJ4" s="91">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="197"/>
     </row>
     <row r="5" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="107">
         <v>1</v>
       </c>
-      <c r="C5" s="153" t="s">
+      <c r="C5" s="146" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="154"/>
+      <c r="D5" s="147"/>
       <c r="F5" s="94" t="s">
         <v>194</v>
       </c>
@@ -39481,10 +38924,10 @@
       <c r="B6" s="107">
         <v>2</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="146" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="154"/>
+      <c r="D6" s="147"/>
       <c r="F6" s="94" t="s">
         <v>194</v>
       </c>
@@ -39588,10 +39031,10 @@
       <c r="B7" s="107">
         <v>3</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C7" s="146" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="154"/>
+      <c r="D7" s="147"/>
       <c r="F7" s="95" t="s">
         <v>195</v>
       </c>
@@ -39710,10 +39153,10 @@
       <c r="B8" s="107">
         <v>4</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="146" t="s">
         <v>166</v>
       </c>
-      <c r="D8" s="154"/>
+      <c r="D8" s="147"/>
       <c r="F8" s="96" t="s">
         <v>218</v>
       </c>
@@ -39832,10 +39275,10 @@
       <c r="B9" s="107">
         <v>5</v>
       </c>
-      <c r="C9" s="153" t="s">
+      <c r="C9" s="146" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="154"/>
+      <c r="D9" s="147"/>
       <c r="F9" s="96" t="s">
         <v>218</v>
       </c>
@@ -39954,10 +39397,10 @@
       <c r="B10" s="107">
         <v>6</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="146" t="s">
         <v>168</v>
       </c>
-      <c r="D10" s="154"/>
+      <c r="D10" s="147"/>
       <c r="F10" s="96" t="s">
         <v>219</v>
       </c>
@@ -40076,10 +39519,10 @@
       <c r="B11" s="107">
         <v>7</v>
       </c>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="146" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="154"/>
+      <c r="D11" s="147"/>
       <c r="F11" s="94" t="s">
         <v>219</v>
       </c>
@@ -40198,10 +39641,10 @@
       <c r="B12" s="107">
         <v>8</v>
       </c>
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="146" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="154"/>
+      <c r="D12" s="147"/>
       <c r="F12" s="94" t="s">
         <v>194</v>
       </c>
@@ -40320,10 +39763,10 @@
       <c r="B13" s="108">
         <v>9</v>
       </c>
-      <c r="C13" s="153" t="s">
+      <c r="C13" s="146" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="154"/>
+      <c r="D13" s="147"/>
       <c r="F13" s="94" t="s">
         <v>195</v>
       </c>
@@ -40442,10 +39885,10 @@
       <c r="B14" s="107">
         <v>10</v>
       </c>
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="146" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="154"/>
+      <c r="D14" s="147"/>
       <c r="F14" s="94" t="s">
         <v>195</v>
       </c>
@@ -40564,10 +40007,10 @@
       <c r="B15" s="108">
         <v>11</v>
       </c>
-      <c r="C15" s="153" t="s">
+      <c r="C15" s="146" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="154"/>
+      <c r="D15" s="147"/>
       <c r="F15" s="95" t="s">
         <v>219</v>
       </c>
@@ -40686,10 +40129,10 @@
       <c r="B16" s="108">
         <v>12</v>
       </c>
-      <c r="C16" s="153" t="s">
+      <c r="C16" s="146" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="154"/>
+      <c r="D16" s="147"/>
       <c r="F16" s="94" t="s">
         <v>219</v>
       </c>
@@ -40758,10 +40201,10 @@
       <c r="B17" s="108">
         <v>13</v>
       </c>
-      <c r="C17" s="153" t="s">
+      <c r="C17" s="146" t="s">
         <v>176</v>
       </c>
-      <c r="D17" s="154"/>
+      <c r="D17" s="147"/>
       <c r="F17" s="94" t="s">
         <v>194</v>
       </c>
@@ -41033,10 +40476,10 @@
       <c r="AI19" s="20"/>
     </row>
     <row r="20" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C20" s="166" t="s">
+      <c r="C20" s="180" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="167"/>
+      <c r="D20" s="181"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37">
         <f>COUNTIF(F$5:F$16,"M*")</f>
@@ -41164,10 +40607,10 @@
       </c>
     </row>
     <row r="21" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C21" s="166" t="s">
+      <c r="C21" s="180" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="167"/>
+      <c r="D21" s="181"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37">
         <f>COUNTIF(F$5:F$16,"A*")</f>
@@ -41295,10 +40738,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C22" s="166" t="s">
+      <c r="C22" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="167"/>
+      <c r="D22" s="181"/>
       <c r="E22" s="36"/>
       <c r="F22" s="37">
         <f>COUNTIF(F$5:F$16,"N*")</f>
@@ -41426,10 +40869,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C23" s="166" t="s">
+      <c r="C23" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="167"/>
+      <c r="D23" s="181"/>
       <c r="E23" s="36"/>
       <c r="F23" s="37">
         <f t="shared" ref="F23:AJ23" si="8">COUNTIF(F$5:F$18,"O*")</f>
@@ -41557,10 +41000,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C24" s="166" t="s">
+      <c r="C24" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="167"/>
+      <c r="D24" s="181"/>
       <c r="E24" s="36"/>
       <c r="F24" s="37">
         <f t="shared" ref="F24:AJ24" si="9">COUNTIF(F$5:F$18,"TR*")</f>
@@ -41688,10 +41131,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C25" s="166" t="s">
+      <c r="C25" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="167"/>
+      <c r="D25" s="181"/>
       <c r="E25" s="36"/>
       <c r="F25" s="37">
         <f t="shared" ref="F25:AJ25" si="10">COUNTIF(F$5:F$18,"ST*")</f>
@@ -41819,10 +41262,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C26" s="255" t="s">
+      <c r="C26" s="258" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="256"/>
+      <c r="D26" s="259"/>
       <c r="E26" s="38"/>
       <c r="F26" s="39">
         <f>COUNTIF(F$5:F$18,"OT*")</f>
@@ -41953,43 +41396,43 @@
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="169"/>
-      <c r="L27" s="169"/>
-      <c r="M27" s="169"/>
-      <c r="N27" s="169"/>
-      <c r="O27" s="169"/>
-      <c r="P27" s="169"/>
-      <c r="Q27" s="169"/>
-      <c r="R27" s="169"/>
-      <c r="S27" s="169"/>
-      <c r="T27" s="169"/>
-      <c r="U27" s="169"/>
-      <c r="V27" s="169"/>
-      <c r="W27" s="169"/>
-      <c r="X27" s="169"/>
-      <c r="Y27" s="169"/>
-      <c r="Z27" s="169"/>
-      <c r="AA27" s="169"/>
-      <c r="AB27" s="169"/>
-      <c r="AC27" s="169"/>
-      <c r="AD27" s="169"/>
-      <c r="AE27" s="169"/>
-      <c r="AF27" s="169"/>
-      <c r="AG27" s="169"/>
-      <c r="AH27" s="169"/>
-      <c r="AI27" s="169"/>
-      <c r="AJ27" s="169"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="183"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="183"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="183"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="183"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="183"/>
+      <c r="U27" s="183"/>
+      <c r="V27" s="183"/>
+      <c r="W27" s="183"/>
+      <c r="X27" s="183"/>
+      <c r="Y27" s="183"/>
+      <c r="Z27" s="183"/>
+      <c r="AA27" s="183"/>
+      <c r="AB27" s="183"/>
+      <c r="AC27" s="183"/>
+      <c r="AD27" s="183"/>
+      <c r="AE27" s="183"/>
+      <c r="AF27" s="183"/>
+      <c r="AG27" s="183"/>
+      <c r="AH27" s="183"/>
+      <c r="AI27" s="183"/>
+      <c r="AJ27" s="183"/>
     </row>
     <row r="28" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C28" s="166" t="s">
+      <c r="C28" s="180" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="167"/>
+      <c r="D28" s="181"/>
       <c r="E28" s="36"/>
       <c r="F28" s="41">
         <f>SUM(F20:F22)</f>
@@ -42117,10 +41560,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C29" s="166" t="s">
+      <c r="C29" s="180" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="167"/>
+      <c r="D29" s="181"/>
       <c r="E29" s="36"/>
       <c r="F29" s="37">
         <v>9</v>
@@ -42217,10 +41660,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C30" s="166" t="s">
+      <c r="C30" s="180" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="167"/>
+      <c r="D30" s="181"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37">
         <f>SUM(F20,F21,F22,F23,F25)</f>
@@ -42349,188 +41792,203 @@
     </row>
     <row r="31" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:42" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="233" t="s">
+      <c r="F32" s="221" t="s">
         <v>197</v>
       </c>
-      <c r="G32" s="234"/>
-      <c r="H32" s="234"/>
-      <c r="I32" s="234"/>
-      <c r="J32" s="234"/>
-      <c r="K32" s="235"/>
+      <c r="G32" s="222"/>
+      <c r="H32" s="222"/>
+      <c r="I32" s="222"/>
+      <c r="J32" s="222"/>
+      <c r="K32" s="223"/>
     </row>
     <row r="33" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F33" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="G33" s="242" t="s">
+      <c r="G33" s="217" t="s">
         <v>193</v>
       </c>
-      <c r="H33" s="242"/>
+      <c r="H33" s="217"/>
       <c r="I33" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="J33" s="240" t="s">
+      <c r="J33" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="K33" s="241"/>
+      <c r="K33" s="229"/>
     </row>
     <row r="34" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F34" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="G34" s="231" t="s">
+      <c r="G34" s="218" t="s">
         <v>229</v>
       </c>
-      <c r="H34" s="231"/>
+      <c r="H34" s="218"/>
       <c r="I34" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="J34" s="231" t="s">
+      <c r="J34" s="218" t="s">
         <v>230</v>
       </c>
-      <c r="K34" s="236"/>
+      <c r="K34" s="224"/>
     </row>
     <row r="35" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F35" s="121" t="s">
         <v>231</v>
       </c>
-      <c r="G35" s="232" t="s">
+      <c r="G35" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="H35" s="232"/>
+      <c r="H35" s="219"/>
       <c r="I35" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="J35" s="232" t="s">
+      <c r="J35" s="219" t="s">
         <v>233</v>
       </c>
-      <c r="K35" s="237"/>
+      <c r="K35" s="225"/>
     </row>
     <row r="36" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F36" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="G36" s="227" t="s">
+      <c r="G36" s="220" t="s">
         <v>235</v>
       </c>
-      <c r="H36" s="227"/>
+      <c r="H36" s="220"/>
       <c r="I36" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="J36" s="238" t="s">
+      <c r="J36" s="226" t="s">
         <v>245</v>
       </c>
-      <c r="K36" s="239"/>
+      <c r="K36" s="227"/>
     </row>
     <row r="37" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F37" s="123" t="s">
         <v>218</v>
       </c>
-      <c r="G37" s="227" t="s">
+      <c r="G37" s="220" t="s">
         <v>236</v>
       </c>
-      <c r="H37" s="227"/>
+      <c r="H37" s="220"/>
       <c r="I37" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="J37" s="225" t="s">
+      <c r="J37" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="K37" s="226"/>
+      <c r="K37" s="239"/>
     </row>
     <row r="38" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F38" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G38" s="228" t="s">
+      <c r="G38" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="H38" s="228"/>
+      <c r="H38" s="240"/>
       <c r="I38" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="J38" s="225" t="s">
+      <c r="J38" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="K38" s="226"/>
+      <c r="K38" s="239"/>
     </row>
     <row r="39" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F39" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="G39" s="229" t="s">
+      <c r="G39" s="241" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="229"/>
+      <c r="H39" s="241"/>
       <c r="I39" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="J39" s="225" t="s">
+      <c r="J39" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="K39" s="226"/>
+      <c r="K39" s="239"/>
     </row>
     <row r="40" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F40" s="112" t="s">
         <v>216</v>
       </c>
-      <c r="G40" s="217" t="s">
+      <c r="G40" s="230" t="s">
         <v>217</v>
       </c>
-      <c r="H40" s="217"/>
+      <c r="H40" s="230"/>
       <c r="I40" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="J40" s="217" t="s">
+      <c r="J40" s="230" t="s">
         <v>215</v>
       </c>
-      <c r="K40" s="218"/>
+      <c r="K40" s="231"/>
     </row>
     <row r="41" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F41" s="114" t="s">
         <v>240</v>
       </c>
-      <c r="G41" s="219" t="s">
+      <c r="G41" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="H41" s="230"/>
+      <c r="H41" s="242"/>
       <c r="I41" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="J41" s="219" t="s">
+      <c r="J41" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="K41" s="220"/>
+      <c r="K41" s="233"/>
     </row>
     <row r="42" spans="6:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F42" s="115" t="s">
         <v>239</v>
       </c>
-      <c r="G42" s="221" t="s">
+      <c r="G42" s="234" t="s">
         <v>244</v>
       </c>
-      <c r="H42" s="222"/>
+      <c r="H42" s="235"/>
       <c r="I42" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="J42" s="223" t="s">
+      <c r="J42" s="236" t="s">
         <v>246</v>
       </c>
-      <c r="K42" s="224"/>
+      <c r="K42" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F27:AJ27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F32:K32"/>
@@ -42546,75 +42004,60 @@
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F27:AJ27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AO2:AO4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ18">
-    <cfRule type="containsText" dxfId="116" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="48" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="115" priority="2" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="47" priority="2" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="114" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="46" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="113" priority="4" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="45" priority="4" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="5" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="111" priority="6" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="43" priority="6" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="42" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="109" priority="10" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="41" priority="10" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="11" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="40" priority="11" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="12" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="39" priority="12" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="13" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="38" priority="13" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="14" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="37" priority="14" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="104" priority="16" operator="containsText" text="NN13">
+    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="NN13">
       <formula>NOT(ISERROR(SEARCH("NN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="20" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="35" priority="20" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42672,19 +42115,19 @@
       <c r="AG2" s="261"/>
       <c r="AH2" s="261"/>
       <c r="AI2" s="261"/>
-      <c r="AK2" s="150" t="s">
+      <c r="AK2" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="AL2" s="150" t="s">
+      <c r="AL2" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="195" t="s">
         <v>114</v>
       </c>
     </row>
@@ -42784,11 +42227,11 @@
         <v>96</v>
       </c>
       <c r="AI3" s="31"/>
-      <c r="AK3" s="151"/>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
+      <c r="AK3" s="196"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="196"/>
+      <c r="AO3" s="196"/>
     </row>
     <row r="4" spans="2:41" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="264"/>
@@ -42884,11 +42327,11 @@
         <v>30</v>
       </c>
       <c r="AI4" s="35"/>
-      <c r="AK4" s="152"/>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
+      <c r="AK4" s="197"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="197"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
     </row>
     <row r="5" spans="2:41" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="260" t="s">
@@ -44212,10 +43655,10 @@
       <c r="AH16" s="20"/>
     </row>
     <row r="17" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B17" s="170" t="s">
+      <c r="B17" s="184" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="170"/>
+      <c r="C17" s="184"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37">
         <f t="shared" ref="E17:AH17" si="5">COUNTIF(E$5:E$15,"M*")</f>
@@ -44342,10 +43785,10 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B18" s="170" t="s">
+      <c r="B18" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="170"/>
+      <c r="C18" s="184"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37">
         <f t="shared" ref="E18:AH18" si="6">COUNTIF(E$5:E$15,"A*")</f>
@@ -44472,10 +43915,10 @@
       </c>
     </row>
     <row r="19" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B19" s="170" t="s">
+      <c r="B19" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="170"/>
+      <c r="C19" s="184"/>
       <c r="D19" s="36"/>
       <c r="E19" s="37">
         <f t="shared" ref="E19:AH19" si="7">COUNTIF(E$5:E$15,"N*")</f>
@@ -44602,10 +44045,10 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B20" s="170" t="s">
+      <c r="B20" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="170"/>
+      <c r="C20" s="184"/>
       <c r="D20" s="36"/>
       <c r="E20" s="37">
         <f t="shared" ref="E20:AH20" si="8">COUNTIF(E$5:E$15,"O*")</f>
@@ -44732,10 +44175,10 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B21" s="166" t="s">
+      <c r="B21" s="180" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="167"/>
+      <c r="C21" s="181"/>
       <c r="D21" s="36"/>
       <c r="E21" s="37">
         <f t="shared" ref="E21:AH21" si="9">COUNTIF(E$5:E$15,"ST*")</f>
@@ -44862,10 +44305,10 @@
       </c>
     </row>
     <row r="22" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B22" s="168" t="s">
+      <c r="B22" s="182" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="168"/>
+      <c r="C22" s="182"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39">
         <f>E24-E25</f>
@@ -44995,43 +44438,43 @@
       <c r="B23" s="40"/>
       <c r="C23" s="40"/>
       <c r="D23" s="36"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="169"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="169"/>
-      <c r="L23" s="169"/>
-      <c r="M23" s="169"/>
-      <c r="N23" s="169"/>
-      <c r="O23" s="169"/>
-      <c r="P23" s="169"/>
-      <c r="Q23" s="169"/>
-      <c r="R23" s="169"/>
-      <c r="S23" s="169"/>
-      <c r="T23" s="169"/>
-      <c r="U23" s="169"/>
-      <c r="V23" s="169"/>
-      <c r="W23" s="169"/>
-      <c r="X23" s="169"/>
-      <c r="Y23" s="169"/>
-      <c r="Z23" s="169"/>
-      <c r="AA23" s="169"/>
-      <c r="AB23" s="169"/>
-      <c r="AC23" s="169"/>
-      <c r="AD23" s="169"/>
-      <c r="AE23" s="169"/>
-      <c r="AF23" s="169"/>
-      <c r="AG23" s="169"/>
-      <c r="AH23" s="169"/>
-      <c r="AI23" s="169"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="183"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="183"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="183"/>
+      <c r="O23" s="183"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="183"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="183"/>
+      <c r="T23" s="183"/>
+      <c r="U23" s="183"/>
+      <c r="V23" s="183"/>
+      <c r="W23" s="183"/>
+      <c r="X23" s="183"/>
+      <c r="Y23" s="183"/>
+      <c r="Z23" s="183"/>
+      <c r="AA23" s="183"/>
+      <c r="AB23" s="183"/>
+      <c r="AC23" s="183"/>
+      <c r="AD23" s="183"/>
+      <c r="AE23" s="183"/>
+      <c r="AF23" s="183"/>
+      <c r="AG23" s="183"/>
+      <c r="AH23" s="183"/>
+      <c r="AI23" s="183"/>
     </row>
     <row r="24" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B24" s="170" t="s">
+      <c r="B24" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="170"/>
+      <c r="C24" s="184"/>
       <c r="D24" s="36"/>
       <c r="E24" s="41">
         <f>SUM(E17:E19)</f>
@@ -45158,10 +44601,10 @@
       </c>
     </row>
     <row r="25" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B25" s="170" t="s">
+      <c r="B25" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="170"/>
+      <c r="C25" s="184"/>
       <c r="D25" s="36"/>
       <c r="E25" s="37">
         <v>7</v>
@@ -45258,10 +44701,10 @@
       </c>
     </row>
     <row r="26" spans="2:35" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B26" s="170" t="s">
+      <c r="B26" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="170"/>
+      <c r="C26" s="184"/>
       <c r="D26" s="36"/>
       <c r="E26" s="37">
         <v>11</v>
@@ -45359,6 +44802,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
     <mergeCell ref="B9:C9"/>
@@ -45371,135 +44830,119 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
-    <cfRule type="containsText" dxfId="102" priority="23" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="24" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="33" priority="24" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="25" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="26" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="27" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="30" priority="27" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="28" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="29" priority="28" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="29" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="28" priority="29" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="95" priority="30" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="27" priority="30" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AH15">
-    <cfRule type="containsText" dxfId="94" priority="19" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="5" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:AH15">
-    <cfRule type="containsText" dxfId="92" priority="16" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="24" priority="16" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="17" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="23" priority="17" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="18" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="22" priority="18" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="6" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="21" priority="6" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="7" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="20" priority="7" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="8" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="9" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="10" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="11" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="12" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="15" priority="12" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="13" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="14" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="15" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="20" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AI15">
-    <cfRule type="containsText" dxfId="78" priority="3" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="4" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="1" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="2" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AH5 E6:AH10">
-    <cfRule type="containsText" dxfId="74" priority="31" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="6" priority="31" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="32" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="5" priority="32" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="33" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="4" priority="33" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="34" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="3" priority="34" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="35" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="2" priority="35" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="36" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="1" priority="36" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="37" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="0" priority="37" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45539,12 +44982,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45824,19 +45268,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7131BC6-00FD-4253-878E-994124306B86}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1e9c892-1499-41bb-8a64-60ef909d8682"/>
+    <ds:schemaRef ds:uri="0ecd8b7c-869e-4f04-a6a3-066c3c63b311"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45862,19 +45315,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7131BC6-00FD-4253-878E-994124306B86}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f1e9c892-1499-41bb-8a64-60ef909d8682"/>
-    <ds:schemaRef ds:uri="0ecd8b7c-869e-4f04-a6a3-066c3c63b311"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/rosters/.versions/2026-10/previous.xlsx
+++ b/rosters/.versions/2026-10/previous.xlsx
@@ -5459,6 +5459,78 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5507,89 +5579,23 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5599,60 +5605,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5738,6 +5690,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5792,18 +5792,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5822,10 +5810,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7887,91 +7887,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="9" customHeight="1">
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
-      <c r="M1" s="164"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="164"/>
-      <c r="P1" s="164"/>
-      <c r="Q1" s="164"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="164"/>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="164"/>
-      <c r="AA1" s="164"/>
-      <c r="AB1" s="164"/>
-      <c r="AC1" s="164"/>
-      <c r="AD1" s="164"/>
-      <c r="AE1" s="164"/>
-      <c r="AF1" s="164"/>
-      <c r="AG1" s="164"/>
-      <c r="AH1" s="164"/>
-      <c r="AI1" s="164"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="157"/>
+      <c r="W1" s="157"/>
+      <c r="X1" s="157"/>
+      <c r="Y1" s="157"/>
+      <c r="Z1" s="157"/>
+      <c r="AA1" s="157"/>
+      <c r="AB1" s="157"/>
+      <c r="AC1" s="157"/>
+      <c r="AD1" s="157"/>
+      <c r="AE1" s="157"/>
+      <c r="AF1" s="157"/>
+      <c r="AG1" s="157"/>
+      <c r="AH1" s="157"/>
+      <c r="AI1" s="157"/>
     </row>
     <row r="2" spans="2:40" ht="28.5">
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="164" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="162"/>
+      <c r="C2" s="164"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="163" t="s">
+      <c r="E2" s="165" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="163"/>
-      <c r="Q2" s="163"/>
-      <c r="R2" s="163"/>
-      <c r="S2" s="163"/>
-      <c r="T2" s="163"/>
-      <c r="U2" s="163"/>
-      <c r="V2" s="163"/>
-      <c r="W2" s="163" t="s">
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="165"/>
+      <c r="Q2" s="165"/>
+      <c r="R2" s="165"/>
+      <c r="S2" s="165"/>
+      <c r="T2" s="165"/>
+      <c r="U2" s="165"/>
+      <c r="V2" s="165"/>
+      <c r="W2" s="165" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="163"/>
-      <c r="Y2" s="163"/>
-      <c r="Z2" s="163"/>
-      <c r="AA2" s="163"/>
-      <c r="AB2" s="163"/>
-      <c r="AC2" s="163">
+      <c r="X2" s="165"/>
+      <c r="Y2" s="165"/>
+      <c r="Z2" s="165"/>
+      <c r="AA2" s="165"/>
+      <c r="AB2" s="165"/>
+      <c r="AC2" s="165">
         <v>2025</v>
       </c>
-      <c r="AD2" s="163"/>
-      <c r="AE2" s="163"/>
-      <c r="AF2" s="163"/>
+      <c r="AD2" s="165"/>
+      <c r="AE2" s="165"/>
+      <c r="AF2" s="165"/>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AK2" s="157" t="s">
+      <c r="AK2" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="157"/>
-      <c r="AM2" s="157"/>
-      <c r="AN2" s="157"/>
+      <c r="AL2" s="161"/>
+      <c r="AM2" s="161"/>
+      <c r="AN2" s="161"/>
     </row>
     <row r="3" spans="2:40">
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
       <c r="D3" s="10"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -8004,14 +8004,14 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AK3" s="157"/>
-      <c r="AL3" s="157"/>
-      <c r="AM3" s="157"/>
-      <c r="AN3" s="157"/>
+      <c r="AK3" s="161"/>
+      <c r="AL3" s="161"/>
+      <c r="AM3" s="161"/>
+      <c r="AN3" s="161"/>
     </row>
     <row r="4" spans="2:40">
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="164"/>
       <c r="D4" s="10"/>
       <c r="E4" s="158" t="s">
         <v>35</v>
@@ -8025,37 +8025,37 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="160" t="s">
+      <c r="M4" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="160"/>
-      <c r="O4" s="160"/>
-      <c r="P4" s="165">
+      <c r="N4" s="159"/>
+      <c r="O4" s="159"/>
+      <c r="P4" s="160">
         <f>IFERROR(DATEVALUE(J4&amp;W2&amp;AC2),"")</f>
         <v>45901</v>
       </c>
-      <c r="Q4" s="165"/>
-      <c r="R4" s="165"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="160"/>
-      <c r="W4" s="160"/>
-      <c r="X4" s="165">
+      <c r="V4" s="159"/>
+      <c r="W4" s="159"/>
+      <c r="X4" s="160">
         <f>IFERROR(EOMONTH(P4,0)+J4-1,"")</f>
         <v>45930</v>
       </c>
-      <c r="Y4" s="165"/>
-      <c r="Z4" s="165"/>
+      <c r="Y4" s="160"/>
+      <c r="Z4" s="160"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="160" t="s">
+      <c r="AC4" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" s="160"/>
-      <c r="AE4" s="160"/>
+      <c r="AD4" s="159"/>
+      <c r="AE4" s="159"/>
       <c r="AF4" s="3">
         <f>COUNTIF(E6:AI6,"*?")</f>
         <v>30</v>
@@ -8063,10 +8063,10 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AK4" s="157"/>
-      <c r="AL4" s="157"/>
-      <c r="AM4" s="157"/>
-      <c r="AN4" s="157"/>
+      <c r="AK4" s="161"/>
+      <c r="AL4" s="161"/>
+      <c r="AM4" s="161"/>
+      <c r="AN4" s="161"/>
     </row>
     <row r="5" spans="2:40" ht="6.75" customHeight="1">
       <c r="B5" s="6"/>
@@ -8105,10 +8105,10 @@
       <c r="AI5" s="3"/>
     </row>
     <row r="6" spans="2:40" ht="27.75">
-      <c r="B6" s="161" t="s">
+      <c r="B6" s="163" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="161" t="s">
+      <c r="C6" s="163" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="12"/>
@@ -8237,22 +8237,22 @@
         <v/>
       </c>
       <c r="AJ6" s="14"/>
-      <c r="AK6" s="159" t="s">
+      <c r="AK6" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="AL6" s="159" t="s">
+      <c r="AL6" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="AM6" s="159" t="s">
+      <c r="AM6" s="162" t="s">
         <v>43</v>
       </c>
-      <c r="AN6" s="159" t="s">
+      <c r="AN6" s="162" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:40">
-      <c r="B7" s="161"/>
-      <c r="C7" s="161"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
         <f>P4</f>
@@ -8379,10 +8379,10 @@
         <v/>
       </c>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="159"/>
-      <c r="AL7" s="159"/>
-      <c r="AM7" s="159"/>
-      <c r="AN7" s="159"/>
+      <c r="AK7" s="162"/>
+      <c r="AL7" s="162"/>
+      <c r="AM7" s="162"/>
+      <c r="AN7" s="162"/>
     </row>
     <row r="8" spans="2:40">
       <c r="B8" s="3" t="s">
@@ -13362,12 +13362,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E1:AI1"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AK2:AN4"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
@@ -13384,6 +13378,12 @@
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="W2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="E1:AI1"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
     <cfRule type="expression" dxfId="176" priority="4">
@@ -13447,61 +13447,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="167" t="s">
+      <c r="F2" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168"/>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="169"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
+      <c r="AD2" s="208"/>
+      <c r="AE2" s="208"/>
+      <c r="AF2" s="208"/>
+      <c r="AG2" s="208"/>
+      <c r="AH2" s="208"/>
+      <c r="AI2" s="208"/>
+      <c r="AJ2" s="209"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
       <c r="F3" s="44" t="s">
         <v>86</v>
       </c>
@@ -13595,16 +13595,16 @@
       <c r="AJ3" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="41">
         <v>1</v>
       </c>
@@ -13698,20 +13698,20 @@
       <c r="AJ4" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="19.5" customHeight="1">
       <c r="B5" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="166" t="s">
+      <c r="C5" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="194"/>
       <c r="F5" s="21" t="s">
         <v>97</v>
       </c>
@@ -13830,10 +13830,10 @@
       <c r="B6" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="166"/>
+      <c r="D6" s="194"/>
       <c r="F6" s="19" t="s">
         <v>100</v>
       </c>
@@ -13952,10 +13952,10 @@
       <c r="B7" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="137" t="s">
+      <c r="C7" s="120" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="138"/>
+      <c r="D7" s="121"/>
       <c r="F7" s="19" t="s">
         <v>103</v>
       </c>
@@ -14059,10 +14059,10 @@
       <c r="B8" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="194" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="166"/>
+      <c r="D8" s="194"/>
       <c r="F8" s="19" t="s">
         <v>104</v>
       </c>
@@ -14181,10 +14181,10 @@
       <c r="B9" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="194" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="166"/>
+      <c r="D9" s="194"/>
       <c r="F9" s="40" t="s">
         <v>103</v>
       </c>
@@ -14303,10 +14303,10 @@
       <c r="B10" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="166"/>
+      <c r="D10" s="194"/>
       <c r="F10" s="19" t="s">
         <v>108</v>
       </c>
@@ -14425,10 +14425,10 @@
       <c r="B11" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="166" t="s">
+      <c r="C11" s="194" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="166"/>
+      <c r="D11" s="194"/>
       <c r="F11" s="19" t="s">
         <v>98</v>
       </c>
@@ -14547,10 +14547,10 @@
       <c r="B12" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="166" t="s">
+      <c r="C12" s="194" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="166"/>
+      <c r="D12" s="194"/>
       <c r="F12" s="19" t="s">
         <v>104</v>
       </c>
@@ -14669,10 +14669,10 @@
       <c r="B13" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="166" t="s">
+      <c r="C13" s="194" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="166"/>
+      <c r="D13" s="194"/>
       <c r="F13" s="19" t="s">
         <v>98</v>
       </c>
@@ -14792,10 +14792,10 @@
       <c r="B14" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="194" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="166"/>
+      <c r="D14" s="194"/>
       <c r="F14" s="50" t="s">
         <v>103</v>
       </c>
@@ -14914,10 +14914,10 @@
       <c r="B15" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="170" t="s">
+      <c r="C15" s="200" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="171"/>
+      <c r="D15" s="201"/>
       <c r="E15" s="71"/>
       <c r="F15" s="93" t="s">
         <v>103</v>
@@ -15037,10 +15037,10 @@
       <c r="B16" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="166" t="s">
+      <c r="C16" s="194" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="137"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="71"/>
       <c r="F16" s="90" t="s">
         <v>103</v>
@@ -15160,10 +15160,10 @@
       <c r="B17" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="166" t="s">
+      <c r="C17" s="194" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="137"/>
+      <c r="D17" s="120"/>
       <c r="E17" s="71"/>
       <c r="F17" s="90" t="s">
         <v>104</v>
@@ -15283,10 +15283,10 @@
       <c r="B18" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="166" t="s">
+      <c r="C18" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="137"/>
+      <c r="D18" s="120"/>
       <c r="E18" s="71"/>
       <c r="F18" s="90" t="s">
         <v>108</v>
@@ -15406,10 +15406,10 @@
       <c r="B19" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="166" t="s">
+      <c r="C19" s="194" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="137"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="71"/>
       <c r="F19" s="95" t="s">
         <v>97</v>
@@ -15529,10 +15529,10 @@
       <c r="B20" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="166" t="s">
+      <c r="C20" s="194" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="137"/>
+      <c r="D20" s="120"/>
       <c r="E20" s="71"/>
       <c r="F20" s="90" t="s">
         <v>98</v>
@@ -15652,10 +15652,10 @@
       <c r="B21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="166" t="s">
+      <c r="C21" s="194" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="137"/>
+      <c r="D21" s="120"/>
       <c r="E21" s="71"/>
       <c r="F21" s="90" t="s">
         <v>98</v>
@@ -15775,10 +15775,10 @@
       <c r="B22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="166" t="s">
+      <c r="C22" s="194" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="137"/>
+      <c r="D22" s="120"/>
       <c r="E22" s="71"/>
       <c r="F22" s="90" t="s">
         <v>103</v>
@@ -15898,10 +15898,10 @@
       <c r="B23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="166" t="s">
+      <c r="C23" s="194" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="137"/>
+      <c r="D23" s="120"/>
       <c r="E23" s="71"/>
       <c r="F23" s="90" t="s">
         <v>104</v>
@@ -16021,10 +16021,10 @@
       <c r="B24" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="166" t="s">
+      <c r="C24" s="194" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="137"/>
+      <c r="D24" s="120"/>
       <c r="E24" s="71"/>
       <c r="F24" s="90" t="s">
         <v>104</v>
@@ -16144,10 +16144,10 @@
       <c r="B25" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="120" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="176"/>
+      <c r="D25" s="206"/>
       <c r="E25" s="71"/>
       <c r="F25" s="90" t="s">
         <v>108</v>
@@ -16267,10 +16267,10 @@
       <c r="B26" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="137" t="s">
+      <c r="C26" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="176"/>
+      <c r="D26" s="206"/>
       <c r="E26" s="71"/>
       <c r="F26" s="90" t="s">
         <v>108</v>
@@ -16390,10 +16390,10 @@
       <c r="B27" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="137" t="s">
+      <c r="C27" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="176"/>
+      <c r="D27" s="206"/>
       <c r="E27" s="71"/>
       <c r="F27" s="95" t="s">
         <v>98</v>
@@ -16513,10 +16513,10 @@
       <c r="B28" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="172" t="s">
+      <c r="C28" s="202" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="173"/>
+      <c r="D28" s="203"/>
       <c r="E28" s="71"/>
       <c r="F28" s="97" t="s">
         <v>98</v>
@@ -16636,10 +16636,10 @@
       <c r="B29" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="174" t="s">
+      <c r="C29" s="204" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="175"/>
+      <c r="D29" s="205"/>
       <c r="E29" s="60"/>
       <c r="F29" s="92" t="s">
         <v>98</v>
@@ -16759,10 +16759,10 @@
       <c r="B30" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="166" t="s">
+      <c r="C30" s="194" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="166"/>
+      <c r="D30" s="194"/>
       <c r="F30" s="93" t="s">
         <v>103</v>
       </c>
@@ -16881,10 +16881,10 @@
       <c r="B31" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="166" t="s">
+      <c r="C31" s="194" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="166"/>
+      <c r="D31" s="194"/>
       <c r="F31" s="90" t="s">
         <v>104</v>
       </c>
@@ -17003,10 +17003,10 @@
       <c r="B32" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="166" t="s">
+      <c r="C32" s="194" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="166"/>
+      <c r="D32" s="194"/>
       <c r="F32" s="90" t="s">
         <v>104</v>
       </c>
@@ -17125,10 +17125,10 @@
       <c r="B33" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="166" t="s">
+      <c r="C33" s="194" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="166"/>
+      <c r="D33" s="194"/>
       <c r="F33" s="90" t="s">
         <v>108</v>
       </c>
@@ -17247,10 +17247,10 @@
       <c r="B34" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="166" t="s">
+      <c r="C34" s="194" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="166"/>
+      <c r="D34" s="194"/>
       <c r="F34" s="90" t="s">
         <v>98</v>
       </c>
@@ -17369,10 +17369,10 @@
       <c r="B35" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="166" t="s">
+      <c r="C35" s="194" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="166"/>
+      <c r="D35" s="194"/>
       <c r="F35" s="90" t="s">
         <v>108</v>
       </c>
@@ -17491,10 +17491,10 @@
       <c r="B36" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="166" t="s">
+      <c r="C36" s="194" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="166"/>
+      <c r="D36" s="194"/>
       <c r="F36" s="90" t="s">
         <v>103</v>
       </c>
@@ -17613,10 +17613,10 @@
       <c r="B37" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="166" t="s">
+      <c r="C37" s="194" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="166"/>
+      <c r="D37" s="194"/>
       <c r="F37" s="90" t="s">
         <v>104</v>
       </c>
@@ -17735,10 +17735,10 @@
       <c r="B38" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="166" t="s">
+      <c r="C38" s="194" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="166"/>
+      <c r="D38" s="194"/>
       <c r="F38" s="90" t="s">
         <v>108</v>
       </c>
@@ -17857,10 +17857,10 @@
       <c r="B39" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="166" t="s">
+      <c r="C39" s="194" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="166"/>
+      <c r="D39" s="194"/>
       <c r="F39" s="90" t="s">
         <v>98</v>
       </c>
@@ -17979,10 +17979,10 @@
       <c r="B40" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="166" t="s">
+      <c r="C40" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="166"/>
+      <c r="D40" s="194"/>
       <c r="F40" s="90" t="s">
         <v>144</v>
       </c>
@@ -18101,10 +18101,10 @@
       <c r="B41" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="166" t="s">
+      <c r="C41" s="194" t="s">
         <v>145</v>
       </c>
-      <c r="D41" s="166"/>
+      <c r="D41" s="194"/>
       <c r="F41" s="90" t="s">
         <v>103</v>
       </c>
@@ -18223,10 +18223,10 @@
       <c r="B42" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="166" t="s">
+      <c r="C42" s="194" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="166"/>
+      <c r="D42" s="194"/>
       <c r="F42" s="90" t="s">
         <v>104</v>
       </c>
@@ -18345,10 +18345,10 @@
       <c r="B43" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C43" s="166" t="s">
+      <c r="C43" s="194" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="166"/>
+      <c r="D43" s="194"/>
       <c r="F43" s="90" t="s">
         <v>108</v>
       </c>
@@ -18467,10 +18467,10 @@
       <c r="B44" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="166" t="s">
+      <c r="C44" s="194" t="s">
         <v>149</v>
       </c>
-      <c r="D44" s="166"/>
+      <c r="D44" s="194"/>
       <c r="F44" s="90" t="s">
         <v>98</v>
       </c>
@@ -18589,10 +18589,10 @@
       <c r="B45" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="166" t="s">
+      <c r="C45" s="194" t="s">
         <v>151</v>
       </c>
-      <c r="D45" s="166"/>
+      <c r="D45" s="194"/>
       <c r="F45" s="90" t="s">
         <v>98</v>
       </c>
@@ -18711,10 +18711,10 @@
       <c r="B46" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="166" t="s">
+      <c r="C46" s="194" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="166"/>
+      <c r="D46" s="194"/>
       <c r="F46" s="90" t="s">
         <v>98</v>
       </c>
@@ -18833,10 +18833,10 @@
       <c r="B47" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="166" t="s">
+      <c r="C47" s="194" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="166"/>
+      <c r="D47" s="194"/>
       <c r="F47" s="90" t="s">
         <v>103</v>
       </c>
@@ -18955,10 +18955,10 @@
       <c r="B48" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="137" t="s">
+      <c r="C48" s="120" t="s">
         <v>154</v>
       </c>
-      <c r="D48" s="138"/>
+      <c r="D48" s="121"/>
       <c r="F48" s="90" t="s">
         <v>103</v>
       </c>
@@ -19077,10 +19077,10 @@
       <c r="B49" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="166" t="s">
+      <c r="C49" s="194" t="s">
         <v>155</v>
       </c>
-      <c r="D49" s="166"/>
+      <c r="D49" s="194"/>
       <c r="F49" s="90" t="s">
         <v>104</v>
       </c>
@@ -19199,10 +19199,10 @@
       <c r="B50" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="166" t="s">
+      <c r="C50" s="194" t="s">
         <v>156</v>
       </c>
-      <c r="D50" s="166"/>
+      <c r="D50" s="194"/>
       <c r="F50" s="90" t="s">
         <v>108</v>
       </c>
@@ -19321,10 +19321,10 @@
       <c r="B51" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="166" t="s">
+      <c r="C51" s="194" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="166"/>
+      <c r="D51" s="194"/>
       <c r="F51" s="90" t="s">
         <v>108</v>
       </c>
@@ -19443,10 +19443,10 @@
       <c r="B52" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C52" s="137" t="s">
+      <c r="C52" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="D52" s="138"/>
+      <c r="D52" s="121"/>
       <c r="F52" s="90" t="s">
         <v>98</v>
       </c>
@@ -19565,10 +19565,10 @@
       <c r="B53" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="137" t="s">
+      <c r="C53" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="D53" s="138"/>
+      <c r="D53" s="121"/>
       <c r="F53" s="90" t="s">
         <v>98</v>
       </c>
@@ -19687,10 +19687,10 @@
       <c r="B54" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="137" t="s">
+      <c r="C54" s="120" t="s">
         <v>160</v>
       </c>
-      <c r="D54" s="138"/>
+      <c r="D54" s="121"/>
       <c r="F54" s="90" t="s">
         <v>103</v>
       </c>
@@ -19809,10 +19809,10 @@
       <c r="B55" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="166" t="s">
+      <c r="C55" s="194" t="s">
         <v>161</v>
       </c>
-      <c r="D55" s="166"/>
+      <c r="D55" s="194"/>
       <c r="F55" s="90" t="s">
         <v>108</v>
       </c>
@@ -19916,10 +19916,10 @@
       <c r="B56" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="137" t="s">
+      <c r="C56" s="120" t="s">
         <v>162</v>
       </c>
-      <c r="D56" s="138"/>
+      <c r="D56" s="121"/>
       <c r="F56" s="90" t="s">
         <v>98</v>
       </c>
@@ -20023,10 +20023,10 @@
       <c r="B57" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="137" t="s">
+      <c r="C57" s="120" t="s">
         <v>163</v>
       </c>
-      <c r="D57" s="138"/>
+      <c r="D57" s="121"/>
       <c r="F57" s="90" t="s">
         <v>104</v>
       </c>
@@ -20145,10 +20145,10 @@
       <c r="B58" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="137" t="s">
+      <c r="C58" s="120" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="138"/>
+      <c r="D58" s="121"/>
       <c r="F58" s="90" t="s">
         <v>104</v>
       </c>
@@ -20267,10 +20267,10 @@
       <c r="B59" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="166" t="s">
+      <c r="C59" s="194" t="s">
         <v>165</v>
       </c>
-      <c r="D59" s="166"/>
+      <c r="D59" s="194"/>
       <c r="F59" s="90" t="s">
         <v>108</v>
       </c>
@@ -20389,10 +20389,10 @@
       <c r="B60" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="177" t="s">
+      <c r="C60" s="195" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="177"/>
+      <c r="D60" s="195"/>
       <c r="F60" s="92" t="s">
         <v>103</v>
       </c>
@@ -20511,10 +20511,10 @@
       <c r="B61" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C61" s="137" t="s">
+      <c r="C61" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="D61" s="138"/>
+      <c r="D61" s="121"/>
       <c r="F61" s="88" t="s">
         <v>103</v>
       </c>
@@ -20633,10 +20633,10 @@
       <c r="B62" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="137" t="s">
+      <c r="C62" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="D62" s="138"/>
+      <c r="D62" s="121"/>
       <c r="F62" s="88" t="s">
         <v>103</v>
       </c>
@@ -20755,10 +20755,10 @@
       <c r="B63" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C63" s="137" t="s">
+      <c r="C63" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="D63" s="138"/>
+      <c r="D63" s="121"/>
       <c r="F63" s="89" t="s">
         <v>104</v>
       </c>
@@ -20877,10 +20877,10 @@
       <c r="B64" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C64" s="137" t="s">
+      <c r="C64" s="120" t="s">
         <v>172</v>
       </c>
-      <c r="D64" s="138"/>
+      <c r="D64" s="121"/>
       <c r="F64" s="90" t="s">
         <v>108</v>
       </c>
@@ -20999,10 +20999,10 @@
       <c r="B65" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C65" s="137" t="s">
+      <c r="C65" s="120" t="s">
         <v>173</v>
       </c>
-      <c r="D65" s="138"/>
+      <c r="D65" s="121"/>
       <c r="F65" s="90" t="s">
         <v>108</v>
       </c>
@@ -21121,10 +21121,10 @@
       <c r="B66" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C66" s="137" t="s">
+      <c r="C66" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="D66" s="138"/>
+      <c r="D66" s="121"/>
       <c r="F66" s="90" t="s">
         <v>98</v>
       </c>
@@ -21243,10 +21243,10 @@
       <c r="B67" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="137" t="s">
+      <c r="C67" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="D67" s="138"/>
+      <c r="D67" s="121"/>
       <c r="F67" s="88" t="s">
         <v>98</v>
       </c>
@@ -21365,10 +21365,10 @@
       <c r="B68" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="137" t="s">
+      <c r="C68" s="120" t="s">
         <v>176</v>
       </c>
-      <c r="D68" s="138"/>
+      <c r="D68" s="121"/>
       <c r="F68" s="88" t="s">
         <v>103</v>
       </c>
@@ -21487,10 +21487,10 @@
       <c r="B69" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C69" s="137" t="s">
+      <c r="C69" s="120" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="138"/>
+      <c r="D69" s="121"/>
       <c r="F69" s="88" t="s">
         <v>104</v>
       </c>
@@ -21609,10 +21609,10 @@
       <c r="B70" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="C70" s="137" t="s">
+      <c r="C70" s="120" t="s">
         <v>178</v>
       </c>
-      <c r="D70" s="138"/>
+      <c r="D70" s="121"/>
       <c r="F70" s="88" t="s">
         <v>104</v>
       </c>
@@ -21731,10 +21731,10 @@
       <c r="B71" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="137" t="s">
+      <c r="C71" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="D71" s="138"/>
+      <c r="D71" s="121"/>
       <c r="F71" s="89" t="s">
         <v>98</v>
       </c>
@@ -21853,10 +21853,10 @@
       <c r="B72" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C72" s="137" t="s">
+      <c r="C72" s="120" t="s">
         <v>180</v>
       </c>
-      <c r="D72" s="138"/>
+      <c r="D72" s="121"/>
       <c r="F72" s="88"/>
       <c r="G72" s="88"/>
       <c r="H72" s="88"/>
@@ -21913,10 +21913,10 @@
       <c r="B73" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C73" s="137" t="s">
+      <c r="C73" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="D73" s="138"/>
+      <c r="D73" s="121"/>
       <c r="F73" s="88" t="s">
         <v>103</v>
       </c>
@@ -22208,10 +22208,10 @@
       </c>
     </row>
     <row r="76" spans="2:42" ht="18.75">
-      <c r="C76" s="181" t="s">
+      <c r="C76" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="181"/>
+      <c r="D76" s="199"/>
       <c r="E76" s="34"/>
       <c r="F76" s="35">
         <f t="shared" ref="F76:AJ76" si="25">COUNTIF(F9:F74,"M*")</f>
@@ -22359,10 +22359,10 @@
       </c>
     </row>
     <row r="77" spans="2:42" ht="18.75">
-      <c r="C77" s="181" t="s">
+      <c r="C77" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="D77" s="181"/>
+      <c r="D77" s="199"/>
       <c r="E77" s="34"/>
       <c r="F77" s="35">
         <f t="shared" ref="F77:AJ77" si="26">COUNTIF(F9:F74,"A*")</f>
@@ -22510,10 +22510,10 @@
       </c>
     </row>
     <row r="78" spans="2:42" ht="18.75">
-      <c r="C78" s="181" t="s">
+      <c r="C78" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D78" s="181"/>
+      <c r="D78" s="199"/>
       <c r="E78" s="34"/>
       <c r="F78" s="35">
         <f t="shared" ref="F78:AJ78" si="27">COUNTIF(F9:F74,"N*")</f>
@@ -22661,10 +22661,10 @@
       </c>
     </row>
     <row r="79" spans="2:42" ht="18.75">
-      <c r="C79" s="181" t="s">
+      <c r="C79" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="181"/>
+      <c r="D79" s="199"/>
       <c r="E79" s="34"/>
       <c r="F79" s="35">
         <f t="shared" ref="F79:AJ79" si="28">COUNTIF(F$30:F$74,"O*")</f>
@@ -22812,10 +22812,10 @@
       </c>
     </row>
     <row r="80" spans="2:42" ht="18.75">
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D80" s="143"/>
+      <c r="D80" s="134"/>
       <c r="E80" s="34"/>
       <c r="F80" s="35">
         <f t="shared" ref="F80:AJ80" si="29">COUNTIF(F9:F74,"TR*")</f>
@@ -22963,10 +22963,10 @@
       </c>
     </row>
     <row r="81" spans="3:42" ht="18.75">
-      <c r="C81" s="142" t="s">
+      <c r="C81" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="143"/>
+      <c r="D81" s="134"/>
       <c r="E81" s="34"/>
       <c r="F81" s="35">
         <f>COUNTIF(F9:F74,"ST*")</f>
@@ -23114,10 +23114,10 @@
       </c>
     </row>
     <row r="82" spans="3:42" ht="18.75">
-      <c r="C82" s="180" t="s">
+      <c r="C82" s="198" t="s">
         <v>187</v>
       </c>
-      <c r="D82" s="180"/>
+      <c r="D82" s="198"/>
       <c r="E82" s="36"/>
       <c r="F82" s="37">
         <f t="shared" ref="F82:AJ82" si="31">COUNTIF(F$5:F$74,"OT*")</f>
@@ -23268,37 +23268,37 @@
       <c r="C83" s="38"/>
       <c r="D83" s="38"/>
       <c r="E83" s="34"/>
-      <c r="F83" s="141"/>
-      <c r="G83" s="141"/>
-      <c r="H83" s="141"/>
-      <c r="I83" s="141"/>
-      <c r="J83" s="141"/>
-      <c r="K83" s="141"/>
-      <c r="L83" s="141"/>
-      <c r="M83" s="141"/>
-      <c r="N83" s="141"/>
-      <c r="O83" s="141"/>
-      <c r="P83" s="141"/>
-      <c r="Q83" s="141"/>
-      <c r="R83" s="141"/>
-      <c r="S83" s="141"/>
-      <c r="T83" s="141"/>
-      <c r="U83" s="141"/>
-      <c r="V83" s="141"/>
-      <c r="W83" s="141"/>
-      <c r="X83" s="141"/>
-      <c r="Y83" s="141"/>
-      <c r="Z83" s="141"/>
-      <c r="AA83" s="141"/>
-      <c r="AB83" s="141"/>
-      <c r="AC83" s="141"/>
-      <c r="AD83" s="141"/>
-      <c r="AE83" s="141"/>
-      <c r="AF83" s="141"/>
-      <c r="AG83" s="141"/>
-      <c r="AH83" s="141"/>
-      <c r="AI83" s="141"/>
-      <c r="AJ83" s="141"/>
+      <c r="F83" s="140"/>
+      <c r="G83" s="140"/>
+      <c r="H83" s="140"/>
+      <c r="I83" s="140"/>
+      <c r="J83" s="140"/>
+      <c r="K83" s="140"/>
+      <c r="L83" s="140"/>
+      <c r="M83" s="140"/>
+      <c r="N83" s="140"/>
+      <c r="O83" s="140"/>
+      <c r="P83" s="140"/>
+      <c r="Q83" s="140"/>
+      <c r="R83" s="140"/>
+      <c r="S83" s="140"/>
+      <c r="T83" s="140"/>
+      <c r="U83" s="140"/>
+      <c r="V83" s="140"/>
+      <c r="W83" s="140"/>
+      <c r="X83" s="140"/>
+      <c r="Y83" s="140"/>
+      <c r="Z83" s="140"/>
+      <c r="AA83" s="140"/>
+      <c r="AB83" s="140"/>
+      <c r="AC83" s="140"/>
+      <c r="AD83" s="140"/>
+      <c r="AE83" s="140"/>
+      <c r="AF83" s="140"/>
+      <c r="AG83" s="140"/>
+      <c r="AH83" s="140"/>
+      <c r="AI83" s="140"/>
+      <c r="AJ83" s="140"/>
       <c r="AL83" s="20">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -23321,10 +23321,10 @@
       </c>
     </row>
     <row r="84" spans="3:42" ht="18.75">
-      <c r="C84" s="181" t="s">
+      <c r="C84" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="D84" s="181"/>
+      <c r="D84" s="199"/>
       <c r="E84" s="34"/>
       <c r="F84" s="39">
         <f>SUM(F76:F78)</f>
@@ -23471,10 +23471,10 @@
       </c>
     </row>
     <row r="85" spans="3:42" ht="18.75">
-      <c r="C85" s="181" t="s">
+      <c r="C85" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="D85" s="181"/>
+      <c r="D85" s="199"/>
       <c r="E85" s="34"/>
       <c r="F85" s="35">
         <v>45</v>
@@ -23591,10 +23591,10 @@
       </c>
     </row>
     <row r="86" spans="3:42" ht="18.75">
-      <c r="C86" s="181" t="s">
+      <c r="C86" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="D86" s="181"/>
+      <c r="D86" s="199"/>
       <c r="E86" s="34"/>
       <c r="F86" s="35">
         <f>SUM(F76,F77,F78,F79,F81)</f>
@@ -23763,14 +23763,14 @@
       </c>
     </row>
     <row r="88" spans="3:42" ht="16.5" thickBot="1">
-      <c r="F88" s="197" t="s">
+      <c r="F88" s="181" t="s">
         <v>191</v>
       </c>
-      <c r="G88" s="198"/>
-      <c r="H88" s="198"/>
-      <c r="I88" s="198"/>
-      <c r="J88" s="198"/>
-      <c r="K88" s="199"/>
+      <c r="G88" s="182"/>
+      <c r="H88" s="182"/>
+      <c r="I88" s="182"/>
+      <c r="J88" s="182"/>
+      <c r="K88" s="183"/>
       <c r="AL88" s="20" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -23796,17 +23796,17 @@
       <c r="F89" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="G89" s="200" t="s">
+      <c r="G89" s="184" t="s">
         <v>193</v>
       </c>
-      <c r="H89" s="201"/>
+      <c r="H89" s="185"/>
       <c r="I89" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J89" s="185" t="s">
+      <c r="J89" s="169" t="s">
         <v>194</v>
       </c>
-      <c r="K89" s="186"/>
+      <c r="K89" s="170"/>
       <c r="AL89" s="20" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -23832,17 +23832,17 @@
       <c r="F90" s="62" t="s">
         <v>195</v>
       </c>
-      <c r="G90" s="202" t="s">
-        <v>103</v>
-      </c>
-      <c r="H90" s="203"/>
+      <c r="G90" s="186" t="s">
+        <v>103</v>
+      </c>
+      <c r="H90" s="187"/>
       <c r="I90" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="J90" s="204" t="s">
+      <c r="J90" s="188" t="s">
         <v>196</v>
       </c>
-      <c r="K90" s="205"/>
+      <c r="K90" s="189"/>
       <c r="AL90" s="20" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -23868,17 +23868,17 @@
       <c r="F91" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="G91" s="206" t="s">
-        <v>104</v>
-      </c>
-      <c r="H91" s="207"/>
+      <c r="G91" s="190" t="s">
+        <v>104</v>
+      </c>
+      <c r="H91" s="191"/>
       <c r="I91" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="J91" s="208" t="s">
+      <c r="J91" s="192" t="s">
         <v>199</v>
       </c>
-      <c r="K91" s="209"/>
+      <c r="K91" s="193"/>
       <c r="AL91" s="20" t="e">
         <f>COUNTIF(#REF!,"ST*")</f>
         <v>#REF!</v>
@@ -23904,94 +23904,121 @@
       <c r="F92" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="G92" s="178" t="s">
+      <c r="G92" s="196" t="s">
         <v>201</v>
       </c>
-      <c r="H92" s="179"/>
+      <c r="H92" s="197"/>
       <c r="I92" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="J92" s="187" t="s">
+      <c r="J92" s="171" t="s">
         <v>202</v>
       </c>
-      <c r="K92" s="188"/>
+      <c r="K92" s="172"/>
     </row>
     <row r="93" spans="3:42">
       <c r="F93" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G93" s="189" t="s">
+      <c r="G93" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="H93" s="190"/>
+      <c r="H93" s="174"/>
       <c r="I93" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J93" s="191" t="s">
+      <c r="J93" s="175" t="s">
         <v>204</v>
       </c>
-      <c r="K93" s="192"/>
+      <c r="K93" s="176"/>
     </row>
     <row r="94" spans="3:42">
       <c r="F94" s="66"/>
-      <c r="G94" s="193" t="s">
+      <c r="G94" s="177" t="s">
         <v>205</v>
       </c>
-      <c r="H94" s="194"/>
+      <c r="H94" s="178"/>
       <c r="I94" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="J94" s="195" t="s">
+      <c r="J94" s="179" t="s">
         <v>206</v>
       </c>
-      <c r="K94" s="196"/>
+      <c r="K94" s="180"/>
     </row>
     <row r="95" spans="3:42" ht="16.5" thickBot="1">
       <c r="F95" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="G95" s="182" t="s">
+      <c r="G95" s="166" t="s">
         <v>208</v>
       </c>
-      <c r="H95" s="183"/>
+      <c r="H95" s="167"/>
       <c r="I95" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="J95" s="182" t="s">
+      <c r="J95" s="166" t="s">
         <v>209</v>
       </c>
-      <c r="K95" s="184"/>
+      <c r="K95" s="168"/>
     </row>
     <row r="100" ht="9.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="F4:AJ82" xr:uid="{10A87D31-A428-49C7-B3CE-66B468A7BADA}"/>
   <mergeCells count="102">
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="J95:K95"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="J93:K93"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="J94:K94"/>
-    <mergeCell ref="F88:K88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="J91:K91"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="C53:D53"/>
@@ -24014,60 +24041,33 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C69:D69"/>
     <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
     <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="F88:K88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F15:AJ29">
@@ -24309,61 +24309,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="167" t="s">
+      <c r="F2" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168"/>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="169"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
+      <c r="AD2" s="208"/>
+      <c r="AE2" s="208"/>
+      <c r="AF2" s="208"/>
+      <c r="AG2" s="208"/>
+      <c r="AH2" s="208"/>
+      <c r="AI2" s="208"/>
+      <c r="AJ2" s="209"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
       <c r="F3" s="44" t="s">
         <v>88</v>
       </c>
@@ -24457,16 +24457,16 @@
       <c r="AJ3" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="41">
         <v>1</v>
       </c>
@@ -24560,20 +24560,20 @@
       <c r="AJ4" s="76">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="166" t="s">
+      <c r="C5" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="194"/>
       <c r="F5" s="21" t="s">
         <v>97</v>
       </c>
@@ -24692,10 +24692,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="166"/>
+      <c r="D6" s="194"/>
       <c r="F6" s="19" t="s">
         <v>100</v>
       </c>
@@ -24814,10 +24814,10 @@
       <c r="B7" s="35">
         <v>4</v>
       </c>
-      <c r="C7" s="137" t="s">
+      <c r="C7" s="120" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="138"/>
+      <c r="D7" s="121"/>
       <c r="F7" s="19" t="s">
         <v>103</v>
       </c>
@@ -24921,10 +24921,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="194" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="166"/>
+      <c r="D8" s="194"/>
       <c r="F8" s="19" t="s">
         <v>104</v>
       </c>
@@ -25074,10 +25074,10 @@
       <c r="AI9" s="18"/>
     </row>
     <row r="10" spans="2:42" ht="18.75">
-      <c r="C10" s="181" t="s">
+      <c r="C10" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="181"/>
+      <c r="D10" s="199"/>
       <c r="E10" s="34"/>
       <c r="F10" s="35">
         <f t="shared" ref="F10:AJ10" si="5">COUNTIF(F$5:F$8,"M*")</f>
@@ -25205,10 +25205,10 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75">
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="181"/>
+      <c r="D11" s="199"/>
       <c r="E11" s="34"/>
       <c r="F11" s="35">
         <f t="shared" ref="F11:AJ11" si="6">COUNTIF(F$5:F$8,"A*")</f>
@@ -25336,10 +25336,10 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="181" t="s">
+      <c r="C12" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="181"/>
+      <c r="D12" s="199"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f t="shared" ref="F12:AJ12" si="7">COUNTIF(F$5:F$8,"N*")</f>
@@ -25467,10 +25467,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="181" t="s">
+      <c r="C13" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="181"/>
+      <c r="D13" s="199"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f t="shared" ref="F13:AJ13" si="8">COUNTIF(F$5:F$8,"O*")</f>
@@ -25598,10 +25598,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D14" s="143"/>
+      <c r="D14" s="134"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f t="shared" ref="F14:AJ14" si="9">COUNTIF(F$5:F$8,"TR*")</f>
@@ -25729,10 +25729,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D15" s="143"/>
+      <c r="D15" s="134"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="10">COUNTIF(F$5:F$8,"ST*")</f>
@@ -25860,10 +25860,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="180" t="s">
+      <c r="C16" s="198" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="180"/>
+      <c r="D16" s="198"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37">
         <f>F18-F19</f>
@@ -25994,43 +25994,43 @@
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="141"/>
-      <c r="P17" s="141"/>
-      <c r="Q17" s="141"/>
-      <c r="R17" s="141"/>
-      <c r="S17" s="141"/>
-      <c r="T17" s="141"/>
-      <c r="U17" s="141"/>
-      <c r="V17" s="141"/>
-      <c r="W17" s="141"/>
-      <c r="X17" s="141"/>
-      <c r="Y17" s="141"/>
-      <c r="Z17" s="141"/>
-      <c r="AA17" s="141"/>
-      <c r="AB17" s="141"/>
-      <c r="AC17" s="141"/>
-      <c r="AD17" s="141"/>
-      <c r="AE17" s="141"/>
-      <c r="AF17" s="141"/>
-      <c r="AG17" s="141"/>
-      <c r="AH17" s="141"/>
-      <c r="AI17" s="141"/>
-      <c r="AJ17" s="141"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="140"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="140"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="140"/>
+      <c r="R17" s="140"/>
+      <c r="S17" s="140"/>
+      <c r="T17" s="140"/>
+      <c r="U17" s="140"/>
+      <c r="V17" s="140"/>
+      <c r="W17" s="140"/>
+      <c r="X17" s="140"/>
+      <c r="Y17" s="140"/>
+      <c r="Z17" s="140"/>
+      <c r="AA17" s="140"/>
+      <c r="AB17" s="140"/>
+      <c r="AC17" s="140"/>
+      <c r="AD17" s="140"/>
+      <c r="AE17" s="140"/>
+      <c r="AF17" s="140"/>
+      <c r="AG17" s="140"/>
+      <c r="AH17" s="140"/>
+      <c r="AI17" s="140"/>
+      <c r="AJ17" s="140"/>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="181" t="s">
+      <c r="C18" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="181"/>
+      <c r="D18" s="199"/>
       <c r="E18" s="34"/>
       <c r="F18" s="39">
         <f>SUM(F10:F12)</f>
@@ -26157,10 +26157,10 @@
       </c>
     </row>
     <row r="19" spans="3:36" ht="18.75">
-      <c r="C19" s="181" t="s">
+      <c r="C19" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="181"/>
+      <c r="D19" s="199"/>
       <c r="E19" s="34"/>
       <c r="F19" s="35">
         <v>2</v>
@@ -26257,10 +26257,10 @@
       </c>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="181" t="s">
+      <c r="C20" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="181"/>
+      <c r="D20" s="199"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35">
         <f>SUM(F10,F11,F12,F13,F15)</f>
@@ -26471,17 +26471,15 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
     <mergeCell ref="F17:AJ17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -26493,15 +26491,17 @@
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
@@ -26554,61 +26554,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="167" t="s">
+      <c r="F2" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168"/>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="169"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
+      <c r="AD2" s="208"/>
+      <c r="AE2" s="208"/>
+      <c r="AF2" s="208"/>
+      <c r="AG2" s="208"/>
+      <c r="AH2" s="208"/>
+      <c r="AI2" s="208"/>
+      <c r="AJ2" s="209"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
       <c r="F3" s="44" t="s">
         <v>88</v>
       </c>
@@ -26702,16 +26702,16 @@
       <c r="AJ3" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="41">
         <v>1</v>
       </c>
@@ -26805,20 +26805,20 @@
       <c r="AJ4" s="76">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="166" t="s">
+      <c r="C5" s="194" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="194"/>
       <c r="F5" s="40" t="s">
         <v>103</v>
       </c>
@@ -26937,10 +26937,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="166"/>
+      <c r="D6" s="194"/>
       <c r="F6" s="19" t="s">
         <v>108</v>
       </c>
@@ -27059,10 +27059,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="166" t="s">
+      <c r="C7" s="194" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="166"/>
+      <c r="D7" s="194"/>
       <c r="F7" s="19" t="s">
         <v>98</v>
       </c>
@@ -27181,10 +27181,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="194" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="166"/>
+      <c r="D8" s="194"/>
       <c r="F8" s="19" t="s">
         <v>104</v>
       </c>
@@ -27303,10 +27303,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="194" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="166"/>
+      <c r="D9" s="194"/>
       <c r="F9" s="19" t="s">
         <v>98</v>
       </c>
@@ -27426,10 +27426,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="194" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="166"/>
+      <c r="D10" s="194"/>
       <c r="F10" s="50" t="s">
         <v>103</v>
       </c>
@@ -27579,10 +27579,10 @@
       <c r="AI11" s="18"/>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="181" t="s">
+      <c r="C12" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="181"/>
+      <c r="D12" s="199"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f>COUNTIF(F$5:F$9,"M*")</f>
@@ -27710,10 +27710,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="181" t="s">
+      <c r="C13" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="181"/>
+      <c r="D13" s="199"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f>COUNTIF(F$5:F$9,"A*")</f>
@@ -27841,10 +27841,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="181" t="s">
+      <c r="C14" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="181"/>
+      <c r="D14" s="199"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f>COUNTIF(F$5:F$9,"N*")</f>
@@ -27972,10 +27972,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="181" t="s">
+      <c r="C15" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="181"/>
+      <c r="D15" s="199"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="8">COUNTIF(F$5:F$10,"O*")</f>
@@ -28103,10 +28103,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="143"/>
+      <c r="D16" s="134"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35">
         <f t="shared" ref="F16:AJ16" si="9">COUNTIF(F$5:F$10,"TR*")</f>
@@ -28234,10 +28234,10 @@
       </c>
     </row>
     <row r="17" spans="3:36" ht="18.75">
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="143"/>
+      <c r="D17" s="134"/>
       <c r="E17" s="34"/>
       <c r="F17" s="35">
         <f t="shared" ref="F17:AJ17" si="10">COUNTIF(F$5:F$10,"ST*")</f>
@@ -28365,10 +28365,10 @@
       </c>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="198" t="s">
         <v>213</v>
       </c>
-      <c r="D18" s="180"/>
+      <c r="D18" s="198"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37">
         <f>COUNTIF(F$5:F$10,"OT*")</f>
@@ -28499,43 +28499,43 @@
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="141"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="141"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="141"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="141"/>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
-      <c r="R19" s="141"/>
-      <c r="S19" s="141"/>
-      <c r="T19" s="141"/>
-      <c r="U19" s="141"/>
-      <c r="V19" s="141"/>
-      <c r="W19" s="141"/>
-      <c r="X19" s="141"/>
-      <c r="Y19" s="141"/>
-      <c r="Z19" s="141"/>
-      <c r="AA19" s="141"/>
-      <c r="AB19" s="141"/>
-      <c r="AC19" s="141"/>
-      <c r="AD19" s="141"/>
-      <c r="AE19" s="141"/>
-      <c r="AF19" s="141"/>
-      <c r="AG19" s="141"/>
-      <c r="AH19" s="141"/>
-      <c r="AI19" s="141"/>
-      <c r="AJ19" s="141"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
+      <c r="L19" s="140"/>
+      <c r="M19" s="140"/>
+      <c r="N19" s="140"/>
+      <c r="O19" s="140"/>
+      <c r="P19" s="140"/>
+      <c r="Q19" s="140"/>
+      <c r="R19" s="140"/>
+      <c r="S19" s="140"/>
+      <c r="T19" s="140"/>
+      <c r="U19" s="140"/>
+      <c r="V19" s="140"/>
+      <c r="W19" s="140"/>
+      <c r="X19" s="140"/>
+      <c r="Y19" s="140"/>
+      <c r="Z19" s="140"/>
+      <c r="AA19" s="140"/>
+      <c r="AB19" s="140"/>
+      <c r="AC19" s="140"/>
+      <c r="AD19" s="140"/>
+      <c r="AE19" s="140"/>
+      <c r="AF19" s="140"/>
+      <c r="AG19" s="140"/>
+      <c r="AH19" s="140"/>
+      <c r="AI19" s="140"/>
+      <c r="AJ19" s="140"/>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="181" t="s">
+      <c r="C20" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="D20" s="181"/>
+      <c r="D20" s="199"/>
       <c r="E20" s="34"/>
       <c r="F20" s="39">
         <f>SUM(F12:F14)</f>
@@ -28662,10 +28662,10 @@
       </c>
     </row>
     <row r="21" spans="3:36" ht="18.75">
-      <c r="C21" s="181" t="s">
+      <c r="C21" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="D21" s="181"/>
+      <c r="D21" s="199"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <v>3</v>
@@ -28762,10 +28762,10 @@
       </c>
     </row>
     <row r="22" spans="3:36" ht="18.75">
-      <c r="C22" s="181" t="s">
+      <c r="C22" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="D22" s="181"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f>SUM(F12,F13,F14,F15,F17)</f>
@@ -28893,177 +28893,206 @@
     </row>
     <row r="23" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="24" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F24" s="144" t="s">
+      <c r="F24" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="G24" s="145"/>
-      <c r="H24" s="145"/>
-      <c r="I24" s="145"/>
-      <c r="J24" s="145"/>
-      <c r="K24" s="146"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="128"/>
     </row>
     <row r="25" spans="3:36">
       <c r="F25" s="100" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="135" t="s">
+      <c r="G25" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="135"/>
+      <c r="H25" s="137"/>
       <c r="I25" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="147" t="s">
+      <c r="J25" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="K25" s="148"/>
+      <c r="K25" s="130"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G26" s="136" t="s">
+      <c r="G26" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H26" s="136"/>
+      <c r="H26" s="131"/>
       <c r="I26" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="J26" s="136" t="s">
+      <c r="J26" s="131" t="s">
         <v>217</v>
       </c>
-      <c r="K26" s="149"/>
+      <c r="K26" s="132"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="G27" s="133" t="s">
+      <c r="G27" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="H27" s="133"/>
+      <c r="H27" s="135"/>
       <c r="I27" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="J27" s="133" t="s">
+      <c r="J27" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="K27" s="134"/>
+      <c r="K27" s="136"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="G28" s="130" t="s">
+      <c r="G28" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="H28" s="130"/>
+      <c r="H28" s="154"/>
       <c r="I28" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="J28" s="124" t="s">
+      <c r="J28" s="148" t="s">
         <v>223</v>
       </c>
-      <c r="K28" s="125"/>
+      <c r="K28" s="149"/>
     </row>
     <row r="29" spans="3:36">
       <c r="F29" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="130" t="s">
+      <c r="G29" s="154" t="s">
         <v>224</v>
       </c>
-      <c r="H29" s="130"/>
+      <c r="H29" s="154"/>
       <c r="I29" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="126" t="s">
+      <c r="J29" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="127"/>
+      <c r="K29" s="151"/>
     </row>
     <row r="30" spans="3:36">
       <c r="F30" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="131" t="s">
+      <c r="G30" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="H30" s="131"/>
+      <c r="H30" s="155"/>
       <c r="I30" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J30" s="126" t="s">
+      <c r="J30" s="150" t="s">
         <v>204</v>
       </c>
-      <c r="K30" s="127"/>
+      <c r="K30" s="151"/>
     </row>
     <row r="31" spans="3:36">
       <c r="F31" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="132" t="s">
+      <c r="G31" s="156" t="s">
         <v>205</v>
       </c>
-      <c r="H31" s="132"/>
+      <c r="H31" s="156"/>
       <c r="I31" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J31" s="126" t="s">
+      <c r="J31" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="K31" s="127"/>
+      <c r="K31" s="151"/>
     </row>
     <row r="32" spans="3:36">
       <c r="F32" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="G32" s="128" t="s">
+      <c r="G32" s="152" t="s">
         <v>208</v>
       </c>
-      <c r="H32" s="128"/>
+      <c r="H32" s="152"/>
       <c r="I32" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="J32" s="128" t="s">
+      <c r="J32" s="152" t="s">
         <v>209</v>
       </c>
-      <c r="K32" s="129"/>
+      <c r="K32" s="153"/>
     </row>
     <row r="33" spans="6:11">
       <c r="F33" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="G33" s="117" t="s">
+      <c r="G33" s="141" t="s">
         <v>227</v>
       </c>
-      <c r="H33" s="118"/>
+      <c r="H33" s="142"/>
       <c r="I33" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="J33" s="117" t="s">
+      <c r="J33" s="141" t="s">
         <v>228</v>
       </c>
-      <c r="K33" s="119"/>
+      <c r="K33" s="143"/>
     </row>
     <row r="34" spans="6:11" ht="16.5" thickBot="1">
       <c r="F34" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="120" t="s">
+      <c r="G34" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="H34" s="121"/>
+      <c r="H34" s="145"/>
       <c r="I34" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="J34" s="122" t="s">
+      <c r="J34" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="K34" s="123"/>
+      <c r="K34" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="F24:K24"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="F19:AJ19"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="B3:D4"/>
@@ -29080,35 +29109,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="F19:AJ19"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="F24:K24"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
@@ -29177,61 +29177,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="238" t="s">
+      <c r="F2" s="235" t="s">
         <v>232</v>
       </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238"/>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="238"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="238"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="238"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="235"/>
+      <c r="H2" s="235"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="M2" s="235"/>
+      <c r="N2" s="235"/>
+      <c r="O2" s="235"/>
+      <c r="P2" s="235"/>
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
+      <c r="AD2" s="235"/>
+      <c r="AE2" s="235"/>
+      <c r="AF2" s="235"/>
+      <c r="AG2" s="235"/>
+      <c r="AH2" s="235"/>
+      <c r="AI2" s="235"/>
+      <c r="AJ2" s="235"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="232" t="s">
+      <c r="B3" s="228" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="233"/>
-      <c r="D3" s="234"/>
+      <c r="C3" s="229"/>
+      <c r="D3" s="230"/>
       <c r="F3" s="80" t="s">
         <v>88</v>
       </c>
@@ -29325,16 +29325,16 @@
       <c r="AJ3" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="235"/>
-      <c r="C4" s="236"/>
-      <c r="D4" s="237"/>
+      <c r="B4" s="231"/>
+      <c r="C4" s="232"/>
+      <c r="D4" s="233"/>
       <c r="F4" s="77">
         <v>1</v>
       </c>
@@ -29428,20 +29428,20 @@
       <c r="AJ4" s="79">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="51">
         <v>1</v>
       </c>
-      <c r="C5" s="170" t="s">
+      <c r="C5" s="200" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="239"/>
+      <c r="D5" s="236"/>
       <c r="F5" s="93" t="s">
         <v>103</v>
       </c>
@@ -29560,10 +29560,10 @@
       <c r="B6" s="48">
         <v>2</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="194" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="228"/>
+      <c r="D6" s="234"/>
       <c r="F6" s="90" t="s">
         <v>103</v>
       </c>
@@ -29682,10 +29682,10 @@
       <c r="B7" s="48">
         <v>3</v>
       </c>
-      <c r="C7" s="166" t="s">
+      <c r="C7" s="194" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="228"/>
+      <c r="D7" s="234"/>
       <c r="F7" s="90" t="s">
         <v>104</v>
       </c>
@@ -29804,10 +29804,10 @@
       <c r="B8" s="48">
         <v>4</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="228"/>
+      <c r="D8" s="234"/>
       <c r="F8" s="90" t="s">
         <v>108</v>
       </c>
@@ -29926,10 +29926,10 @@
       <c r="B9" s="48">
         <v>5</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="194" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="228"/>
+      <c r="D9" s="234"/>
       <c r="F9" s="95" t="s">
         <v>97</v>
       </c>
@@ -30048,10 +30048,10 @@
       <c r="B10" s="48">
         <v>6</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="194" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="228"/>
+      <c r="D10" s="234"/>
       <c r="F10" s="90" t="s">
         <v>98</v>
       </c>
@@ -30170,10 +30170,10 @@
       <c r="B11" s="48">
         <v>7</v>
       </c>
-      <c r="C11" s="166" t="s">
+      <c r="C11" s="194" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="228"/>
+      <c r="D11" s="234"/>
       <c r="F11" s="90" t="s">
         <v>98</v>
       </c>
@@ -30292,10 +30292,10 @@
       <c r="B12" s="48">
         <v>8</v>
       </c>
-      <c r="C12" s="166" t="s">
+      <c r="C12" s="194" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="228"/>
+      <c r="D12" s="234"/>
       <c r="F12" s="90" t="s">
         <v>103</v>
       </c>
@@ -30414,10 +30414,10 @@
       <c r="B13" s="48">
         <v>9</v>
       </c>
-      <c r="C13" s="166" t="s">
+      <c r="C13" s="194" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="228"/>
+      <c r="D13" s="234"/>
       <c r="F13" s="90" t="s">
         <v>104</v>
       </c>
@@ -30536,10 +30536,10 @@
       <c r="B14" s="48">
         <v>10</v>
       </c>
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="194" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="228"/>
+      <c r="D14" s="234"/>
       <c r="F14" s="90" t="s">
         <v>104</v>
       </c>
@@ -30658,10 +30658,10 @@
       <c r="B15" s="48">
         <v>11</v>
       </c>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="120" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="229"/>
+      <c r="D15" s="237"/>
       <c r="F15" s="90" t="s">
         <v>108</v>
       </c>
@@ -30780,10 +30780,10 @@
       <c r="B16" s="48">
         <v>12</v>
       </c>
-      <c r="C16" s="137" t="s">
+      <c r="C16" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="229"/>
+      <c r="D16" s="237"/>
       <c r="F16" s="90" t="s">
         <v>108</v>
       </c>
@@ -30902,10 +30902,10 @@
       <c r="B17" s="48">
         <v>13</v>
       </c>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="229"/>
+      <c r="D17" s="237"/>
       <c r="F17" s="95" t="s">
         <v>98</v>
       </c>
@@ -31024,10 +31024,10 @@
       <c r="B18" s="114">
         <v>15</v>
       </c>
-      <c r="C18" s="172" t="s">
+      <c r="C18" s="202" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="230"/>
+      <c r="D18" s="238"/>
       <c r="F18" s="97" t="s">
         <v>98</v>
       </c>
@@ -31146,10 +31146,10 @@
       <c r="B19" s="49">
         <v>14</v>
       </c>
-      <c r="C19" s="174" t="s">
+      <c r="C19" s="204" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="231"/>
+      <c r="D19" s="239"/>
       <c r="E19" s="116"/>
       <c r="F19" s="92" t="s">
         <v>98</v>
@@ -31300,10 +31300,10 @@
       <c r="AI20" s="18"/>
     </row>
     <row r="21" spans="2:42" ht="18.75">
-      <c r="C21" s="181" t="s">
+      <c r="C21" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="181"/>
+      <c r="D21" s="199"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <f t="shared" ref="F21:AJ21" si="5">COUNTIF(F$5:F$19,"M*")</f>
@@ -31431,10 +31431,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75">
-      <c r="C22" s="181" t="s">
+      <c r="C22" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="181"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f t="shared" ref="F22:AJ22" si="6">COUNTIF(F$5:F$19,"A*")</f>
@@ -31562,10 +31562,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75">
-      <c r="C23" s="181" t="s">
+      <c r="C23" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="181"/>
+      <c r="D23" s="199"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35">
         <f t="shared" ref="F23:AJ23" si="7">COUNTIF(F$5:F$19,"N*")</f>
@@ -31693,10 +31693,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75">
-      <c r="C24" s="181" t="s">
+      <c r="C24" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="181"/>
+      <c r="D24" s="199"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35">
         <f t="shared" ref="F24:AJ24" si="8">COUNTIF(F$5:F$19,"O*")</f>
@@ -31824,10 +31824,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="143"/>
+      <c r="D25" s="134"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f t="shared" ref="F25:AJ25" si="9">COUNTIF(F$5:F$19,"ST*")</f>
@@ -31955,10 +31955,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="180" t="s">
+      <c r="C26" s="198" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="180"/>
+      <c r="D26" s="198"/>
       <c r="E26" s="36"/>
       <c r="F26" s="37">
         <f>COUNTIF(F$5:F$19,"OT*")</f>
@@ -32089,43 +32089,43 @@
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="141"/>
-      <c r="Q27" s="141"/>
-      <c r="R27" s="141"/>
-      <c r="S27" s="141"/>
-      <c r="T27" s="141"/>
-      <c r="U27" s="141"/>
-      <c r="V27" s="141"/>
-      <c r="W27" s="141"/>
-      <c r="X27" s="141"/>
-      <c r="Y27" s="141"/>
-      <c r="Z27" s="141"/>
-      <c r="AA27" s="141"/>
-      <c r="AB27" s="141"/>
-      <c r="AC27" s="141"/>
-      <c r="AD27" s="141"/>
-      <c r="AE27" s="141"/>
-      <c r="AF27" s="141"/>
-      <c r="AG27" s="141"/>
-      <c r="AH27" s="141"/>
-      <c r="AI27" s="141"/>
-      <c r="AJ27" s="141"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="140"/>
+      <c r="O27" s="140"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="140"/>
+      <c r="R27" s="140"/>
+      <c r="S27" s="140"/>
+      <c r="T27" s="140"/>
+      <c r="U27" s="140"/>
+      <c r="V27" s="140"/>
+      <c r="W27" s="140"/>
+      <c r="X27" s="140"/>
+      <c r="Y27" s="140"/>
+      <c r="Z27" s="140"/>
+      <c r="AA27" s="140"/>
+      <c r="AB27" s="140"/>
+      <c r="AC27" s="140"/>
+      <c r="AD27" s="140"/>
+      <c r="AE27" s="140"/>
+      <c r="AF27" s="140"/>
+      <c r="AG27" s="140"/>
+      <c r="AH27" s="140"/>
+      <c r="AI27" s="140"/>
+      <c r="AJ27" s="140"/>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="181" t="s">
+      <c r="C28" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="181"/>
+      <c r="D28" s="199"/>
       <c r="E28" s="34"/>
       <c r="F28" s="39">
         <f>SUM(F21:F23)</f>
@@ -32252,10 +32252,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="181" t="s">
+      <c r="C29" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="181"/>
+      <c r="D29" s="199"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <v>6</v>
@@ -32352,10 +32352,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="181" t="s">
+      <c r="C30" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="D30" s="181"/>
+      <c r="D30" s="199"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f>SUM(F21,F22,F23,F24,F25)</f>
@@ -32483,198 +32483,193 @@
     </row>
     <row r="32" spans="2:42" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="6:11" ht="16.5" thickBot="1">
-      <c r="F33" s="144" t="s">
+      <c r="F33" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="145"/>
-      <c r="H33" s="145"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145"/>
-      <c r="K33" s="146"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="127"/>
+      <c r="K33" s="128"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="100" t="s">
         <v>192</v>
       </c>
-      <c r="G34" s="135" t="s">
+      <c r="G34" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H34" s="135"/>
+      <c r="H34" s="137"/>
       <c r="I34" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="J34" s="147" t="s">
+      <c r="J34" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="K34" s="148"/>
+      <c r="K34" s="130"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G35" s="136" t="s">
+      <c r="G35" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H35" s="136"/>
+      <c r="H35" s="131"/>
       <c r="I35" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="J35" s="136" t="s">
+      <c r="J35" s="131" t="s">
         <v>217</v>
       </c>
-      <c r="K35" s="149"/>
+      <c r="K35" s="132"/>
     </row>
     <row r="36" spans="6:11">
       <c r="F36" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="G36" s="133" t="s">
+      <c r="G36" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="H36" s="133"/>
+      <c r="H36" s="135"/>
       <c r="I36" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="J36" s="133" t="s">
+      <c r="J36" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="K36" s="134"/>
+      <c r="K36" s="136"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="G37" s="130" t="s">
+      <c r="G37" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="H37" s="130"/>
+      <c r="H37" s="154"/>
       <c r="I37" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="J37" s="124" t="s">
+      <c r="J37" s="148" t="s">
         <v>223</v>
       </c>
-      <c r="K37" s="125"/>
+      <c r="K37" s="149"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="G38" s="130" t="s">
+      <c r="G38" s="154" t="s">
         <v>224</v>
       </c>
-      <c r="H38" s="130"/>
+      <c r="H38" s="154"/>
       <c r="I38" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="J38" s="126" t="s">
+      <c r="J38" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="K38" s="127"/>
+      <c r="K38" s="151"/>
     </row>
     <row r="39" spans="6:11">
       <c r="F39" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="131" t="s">
+      <c r="G39" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="H39" s="131"/>
+      <c r="H39" s="155"/>
       <c r="I39" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J39" s="126" t="s">
+      <c r="J39" s="150" t="s">
         <v>204</v>
       </c>
-      <c r="K39" s="127"/>
+      <c r="K39" s="151"/>
     </row>
     <row r="40" spans="6:11">
       <c r="F40" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="G40" s="132" t="s">
+      <c r="G40" s="156" t="s">
         <v>205</v>
       </c>
-      <c r="H40" s="132"/>
+      <c r="H40" s="156"/>
       <c r="I40" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J40" s="126" t="s">
+      <c r="J40" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="K40" s="127"/>
+      <c r="K40" s="151"/>
     </row>
     <row r="41" spans="6:11">
       <c r="F41" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="128" t="s">
+      <c r="G41" s="152" t="s">
         <v>208</v>
       </c>
-      <c r="H41" s="128"/>
+      <c r="H41" s="152"/>
       <c r="I41" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="J41" s="128" t="s">
+      <c r="J41" s="152" t="s">
         <v>209</v>
       </c>
-      <c r="K41" s="129"/>
+      <c r="K41" s="153"/>
     </row>
     <row r="42" spans="6:11">
       <c r="F42" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="G42" s="117" t="s">
+      <c r="G42" s="141" t="s">
         <v>227</v>
       </c>
-      <c r="H42" s="118"/>
+      <c r="H42" s="142"/>
       <c r="I42" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="J42" s="117" t="s">
+      <c r="J42" s="141" t="s">
         <v>228</v>
       </c>
-      <c r="K42" s="119"/>
+      <c r="K42" s="143"/>
     </row>
     <row r="43" spans="6:11" ht="16.5" thickBot="1">
       <c r="F43" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="120" t="s">
+      <c r="G43" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="H43" s="121"/>
+      <c r="H43" s="145"/>
       <c r="I43" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="J43" s="122" t="s">
+      <c r="J43" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="K43" s="123"/>
+      <c r="K43" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="F27:AJ27"/>
     <mergeCell ref="C14:D14"/>
@@ -32691,22 +32686,27 @@
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
@@ -32778,61 +32778,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="167" t="s">
+      <c r="F2" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168"/>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="169"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
+      <c r="AD2" s="208"/>
+      <c r="AE2" s="208"/>
+      <c r="AF2" s="208"/>
+      <c r="AG2" s="208"/>
+      <c r="AH2" s="208"/>
+      <c r="AI2" s="208"/>
+      <c r="AJ2" s="209"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
       <c r="F3" s="44" t="s">
         <v>88</v>
       </c>
@@ -32926,16 +32926,16 @@
       <c r="AJ3" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="41">
         <v>1</v>
       </c>
@@ -33029,20 +33029,20 @@
       <c r="AJ4" s="76">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="166" t="s">
+      <c r="C5" s="194" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="194"/>
       <c r="F5" s="93" t="s">
         <v>103</v>
       </c>
@@ -33161,10 +33161,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="194" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="166"/>
+      <c r="D6" s="194"/>
       <c r="F6" s="90" t="s">
         <v>104</v>
       </c>
@@ -33283,10 +33283,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="166" t="s">
+      <c r="C7" s="194" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="166"/>
+      <c r="D7" s="194"/>
       <c r="F7" s="90" t="s">
         <v>104</v>
       </c>
@@ -33405,10 +33405,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="194" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="166"/>
+      <c r="D8" s="194"/>
       <c r="F8" s="90" t="s">
         <v>108</v>
       </c>
@@ -33527,10 +33527,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="194" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="166"/>
+      <c r="D9" s="194"/>
       <c r="F9" s="90" t="s">
         <v>98</v>
       </c>
@@ -33649,10 +33649,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="194" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="166"/>
+      <c r="D10" s="194"/>
       <c r="F10" s="90" t="s">
         <v>108</v>
       </c>
@@ -33771,10 +33771,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="166" t="s">
+      <c r="C11" s="194" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="166"/>
+      <c r="D11" s="194"/>
       <c r="F11" s="90" t="s">
         <v>103</v>
       </c>
@@ -33893,10 +33893,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="166" t="s">
+      <c r="C12" s="194" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="166"/>
+      <c r="D12" s="194"/>
       <c r="F12" s="90" t="s">
         <v>104</v>
       </c>
@@ -34015,10 +34015,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="166" t="s">
+      <c r="C13" s="194" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="166"/>
+      <c r="D13" s="194"/>
       <c r="F13" s="90" t="s">
         <v>108</v>
       </c>
@@ -34137,10 +34137,10 @@
       <c r="B14" s="98">
         <v>10</v>
       </c>
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="194" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="166"/>
+      <c r="D14" s="194"/>
       <c r="F14" s="90" t="s">
         <v>98</v>
       </c>
@@ -34259,10 +34259,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="166" t="s">
+      <c r="C15" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="166"/>
+      <c r="D15" s="194"/>
       <c r="F15" s="90" t="s">
         <v>144</v>
       </c>
@@ -34381,10 +34381,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="166" t="s">
+      <c r="C16" s="194" t="s">
         <v>145</v>
       </c>
-      <c r="D16" s="166"/>
+      <c r="D16" s="194"/>
       <c r="F16" s="90" t="s">
         <v>103</v>
       </c>
@@ -34503,10 +34503,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="166" t="s">
+      <c r="C17" s="194" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="166"/>
+      <c r="D17" s="194"/>
       <c r="F17" s="90" t="s">
         <v>104</v>
       </c>
@@ -34625,10 +34625,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="166" t="s">
+      <c r="C18" s="194" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="166"/>
+      <c r="D18" s="194"/>
       <c r="F18" s="90" t="s">
         <v>108</v>
       </c>
@@ -34747,10 +34747,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="166" t="s">
+      <c r="C19" s="194" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="166"/>
+      <c r="D19" s="194"/>
       <c r="F19" s="90" t="s">
         <v>98</v>
       </c>
@@ -34869,10 +34869,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="166" t="s">
+      <c r="C20" s="194" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="166"/>
+      <c r="D20" s="194"/>
       <c r="F20" s="90" t="s">
         <v>98</v>
       </c>
@@ -34991,10 +34991,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="166" t="s">
+      <c r="C21" s="194" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="166"/>
+      <c r="D21" s="194"/>
       <c r="F21" s="90" t="s">
         <v>98</v>
       </c>
@@ -35113,10 +35113,10 @@
       <c r="B22" s="35">
         <v>18</v>
       </c>
-      <c r="C22" s="166" t="s">
+      <c r="C22" s="194" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="166"/>
+      <c r="D22" s="194"/>
       <c r="F22" s="90" t="s">
         <v>103</v>
       </c>
@@ -35235,10 +35235,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="137" t="s">
+      <c r="C23" s="120" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="138"/>
+      <c r="D23" s="121"/>
       <c r="F23" s="90" t="s">
         <v>103</v>
       </c>
@@ -35357,10 +35357,10 @@
       <c r="B24" s="35">
         <v>20</v>
       </c>
-      <c r="C24" s="166" t="s">
+      <c r="C24" s="194" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="166"/>
+      <c r="D24" s="194"/>
       <c r="F24" s="90" t="s">
         <v>104</v>
       </c>
@@ -35479,10 +35479,10 @@
       <c r="B25" s="35">
         <v>21</v>
       </c>
-      <c r="C25" s="166" t="s">
+      <c r="C25" s="194" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="166"/>
+      <c r="D25" s="194"/>
       <c r="F25" s="90" t="s">
         <v>108</v>
       </c>
@@ -35601,10 +35601,10 @@
       <c r="B26" s="35">
         <v>22</v>
       </c>
-      <c r="C26" s="166" t="s">
+      <c r="C26" s="194" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="166"/>
+      <c r="D26" s="194"/>
       <c r="F26" s="90" t="s">
         <v>108</v>
       </c>
@@ -35723,10 +35723,10 @@
       <c r="B27" s="35">
         <v>23</v>
       </c>
-      <c r="C27" s="137" t="s">
+      <c r="C27" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="D27" s="138"/>
+      <c r="D27" s="121"/>
       <c r="F27" s="90" t="s">
         <v>98</v>
       </c>
@@ -35845,10 +35845,10 @@
       <c r="B28" s="35">
         <v>24</v>
       </c>
-      <c r="C28" s="137" t="s">
+      <c r="C28" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="138"/>
+      <c r="D28" s="121"/>
       <c r="F28" s="90" t="s">
         <v>98</v>
       </c>
@@ -35967,10 +35967,10 @@
       <c r="B29" s="35">
         <v>25</v>
       </c>
-      <c r="C29" s="137" t="s">
+      <c r="C29" s="120" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="138"/>
+      <c r="D29" s="121"/>
       <c r="F29" s="90" t="s">
         <v>103</v>
       </c>
@@ -36089,10 +36089,10 @@
       <c r="B30" s="35">
         <v>26</v>
       </c>
-      <c r="C30" s="166" t="s">
+      <c r="C30" s="194" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="166"/>
+      <c r="D30" s="194"/>
       <c r="F30" s="90" t="s">
         <v>108</v>
       </c>
@@ -36211,10 +36211,10 @@
       <c r="B31" s="35">
         <v>27</v>
       </c>
-      <c r="C31" s="137" t="s">
+      <c r="C31" s="120" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="138"/>
+      <c r="D31" s="121"/>
       <c r="F31" s="90" t="s">
         <v>98</v>
       </c>
@@ -36333,10 +36333,10 @@
       <c r="B32" s="35">
         <v>28</v>
       </c>
-      <c r="C32" s="137" t="s">
+      <c r="C32" s="120" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="138"/>
+      <c r="D32" s="121"/>
       <c r="F32" s="90" t="s">
         <v>104</v>
       </c>
@@ -36455,10 +36455,10 @@
       <c r="B33" s="35">
         <v>29</v>
       </c>
-      <c r="C33" s="137" t="s">
+      <c r="C33" s="120" t="s">
         <v>164</v>
       </c>
-      <c r="D33" s="138"/>
+      <c r="D33" s="121"/>
       <c r="F33" s="90" t="s">
         <v>104</v>
       </c>
@@ -36577,10 +36577,10 @@
       <c r="B34" s="35">
         <v>30</v>
       </c>
-      <c r="C34" s="166" t="s">
+      <c r="C34" s="194" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="166"/>
+      <c r="D34" s="194"/>
       <c r="F34" s="90" t="s">
         <v>108</v>
       </c>
@@ -36699,10 +36699,10 @@
       <c r="B35" s="35">
         <v>31</v>
       </c>
-      <c r="C35" s="177" t="s">
+      <c r="C35" s="195" t="s">
         <v>166</v>
       </c>
-      <c r="D35" s="177"/>
+      <c r="D35" s="195"/>
       <c r="F35" s="92" t="s">
         <v>103</v>
       </c>
@@ -36852,10 +36852,10 @@
       <c r="AI36" s="18"/>
     </row>
     <row r="37" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C37" s="181" t="s">
+      <c r="C37" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="181"/>
+      <c r="D37" s="199"/>
       <c r="E37" s="34"/>
       <c r="F37" s="35">
         <f t="shared" ref="F37:AJ37" si="5">COUNTIF(F$5:F$33,"M*")</f>
@@ -36983,10 +36983,10 @@
       </c>
     </row>
     <row r="38" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C38" s="181" t="s">
+      <c r="C38" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="D38" s="181"/>
+      <c r="D38" s="199"/>
       <c r="E38" s="34"/>
       <c r="F38" s="35">
         <f t="shared" ref="F38:AJ38" si="6">COUNTIF(F$5:F$33,"A*")</f>
@@ -37114,10 +37114,10 @@
       </c>
     </row>
     <row r="39" spans="2:42" ht="18.75">
-      <c r="C39" s="181" t="s">
+      <c r="C39" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="181"/>
+      <c r="D39" s="199"/>
       <c r="E39" s="34"/>
       <c r="F39" s="35">
         <f t="shared" ref="F39:AJ39" si="7">COUNTIF(F$5:F$33,"N*")</f>
@@ -37245,10 +37245,10 @@
       </c>
     </row>
     <row r="40" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C40" s="181" t="s">
+      <c r="C40" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="181"/>
+      <c r="D40" s="199"/>
       <c r="E40" s="34"/>
       <c r="F40" s="35">
         <f t="shared" ref="F40:AJ40" si="8">COUNTIF(F$5:F$35,"O*")</f>
@@ -37376,10 +37376,10 @@
       </c>
     </row>
     <row r="41" spans="2:42" ht="18.75">
-      <c r="C41" s="142" t="s">
+      <c r="C41" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D41" s="143"/>
+      <c r="D41" s="134"/>
       <c r="E41" s="34"/>
       <c r="F41" s="35">
         <f t="shared" ref="F41:AJ41" si="9">COUNTIF(F$5:F$35,"TR*")</f>
@@ -37507,10 +37507,10 @@
       </c>
     </row>
     <row r="42" spans="2:42" ht="18.75">
-      <c r="C42" s="142" t="s">
+      <c r="C42" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="143"/>
+      <c r="D42" s="134"/>
       <c r="E42" s="34"/>
       <c r="F42" s="35">
         <f>COUNTIF(F$5:F$35,"ST*")</f>
@@ -37638,10 +37638,10 @@
       </c>
     </row>
     <row r="43" spans="2:42" ht="18.75">
-      <c r="C43" s="180" t="s">
+      <c r="C43" s="198" t="s">
         <v>187</v>
       </c>
-      <c r="D43" s="180"/>
+      <c r="D43" s="198"/>
       <c r="E43" s="36"/>
       <c r="F43" s="37">
         <f t="shared" ref="F43:AJ43" si="11">COUNTIF(F$5:F$35,"OT*")</f>
@@ -37772,43 +37772,43 @@
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
       <c r="E44" s="34"/>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
-      <c r="L44" s="141"/>
-      <c r="M44" s="141"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="141"/>
-      <c r="P44" s="141"/>
-      <c r="Q44" s="141"/>
-      <c r="R44" s="141"/>
-      <c r="S44" s="141"/>
-      <c r="T44" s="141"/>
-      <c r="U44" s="141"/>
-      <c r="V44" s="141"/>
-      <c r="W44" s="141"/>
-      <c r="X44" s="141"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="141"/>
-      <c r="AA44" s="141"/>
-      <c r="AB44" s="141"/>
-      <c r="AC44" s="141"/>
-      <c r="AD44" s="141"/>
-      <c r="AE44" s="141"/>
-      <c r="AF44" s="141"/>
-      <c r="AG44" s="141"/>
-      <c r="AH44" s="141"/>
-      <c r="AI44" s="141"/>
-      <c r="AJ44" s="141"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="140"/>
+      <c r="I44" s="140"/>
+      <c r="J44" s="140"/>
+      <c r="K44" s="140"/>
+      <c r="L44" s="140"/>
+      <c r="M44" s="140"/>
+      <c r="N44" s="140"/>
+      <c r="O44" s="140"/>
+      <c r="P44" s="140"/>
+      <c r="Q44" s="140"/>
+      <c r="R44" s="140"/>
+      <c r="S44" s="140"/>
+      <c r="T44" s="140"/>
+      <c r="U44" s="140"/>
+      <c r="V44" s="140"/>
+      <c r="W44" s="140"/>
+      <c r="X44" s="140"/>
+      <c r="Y44" s="140"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="140"/>
+      <c r="AB44" s="140"/>
+      <c r="AC44" s="140"/>
+      <c r="AD44" s="140"/>
+      <c r="AE44" s="140"/>
+      <c r="AF44" s="140"/>
+      <c r="AG44" s="140"/>
+      <c r="AH44" s="140"/>
+      <c r="AI44" s="140"/>
+      <c r="AJ44" s="140"/>
     </row>
     <row r="45" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C45" s="181" t="s">
+      <c r="C45" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="181"/>
+      <c r="D45" s="199"/>
       <c r="E45" s="34"/>
       <c r="F45" s="39">
         <f>SUM(F37:F39)</f>
@@ -37935,10 +37935,10 @@
       </c>
     </row>
     <row r="46" spans="2:42" ht="18.75">
-      <c r="C46" s="181" t="s">
+      <c r="C46" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="D46" s="181"/>
+      <c r="D46" s="199"/>
       <c r="E46" s="34"/>
       <c r="F46" s="35">
         <v>18</v>
@@ -38035,10 +38035,10 @@
       </c>
     </row>
     <row r="47" spans="2:42" ht="18.75">
-      <c r="C47" s="181" t="s">
+      <c r="C47" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="D47" s="181"/>
+      <c r="D47" s="199"/>
       <c r="E47" s="34"/>
       <c r="F47" s="35">
         <f>SUM(F37,F38,F39,F40,F42)</f>
@@ -38166,178 +38166,232 @@
     </row>
     <row r="48" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="49" spans="6:11" ht="16.5" thickBot="1">
-      <c r="F49" s="144" t="s">
+      <c r="F49" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="G49" s="145"/>
-      <c r="H49" s="145"/>
-      <c r="I49" s="145"/>
-      <c r="J49" s="145"/>
-      <c r="K49" s="146"/>
+      <c r="G49" s="127"/>
+      <c r="H49" s="127"/>
+      <c r="I49" s="127"/>
+      <c r="J49" s="127"/>
+      <c r="K49" s="128"/>
     </row>
     <row r="50" spans="6:11">
       <c r="F50" s="100" t="s">
         <v>192</v>
       </c>
-      <c r="G50" s="135" t="s">
+      <c r="G50" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H50" s="135"/>
+      <c r="H50" s="137"/>
       <c r="I50" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="J50" s="147" t="s">
+      <c r="J50" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="K50" s="148"/>
+      <c r="K50" s="130"/>
     </row>
     <row r="51" spans="6:11">
       <c r="F51" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="136" t="s">
+      <c r="G51" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H51" s="136"/>
+      <c r="H51" s="131"/>
       <c r="I51" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="J51" s="136" t="s">
+      <c r="J51" s="131" t="s">
         <v>217</v>
       </c>
-      <c r="K51" s="149"/>
+      <c r="K51" s="132"/>
     </row>
     <row r="52" spans="6:11">
       <c r="F52" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="G52" s="133" t="s">
+      <c r="G52" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="H52" s="133"/>
+      <c r="H52" s="135"/>
       <c r="I52" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="J52" s="133" t="s">
+      <c r="J52" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="K52" s="134"/>
+      <c r="K52" s="136"/>
     </row>
     <row r="53" spans="6:11">
       <c r="F53" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="G53" s="130" t="s">
+      <c r="G53" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="H53" s="130"/>
+      <c r="H53" s="154"/>
       <c r="I53" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="J53" s="124" t="s">
+      <c r="J53" s="148" t="s">
         <v>223</v>
       </c>
-      <c r="K53" s="125"/>
+      <c r="K53" s="149"/>
     </row>
     <row r="54" spans="6:11">
       <c r="F54" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="G54" s="130" t="s">
+      <c r="G54" s="154" t="s">
         <v>224</v>
       </c>
-      <c r="H54" s="130"/>
+      <c r="H54" s="154"/>
       <c r="I54" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="J54" s="126" t="s">
+      <c r="J54" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="K54" s="127"/>
+      <c r="K54" s="151"/>
     </row>
     <row r="55" spans="6:11">
       <c r="F55" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G55" s="131" t="s">
+      <c r="G55" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="H55" s="131"/>
+      <c r="H55" s="155"/>
       <c r="I55" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J55" s="126" t="s">
+      <c r="J55" s="150" t="s">
         <v>204</v>
       </c>
-      <c r="K55" s="127"/>
+      <c r="K55" s="151"/>
     </row>
     <row r="56" spans="6:11">
       <c r="F56" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="G56" s="132" t="s">
+      <c r="G56" s="156" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="132"/>
+      <c r="H56" s="156"/>
       <c r="I56" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J56" s="126" t="s">
+      <c r="J56" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="K56" s="127"/>
+      <c r="K56" s="151"/>
     </row>
     <row r="57" spans="6:11">
       <c r="F57" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="G57" s="128" t="s">
+      <c r="G57" s="152" t="s">
         <v>208</v>
       </c>
-      <c r="H57" s="128"/>
+      <c r="H57" s="152"/>
       <c r="I57" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="J57" s="128" t="s">
+      <c r="J57" s="152" t="s">
         <v>209</v>
       </c>
-      <c r="K57" s="129"/>
+      <c r="K57" s="153"/>
     </row>
     <row r="58" spans="6:11">
       <c r="F58" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="G58" s="117" t="s">
+      <c r="G58" s="141" t="s">
         <v>227</v>
       </c>
-      <c r="H58" s="118"/>
+      <c r="H58" s="142"/>
       <c r="I58" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="J58" s="117" t="s">
+      <c r="J58" s="141" t="s">
         <v>228</v>
       </c>
-      <c r="K58" s="119"/>
+      <c r="K58" s="143"/>
     </row>
     <row r="59" spans="6:11" ht="16.5" thickBot="1">
       <c r="F59" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="G59" s="120" t="s">
+      <c r="G59" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="H59" s="121"/>
+      <c r="H59" s="145"/>
       <c r="I59" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="J59" s="122" t="s">
+      <c r="J59" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="K59" s="123"/>
+      <c r="K59" s="147"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="70">
+    <mergeCell ref="F49:K49"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F44:AJ44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
@@ -38354,60 +38408,6 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F44:AJ44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="F49:K49"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ35">
@@ -38488,61 +38488,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="153" t="s">
+      <c r="F2" s="122" t="s">
         <v>233</v>
       </c>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="154"/>
-      <c r="P2" s="154"/>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="154"/>
-      <c r="U2" s="154"/>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="154"/>
-      <c r="AE2" s="154"/>
-      <c r="AF2" s="154"/>
-      <c r="AG2" s="154"/>
-      <c r="AH2" s="154"/>
-      <c r="AI2" s="154"/>
-      <c r="AJ2" s="155"/>
-      <c r="AL2" s="150" t="s">
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="123"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
+      <c r="AH2" s="123"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="124"/>
+      <c r="AL2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="150" t="s">
+      <c r="AP2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
       <c r="F3" s="82" t="s">
         <v>88</v>
       </c>
@@ -38636,16 +38636,16 @@
       <c r="AJ3" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
-      <c r="AP3" s="151"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="30">
         <v>1</v>
       </c>
@@ -38739,20 +38739,20 @@
       <c r="AJ4" s="85">
         <v>31</v>
       </c>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
-      <c r="AP4" s="152"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="98">
         <v>1</v>
       </c>
-      <c r="C5" s="137" t="s">
+      <c r="C5" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="138"/>
+      <c r="D5" s="121"/>
       <c r="F5" s="88" t="s">
         <v>103</v>
       </c>
@@ -38871,10 +38871,10 @@
       <c r="B6" s="98">
         <v>2</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="138"/>
+      <c r="D6" s="121"/>
       <c r="F6" s="88" t="s">
         <v>103</v>
       </c>
@@ -38978,10 +38978,10 @@
       <c r="B7" s="98">
         <v>3</v>
       </c>
-      <c r="C7" s="137" t="s">
+      <c r="C7" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="138"/>
+      <c r="D7" s="121"/>
       <c r="F7" s="89" t="s">
         <v>104</v>
       </c>
@@ -39100,10 +39100,10 @@
       <c r="B8" s="98">
         <v>4</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="120" t="s">
         <v>172</v>
       </c>
-      <c r="D8" s="138"/>
+      <c r="D8" s="121"/>
       <c r="F8" s="90" t="s">
         <v>108</v>
       </c>
@@ -39222,10 +39222,10 @@
       <c r="B9" s="98">
         <v>5</v>
       </c>
-      <c r="C9" s="137" t="s">
+      <c r="C9" s="120" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="138"/>
+      <c r="D9" s="121"/>
       <c r="F9" s="90" t="s">
         <v>108</v>
       </c>
@@ -39344,10 +39344,10 @@
       <c r="B10" s="98">
         <v>6</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="138"/>
+      <c r="D10" s="121"/>
       <c r="F10" s="90" t="s">
         <v>98</v>
       </c>
@@ -39466,10 +39466,10 @@
       <c r="B11" s="98">
         <v>7</v>
       </c>
-      <c r="C11" s="137" t="s">
+      <c r="C11" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="138"/>
+      <c r="D11" s="121"/>
       <c r="F11" s="88" t="s">
         <v>98</v>
       </c>
@@ -39588,10 +39588,10 @@
       <c r="B12" s="98">
         <v>8</v>
       </c>
-      <c r="C12" s="137" t="s">
+      <c r="C12" s="120" t="s">
         <v>176</v>
       </c>
-      <c r="D12" s="138"/>
+      <c r="D12" s="121"/>
       <c r="F12" s="88" t="s">
         <v>103</v>
       </c>
@@ -39710,10 +39710,10 @@
       <c r="B13" s="99">
         <v>9</v>
       </c>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="120" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="138"/>
+      <c r="D13" s="121"/>
       <c r="F13" s="88" t="s">
         <v>104</v>
       </c>
@@ -39832,10 +39832,10 @@
       <c r="B14" s="98">
         <v>10</v>
       </c>
-      <c r="C14" s="137" t="s">
+      <c r="C14" s="120" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="138"/>
+      <c r="D14" s="121"/>
       <c r="F14" s="88" t="s">
         <v>104</v>
       </c>
@@ -39954,10 +39954,10 @@
       <c r="B15" s="99">
         <v>11</v>
       </c>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="138"/>
+      <c r="D15" s="121"/>
       <c r="F15" s="89" t="s">
         <v>98</v>
       </c>
@@ -40076,10 +40076,10 @@
       <c r="B16" s="99">
         <v>12</v>
       </c>
-      <c r="C16" s="137" t="s">
+      <c r="C16" s="120" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="138"/>
+      <c r="D16" s="121"/>
       <c r="F16" s="88"/>
       <c r="G16" s="88"/>
       <c r="H16" s="88"/>
@@ -40136,10 +40136,10 @@
       <c r="B17" s="99">
         <v>13</v>
       </c>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="138"/>
+      <c r="D17" s="121"/>
       <c r="F17" s="88" t="s">
         <v>103</v>
       </c>
@@ -40411,10 +40411,10 @@
       <c r="AI19" s="18"/>
     </row>
     <row r="20" spans="2:42" ht="18.75">
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="133" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="143"/>
+      <c r="D20" s="134"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35">
         <f>COUNTIF(F$5:F$16,"M*")</f>
@@ -40542,10 +40542,10 @@
       </c>
     </row>
     <row r="21" spans="2:42" ht="18.75">
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="133" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="143"/>
+      <c r="D21" s="134"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <f>COUNTIF(F$5:F$16,"A*")</f>
@@ -40673,10 +40673,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75">
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="143"/>
+      <c r="D22" s="134"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f>COUNTIF(F$5:F$16,"N*")</f>
@@ -40804,10 +40804,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75">
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="133" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="143"/>
+      <c r="D23" s="134"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35">
         <f t="shared" ref="F23:AJ23" si="8">COUNTIF(F$5:F$18,"O*")</f>
@@ -40935,10 +40935,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75">
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="143"/>
+      <c r="D24" s="134"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35">
         <f t="shared" ref="F24:AJ24" si="9">COUNTIF(F$5:F$18,"TR*")</f>
@@ -41066,10 +41066,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="143"/>
+      <c r="D25" s="134"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f t="shared" ref="F25:AJ25" si="10">COUNTIF(F$5:F$18,"ST*")</f>
@@ -41197,10 +41197,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="140"/>
+      <c r="D26" s="139"/>
       <c r="E26" s="36"/>
       <c r="F26" s="37">
         <f>COUNTIF(F$5:F$18,"OT*")</f>
@@ -41331,43 +41331,43 @@
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="141"/>
-      <c r="Q27" s="141"/>
-      <c r="R27" s="141"/>
-      <c r="S27" s="141"/>
-      <c r="T27" s="141"/>
-      <c r="U27" s="141"/>
-      <c r="V27" s="141"/>
-      <c r="W27" s="141"/>
-      <c r="X27" s="141"/>
-      <c r="Y27" s="141"/>
-      <c r="Z27" s="141"/>
-      <c r="AA27" s="141"/>
-      <c r="AB27" s="141"/>
-      <c r="AC27" s="141"/>
-      <c r="AD27" s="141"/>
-      <c r="AE27" s="141"/>
-      <c r="AF27" s="141"/>
-      <c r="AG27" s="141"/>
-      <c r="AH27" s="141"/>
-      <c r="AI27" s="141"/>
-      <c r="AJ27" s="141"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="140"/>
+      <c r="O27" s="140"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="140"/>
+      <c r="R27" s="140"/>
+      <c r="S27" s="140"/>
+      <c r="T27" s="140"/>
+      <c r="U27" s="140"/>
+      <c r="V27" s="140"/>
+      <c r="W27" s="140"/>
+      <c r="X27" s="140"/>
+      <c r="Y27" s="140"/>
+      <c r="Z27" s="140"/>
+      <c r="AA27" s="140"/>
+      <c r="AB27" s="140"/>
+      <c r="AC27" s="140"/>
+      <c r="AD27" s="140"/>
+      <c r="AE27" s="140"/>
+      <c r="AF27" s="140"/>
+      <c r="AG27" s="140"/>
+      <c r="AH27" s="140"/>
+      <c r="AI27" s="140"/>
+      <c r="AJ27" s="140"/>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="142" t="s">
+      <c r="C28" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="143"/>
+      <c r="D28" s="134"/>
       <c r="E28" s="34"/>
       <c r="F28" s="39">
         <f>SUM(F20:F22)</f>
@@ -41495,10 +41495,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="143"/>
+      <c r="D29" s="134"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <v>9</v>
@@ -41595,10 +41595,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="142" t="s">
+      <c r="C30" s="133" t="s">
         <v>190</v>
       </c>
-      <c r="D30" s="143"/>
+      <c r="D30" s="134"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f>SUM(F20,F21,F22,F23,F25)</f>
@@ -41727,188 +41727,203 @@
     </row>
     <row r="31" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="32" spans="2:42" ht="16.5" thickBot="1">
-      <c r="F32" s="144" t="s">
+      <c r="F32" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="145"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="146"/>
+      <c r="G32" s="127"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="127"/>
+      <c r="K32" s="128"/>
     </row>
     <row r="33" spans="6:11">
       <c r="F33" s="100" t="s">
         <v>192</v>
       </c>
-      <c r="G33" s="135" t="s">
+      <c r="G33" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H33" s="135"/>
+      <c r="H33" s="137"/>
       <c r="I33" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="J33" s="147" t="s">
+      <c r="J33" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="K33" s="148"/>
+      <c r="K33" s="130"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G34" s="136" t="s">
+      <c r="G34" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H34" s="136"/>
+      <c r="H34" s="131"/>
       <c r="I34" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="J34" s="136" t="s">
+      <c r="J34" s="131" t="s">
         <v>217</v>
       </c>
-      <c r="K34" s="149"/>
+      <c r="K34" s="132"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="G35" s="133" t="s">
+      <c r="G35" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="H35" s="133"/>
+      <c r="H35" s="135"/>
       <c r="I35" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="J35" s="133" t="s">
+      <c r="J35" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="K35" s="134"/>
+      <c r="K35" s="136"/>
     </row>
     <row r="36" spans="6:11">
       <c r="F36" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="G36" s="130" t="s">
+      <c r="G36" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="H36" s="130"/>
+      <c r="H36" s="154"/>
       <c r="I36" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="J36" s="124" t="s">
+      <c r="J36" s="148" t="s">
         <v>223</v>
       </c>
-      <c r="K36" s="125"/>
+      <c r="K36" s="149"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="G37" s="130" t="s">
+      <c r="G37" s="154" t="s">
         <v>224</v>
       </c>
-      <c r="H37" s="130"/>
+      <c r="H37" s="154"/>
       <c r="I37" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="J37" s="126" t="s">
+      <c r="J37" s="150" t="s">
         <v>202</v>
       </c>
-      <c r="K37" s="127"/>
+      <c r="K37" s="151"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="131" t="s">
+      <c r="G38" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="H38" s="131"/>
+      <c r="H38" s="155"/>
       <c r="I38" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J38" s="126" t="s">
+      <c r="J38" s="150" t="s">
         <v>204</v>
       </c>
-      <c r="K38" s="127"/>
+      <c r="K38" s="151"/>
     </row>
     <row r="39" spans="6:11">
       <c r="F39" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="G39" s="132" t="s">
+      <c r="G39" s="156" t="s">
         <v>205</v>
       </c>
-      <c r="H39" s="132"/>
+      <c r="H39" s="156"/>
       <c r="I39" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J39" s="126" t="s">
+      <c r="J39" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="K39" s="127"/>
+      <c r="K39" s="151"/>
     </row>
     <row r="40" spans="6:11">
       <c r="F40" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="G40" s="128" t="s">
+      <c r="G40" s="152" t="s">
         <v>208</v>
       </c>
-      <c r="H40" s="128"/>
+      <c r="H40" s="152"/>
       <c r="I40" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="J40" s="128" t="s">
+      <c r="J40" s="152" t="s">
         <v>209</v>
       </c>
-      <c r="K40" s="129"/>
+      <c r="K40" s="153"/>
     </row>
     <row r="41" spans="6:11">
       <c r="F41" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="117" t="s">
+      <c r="G41" s="141" t="s">
         <v>227</v>
       </c>
-      <c r="H41" s="118"/>
+      <c r="H41" s="142"/>
       <c r="I41" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="J41" s="117" t="s">
+      <c r="J41" s="141" t="s">
         <v>228</v>
       </c>
-      <c r="K41" s="119"/>
+      <c r="K41" s="143"/>
     </row>
     <row r="42" spans="6:11" ht="16.5" thickBot="1">
       <c r="F42" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="G42" s="120" t="s">
+      <c r="G42" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="H42" s="121"/>
+      <c r="H42" s="145"/>
       <c r="I42" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="J42" s="122" t="s">
+      <c r="J42" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="K42" s="123"/>
+      <c r="K42" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F27:AJ27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F32:K32"/>
@@ -41924,32 +41939,17 @@
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F27:AJ27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AO2:AO4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ18">
@@ -42050,19 +42050,19 @@
       <c r="AG2" s="241"/>
       <c r="AH2" s="241"/>
       <c r="AI2" s="241"/>
-      <c r="AK2" s="150" t="s">
+      <c r="AK2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="150" t="s">
+      <c r="AL2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" s="150" t="s">
+      <c r="AM2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AN2" s="150" t="s">
+      <c r="AN2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="150" t="s">
+      <c r="AO2" s="117" t="s">
         <v>84</v>
       </c>
     </row>
@@ -42162,11 +42162,11 @@
         <v>86</v>
       </c>
       <c r="AI3" s="29"/>
-      <c r="AK3" s="151"/>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="151"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
     </row>
     <row r="4" spans="2:41" ht="19.5" thickBot="1">
       <c r="B4" s="244"/>
@@ -42262,11 +42262,11 @@
         <v>30</v>
       </c>
       <c r="AI4" s="33"/>
-      <c r="AK4" s="152"/>
-      <c r="AL4" s="152"/>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
     </row>
     <row r="5" spans="2:41" ht="18.75">
       <c r="B5" s="240" t="s">
@@ -43590,10 +43590,10 @@
       <c r="AH16" s="18"/>
     </row>
     <row r="17" spans="2:35" ht="18.75">
-      <c r="B17" s="181" t="s">
+      <c r="B17" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="181"/>
+      <c r="C17" s="199"/>
       <c r="D17" s="34"/>
       <c r="E17" s="35">
         <f t="shared" ref="E17:AH17" si="5">COUNTIF(E$5:E$15,"M*")</f>
@@ -43720,10 +43720,10 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="18.75">
-      <c r="B18" s="181" t="s">
+      <c r="B18" s="199" t="s">
         <v>184</v>
       </c>
-      <c r="C18" s="181"/>
+      <c r="C18" s="199"/>
       <c r="D18" s="34"/>
       <c r="E18" s="35">
         <f t="shared" ref="E18:AH18" si="6">COUNTIF(E$5:E$15,"A*")</f>
@@ -43850,10 +43850,10 @@
       </c>
     </row>
     <row r="19" spans="2:35" ht="18.75">
-      <c r="B19" s="181" t="s">
+      <c r="B19" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="181"/>
+      <c r="C19" s="199"/>
       <c r="D19" s="34"/>
       <c r="E19" s="35">
         <f t="shared" ref="E19:AH19" si="7">COUNTIF(E$5:E$15,"N*")</f>
@@ -43980,10 +43980,10 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="18.75">
-      <c r="B20" s="181" t="s">
+      <c r="B20" s="199" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="181"/>
+      <c r="C20" s="199"/>
       <c r="D20" s="34"/>
       <c r="E20" s="35">
         <f t="shared" ref="E20:AH20" si="8">COUNTIF(E$5:E$15,"O*")</f>
@@ -44110,10 +44110,10 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="18.75">
-      <c r="B21" s="142" t="s">
+      <c r="B21" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="143"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="34"/>
       <c r="E21" s="35">
         <f t="shared" ref="E21:AH21" si="9">COUNTIF(E$5:E$15,"ST*")</f>
@@ -44240,10 +44240,10 @@
       </c>
     </row>
     <row r="22" spans="2:35" ht="18.75">
-      <c r="B22" s="180" t="s">
+      <c r="B22" s="198" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="180"/>
+      <c r="C22" s="198"/>
       <c r="D22" s="36"/>
       <c r="E22" s="37">
         <f>E24-E25</f>
@@ -44373,43 +44373,43 @@
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
       <c r="D23" s="34"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="141"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="141"/>
-      <c r="L23" s="141"/>
-      <c r="M23" s="141"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="141"/>
-      <c r="P23" s="141"/>
-      <c r="Q23" s="141"/>
-      <c r="R23" s="141"/>
-      <c r="S23" s="141"/>
-      <c r="T23" s="141"/>
-      <c r="U23" s="141"/>
-      <c r="V23" s="141"/>
-      <c r="W23" s="141"/>
-      <c r="X23" s="141"/>
-      <c r="Y23" s="141"/>
-      <c r="Z23" s="141"/>
-      <c r="AA23" s="141"/>
-      <c r="AB23" s="141"/>
-      <c r="AC23" s="141"/>
-      <c r="AD23" s="141"/>
-      <c r="AE23" s="141"/>
-      <c r="AF23" s="141"/>
-      <c r="AG23" s="141"/>
-      <c r="AH23" s="141"/>
-      <c r="AI23" s="141"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="140"/>
+      <c r="N23" s="140"/>
+      <c r="O23" s="140"/>
+      <c r="P23" s="140"/>
+      <c r="Q23" s="140"/>
+      <c r="R23" s="140"/>
+      <c r="S23" s="140"/>
+      <c r="T23" s="140"/>
+      <c r="U23" s="140"/>
+      <c r="V23" s="140"/>
+      <c r="W23" s="140"/>
+      <c r="X23" s="140"/>
+      <c r="Y23" s="140"/>
+      <c r="Z23" s="140"/>
+      <c r="AA23" s="140"/>
+      <c r="AB23" s="140"/>
+      <c r="AC23" s="140"/>
+      <c r="AD23" s="140"/>
+      <c r="AE23" s="140"/>
+      <c r="AF23" s="140"/>
+      <c r="AG23" s="140"/>
+      <c r="AH23" s="140"/>
+      <c r="AI23" s="140"/>
     </row>
     <row r="24" spans="2:35" ht="18.75">
-      <c r="B24" s="181" t="s">
+      <c r="B24" s="199" t="s">
         <v>188</v>
       </c>
-      <c r="C24" s="181"/>
+      <c r="C24" s="199"/>
       <c r="D24" s="34"/>
       <c r="E24" s="39">
         <f>SUM(E17:E19)</f>
@@ -44536,10 +44536,10 @@
       </c>
     </row>
     <row r="25" spans="2:35" ht="18.75">
-      <c r="B25" s="181" t="s">
+      <c r="B25" s="199" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="181"/>
+      <c r="C25" s="199"/>
       <c r="D25" s="34"/>
       <c r="E25" s="35">
         <v>7</v>
@@ -44636,10 +44636,10 @@
       </c>
     </row>
     <row r="26" spans="2:35" ht="18.75">
-      <c r="B26" s="181" t="s">
+      <c r="B26" s="199" t="s">
         <v>190</v>
       </c>
-      <c r="C26" s="181"/>
+      <c r="C26" s="199"/>
       <c r="D26" s="34"/>
       <c r="E26" s="35">
         <v>11</v>
@@ -44737,6 +44737,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
     <mergeCell ref="B9:C9"/>
@@ -44749,22 +44765,6 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
     <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="STN">
@@ -44917,6 +44917,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="مستند" ma:contentTypeID="0x01010053585A714B17B949862FA1B71BD97610" ma:contentTypeVersion="21" ma:contentTypeDescription="إنشاء مستند جديد." ma:contentTypeScope="" ma:versionID="26eaa5d39eda60f8775bd022d70769f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="f1e9c892-1499-41bb-8a64-60ef909d8682" xmlns:ns4="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c2899f3b08a11c7878800e445033e12" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -45192,16 +45202,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -45212,11 +45212,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBA6F5DD-99D5-4C0F-817B-85F132A9EB4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBA6F5DD-99D5-4C0F-817B-85F132A9EB4D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/rosters/.versions/2026-10/previous.xlsx
+++ b/rosters/.versions/2026-10/previous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\80235\OneDrive - Oman Air\Desktop\Rosters\STAFF OPERATION SCHEDULE\Roster 5 x 3\2026\OPS\10 October 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40008CBF-61AE-48EB-9D54-B1BB89EB89BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE87734E-B5A9-4CF5-9F13-95385DBC9D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <author>Rodolfo C Magcaling</author>
   </authors>
   <commentList>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{E5B95F7E-7FE7-4ACA-8105-3771BA8AEFAC}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{1FB28473-83AC-48A2-A25E-A048AD3569B5}">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{C76FBE1B-49BF-44BE-98A6-6A88BCF213BF}">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{0D642D8A-0622-478C-AA8C-26138A21D067}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{EE90E9F6-FADB-4B65-9658-182404D53C6A}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{5B8D31DC-1978-43D5-851A-74B929C76278}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{626C6050-1C54-4CDD-BC3D-8DE96D9B9350}">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{5D9C2106-0605-46FB-9B70-32714C1F0A3B}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{41EFAABE-0D91-4B7A-AD01-625808329262}">
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{29A2C595-8BB3-476B-AC86-BE2F510163C4}">
       <text>
         <r>
           <rPr>
@@ -180,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W7" authorId="0" shapeId="0" xr:uid="{4F02542B-1375-466B-A28D-EAF15E38E4BA}">
+    <comment ref="W7" authorId="0" shapeId="0" xr:uid="{3130FC4A-4921-40ED-B1AC-EF7A819F140C}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0" xr:uid="{5A9D05C2-B47D-4738-A9A1-20CADBEA6A31}">
+    <comment ref="X7" authorId="0" shapeId="0" xr:uid="{DC009075-5C75-4A7A-AD1C-DC9B02CACAB3}">
       <text>
         <r>
           <rPr>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD7" authorId="0" shapeId="0" xr:uid="{2E2B34CD-59E9-4DDA-84A4-D778D7011FD5}">
+    <comment ref="AD7" authorId="0" shapeId="0" xr:uid="{E5DDB41D-8779-4077-9246-8115C9DEF48C}">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{44B63640-5BC8-4F7F-9692-32D1BA16875C}">
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{B8E4DBA2-ACF5-4663-BCCF-6031BF5BBDE7}">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y8" authorId="0" shapeId="0" xr:uid="{E91E56F6-37BF-4ECC-916C-CC51C3D6F426}">
+    <comment ref="Y8" authorId="0" shapeId="0" xr:uid="{530699A9-0A13-480D-848E-D8FC58CE7329}">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{75A7E804-CE42-47DF-91BA-56842D688ABE}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{84CBB52C-F61F-4D5C-86E2-593BA5229401}">
       <text>
         <r>
           <rPr>
@@ -324,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P9" authorId="0" shapeId="0" xr:uid="{38EC3420-AB56-4267-A1B8-4FFA1F8C884D}">
+    <comment ref="P9" authorId="0" shapeId="0" xr:uid="{9E0C0A75-4DA1-45A8-AE64-FF115422110A}">
       <text>
         <r>
           <rPr>
@@ -348,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH13" authorId="0" shapeId="0" xr:uid="{89904727-D895-4B94-A30B-E8A850D0B7AD}">
+    <comment ref="AH13" authorId="0" shapeId="0" xr:uid="{A5C5D7C8-F494-40D6-9E08-721AB2B7472A}">
       <text>
         <r>
           <rPr>
@@ -372,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{056A3FAB-8F7F-470D-B7E5-D4B02D1C1C1E}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{575C54EE-BD0B-45C2-BAC2-5BA9FF09213E}">
       <text>
         <r>
           <rPr>
@@ -396,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{C7DEA02F-FFFB-4B91-880F-D320A6EDD8A5}">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{937B14A7-64C0-4DCC-A90E-BEA18C74A651}">
       <text>
         <r>
           <rPr>
@@ -420,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O15" authorId="0" shapeId="0" xr:uid="{84360FE1-84C8-48C5-91B5-37393F324F62}">
+    <comment ref="O15" authorId="0" shapeId="0" xr:uid="{800B12B5-4288-4608-9266-7416B396A3EB}">
       <text>
         <r>
           <rPr>
@@ -444,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="0" shapeId="0" xr:uid="{E612757E-32BA-4D8B-9725-027033107ABB}">
+    <comment ref="P15" authorId="0" shapeId="0" xr:uid="{9E294EB2-635D-43A0-8E8B-27DB10752DB2}">
       <text>
         <r>
           <rPr>
@@ -468,7 +468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0" xr:uid="{DB24E70C-C870-4CF2-A121-13A6CA089124}">
+    <comment ref="Q15" authorId="0" shapeId="0" xr:uid="{1655273A-2102-4B41-9A84-C888C6AC4E6D}">
       <text>
         <r>
           <rPr>
@@ -492,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD15" authorId="0" shapeId="0" xr:uid="{2853906F-23D2-4893-BDF8-15B652FAC93E}">
+    <comment ref="AD15" authorId="0" shapeId="0" xr:uid="{2CDAF01C-3F91-4AC7-865D-34CB334F0BD6}">
       <text>
         <r>
           <rPr>
@@ -516,7 +516,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE15" authorId="0" shapeId="0" xr:uid="{361AC406-19E9-4611-A134-8DD7931BB638}">
+    <comment ref="AE15" authorId="0" shapeId="0" xr:uid="{ED616A99-EC43-4D15-BB5E-6B1665D9FDC8}">
       <text>
         <r>
           <rPr>
@@ -540,7 +540,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF15" authorId="0" shapeId="0" xr:uid="{57698312-09A2-4AB6-AA7E-82ED436AA765}">
+    <comment ref="AF15" authorId="0" shapeId="0" xr:uid="{EE2D1A3E-85EA-46D8-B83F-C3921C34D4FD}">
       <text>
         <r>
           <rPr>
@@ -564,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG15" authorId="0" shapeId="0" xr:uid="{20C7CB2F-6038-4E4A-A86A-2ED95412F670}">
+    <comment ref="AG15" authorId="0" shapeId="0" xr:uid="{C2458652-20F6-4853-9ADD-605E1FC8B97C}">
       <text>
         <r>
           <rPr>
@@ -588,7 +588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH15" authorId="0" shapeId="0" xr:uid="{0DDC0084-0558-4450-B845-2DC9ECEE5117}">
+    <comment ref="AH15" authorId="0" shapeId="0" xr:uid="{8E8CDA36-692E-4292-B131-ED306D9C3B77}">
       <text>
         <r>
           <rPr>
@@ -612,7 +612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{D44F74D3-76D7-4DD5-9133-F8987472AE02}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{4B4D59D3-14A5-45D6-A267-EFDDB7709A61}">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0" xr:uid="{74EC443E-B71E-4F27-BE50-17BB54BACB2C}">
+    <comment ref="P20" authorId="0" shapeId="0" xr:uid="{05E2A9D8-387C-4E0B-8F74-174BD4E1D38D}">
       <text>
         <r>
           <rPr>
@@ -660,7 +660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q20" authorId="0" shapeId="0" xr:uid="{88E572D0-0630-4CC7-AED6-3270D3C7CB1F}">
+    <comment ref="Q20" authorId="0" shapeId="0" xr:uid="{37766D7C-0DF8-4459-B117-3039EB518999}">
       <text>
         <r>
           <rPr>
@@ -684,7 +684,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{647F29C4-421E-4838-86C6-50CA94E9D344}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{49BED592-2D84-421E-A3D9-46F5F45FE501}">
       <text>
         <r>
           <rPr>
@@ -708,7 +708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P22" authorId="0" shapeId="0" xr:uid="{484FC985-157F-40EF-984F-0CF56AC3A63E}">
+    <comment ref="P22" authorId="0" shapeId="0" xr:uid="{5580DE47-442D-43E3-AC72-7A5F00217F18}">
       <text>
         <r>
           <rPr>
@@ -732,7 +732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{CBC37A8E-57B2-4F30-BC1E-A96B6B0227A6}">
+    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{A469C8AC-3BBD-490A-B9B8-490D5600D15E}">
       <text>
         <r>
           <rPr>
@@ -756,7 +756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG23" authorId="0" shapeId="0" xr:uid="{4CB0431C-F6DF-4F83-AB44-DD4EB279B51A}">
+    <comment ref="AG23" authorId="0" shapeId="0" xr:uid="{A744EC60-B16D-4E5D-895F-397B9333F093}">
       <text>
         <r>
           <rPr>
@@ -780,7 +780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T24" authorId="0" shapeId="0" xr:uid="{5CCC2C69-2425-415E-A5FA-1B8354FDAF77}">
+    <comment ref="T24" authorId="0" shapeId="0" xr:uid="{65AB467B-BD21-4524-80CC-AC98721DC81C}">
       <text>
         <r>
           <rPr>
@@ -804,7 +804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L25" authorId="0" shapeId="0" xr:uid="{370550EA-ADF1-4935-B023-5B2673BC021D}">
+    <comment ref="L25" authorId="0" shapeId="0" xr:uid="{0A9CD046-3B9B-4C6A-B597-1734D3072487}">
       <text>
         <r>
           <rPr>
@@ -828,7 +828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T26" authorId="0" shapeId="0" xr:uid="{65EB856C-66D9-4718-9A51-EA6E805E3080}">
+    <comment ref="T26" authorId="0" shapeId="0" xr:uid="{A512605E-6755-474C-AC67-C9DEA87443D1}">
       <text>
         <r>
           <rPr>
@@ -852,7 +852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{07316C2C-7B44-420B-B548-2E29612E18AB}">
+    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{4B5007DE-6D81-47AF-9747-3C25BEE94DB2}">
       <text>
         <r>
           <rPr>
@@ -876,7 +876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R28" authorId="0" shapeId="0" xr:uid="{CBEAE7AF-EF06-4369-8EE3-A2EE7DC488C0}">
+    <comment ref="R28" authorId="0" shapeId="0" xr:uid="{BE4472CC-C5DA-4736-B1DD-88A7864E302D}">
       <text>
         <r>
           <rPr>
@@ -900,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0" xr:uid="{7A874946-268D-4591-84AE-8B7E69C85A3F}">
+    <comment ref="S28" authorId="0" shapeId="0" xr:uid="{99897B9B-20A0-48BE-97C8-0DD576046EA0}">
       <text>
         <r>
           <rPr>
@@ -924,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH28" authorId="0" shapeId="0" xr:uid="{9B33E08C-C233-40AD-AEAE-9353B401B8E8}">
+    <comment ref="AH28" authorId="0" shapeId="0" xr:uid="{132C8BC0-ACDD-4273-8F0E-94A2DA2102AB}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P30" authorId="0" shapeId="0" xr:uid="{4DC1D242-CE13-48DC-B40E-3AC77BFA48C7}">
+    <comment ref="P30" authorId="0" shapeId="0" xr:uid="{580913E6-520B-40CC-BCE0-2EDC88626641}">
       <text>
         <r>
           <rPr>
@@ -972,7 +972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{3B1332DF-95CC-4863-B51D-5625BF08C8C3}">
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{586E0B95-E8FF-4A4D-A602-CDE396BE55E1}">
       <text>
         <r>
           <rPr>
@@ -996,7 +996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{406A13A2-60A9-404B-8356-577C93222FAF}">
+    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{3BAACA3D-0D03-49C4-AD10-2220943078DC}">
       <text>
         <r>
           <rPr>
@@ -1020,7 +1020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K38" authorId="0" shapeId="0" xr:uid="{F5413401-D99A-4264-AB93-D96D53809A6F}">
+    <comment ref="K38" authorId="0" shapeId="0" xr:uid="{9D1FE4D1-E439-4D70-AC82-F90716B35905}">
       <text>
         <r>
           <rPr>
@@ -1044,7 +1044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M41" authorId="0" shapeId="0" xr:uid="{14421B94-B268-4240-8EA0-77BA9E6A3EC4}">
+    <comment ref="M41" authorId="0" shapeId="0" xr:uid="{4BAF1E7A-84E7-4F62-A070-4649FA58B06B}">
       <text>
         <r>
           <rPr>
@@ -1068,7 +1068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P41" authorId="0" shapeId="0" xr:uid="{715D1387-E90F-4527-A1A2-E18C1B6C809D}">
+    <comment ref="P41" authorId="0" shapeId="0" xr:uid="{17DC3F4C-EC7A-4F52-AFEF-8FE24F4EDB88}">
       <text>
         <r>
           <rPr>
@@ -1092,7 +1092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG42" authorId="0" shapeId="0" xr:uid="{B12D28E6-2AB5-4211-A1A9-6C9BF6D0BD69}">
+    <comment ref="AG42" authorId="0" shapeId="0" xr:uid="{4D701E8F-AF03-48B5-9A55-07AACCC0D32E}">
       <text>
         <r>
           <rPr>
@@ -1116,7 +1116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T43" authorId="0" shapeId="0" xr:uid="{D78C45C7-51B1-48D7-A14E-B86D53EA7CCE}">
+    <comment ref="T43" authorId="0" shapeId="0" xr:uid="{0F479FEF-DACC-43D5-AC76-96BD6459DBB8}">
       <text>
         <r>
           <rPr>
@@ -1140,7 +1140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X47" authorId="0" shapeId="0" xr:uid="{F947DF51-2292-411A-B44F-1E6505E4F896}">
+    <comment ref="X47" authorId="0" shapeId="0" xr:uid="{91A3640B-3268-4E40-B6CD-5903DCEC98B5}">
       <text>
         <r>
           <rPr>
@@ -1164,7 +1164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE49" authorId="0" shapeId="0" xr:uid="{21C9BABE-6AB3-4E97-B6B1-3CF18D0A28CB}">
+    <comment ref="AE49" authorId="0" shapeId="0" xr:uid="{EE148A49-EDC4-4ECF-B360-BC43A0A61D40}">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T51" authorId="0" shapeId="0" xr:uid="{399AA536-F6B8-4156-9C16-04E48A6CCA29}">
+    <comment ref="T51" authorId="0" shapeId="0" xr:uid="{3B8ADE25-70FA-4C89-8BE9-B06FECFE90F0}">
       <text>
         <r>
           <rPr>
@@ -1212,7 +1212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA51" authorId="0" shapeId="0" xr:uid="{27C9FA1A-D397-49B7-AB6C-622E77ACC420}">
+    <comment ref="AA51" authorId="0" shapeId="0" xr:uid="{E3779567-82A2-4321-96CD-DCED25C76D65}">
       <text>
         <r>
           <rPr>
@@ -1236,7 +1236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG51" authorId="0" shapeId="0" xr:uid="{0EF371DB-DA66-478C-98BA-09C3D94EFAF5}">
+    <comment ref="AG51" authorId="0" shapeId="0" xr:uid="{406FC0E1-72FE-4E8B-A094-F17785E01D95}">
       <text>
         <r>
           <rPr>
@@ -1260,7 +1260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA56" authorId="0" shapeId="0" xr:uid="{5D054998-DBC6-4FD5-B587-FB9B62A9DD98}">
+    <comment ref="AA56" authorId="0" shapeId="0" xr:uid="{3877DDEB-2D6E-4916-8E28-A2E12B91E95E}">
       <text>
         <r>
           <rPr>
@@ -1284,7 +1284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH56" authorId="0" shapeId="0" xr:uid="{78E4F77A-28AB-4B9E-A6F0-DEE122D525F7}">
+    <comment ref="AH56" authorId="0" shapeId="0" xr:uid="{AE24A25E-E2A4-4A8D-9C02-F0F9F4E3E58E}">
       <text>
         <r>
           <rPr>
@@ -1308,7 +1308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L57" authorId="0" shapeId="0" xr:uid="{1205396F-7D8E-46A4-9A2D-D5D84C51F268}">
+    <comment ref="L57" authorId="0" shapeId="0" xr:uid="{F21347E5-25D3-4ED1-B8F4-9D39073B745C}">
       <text>
         <r>
           <rPr>
@@ -1332,7 +1332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K59" authorId="0" shapeId="0" xr:uid="{5F1116E2-5ED4-477A-A53F-32DE835FD13E}">
+    <comment ref="K59" authorId="0" shapeId="0" xr:uid="{8CC2DE01-76BF-4973-B8C4-1D02BA6CCD67}">
       <text>
         <r>
           <rPr>
@@ -1356,7 +1356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH59" authorId="0" shapeId="0" xr:uid="{449349D3-EE15-479F-A7E5-7E3475E65328}">
+    <comment ref="AH59" authorId="0" shapeId="0" xr:uid="{D532CE5B-20A9-453E-BD0A-8016CD46219D}">
       <text>
         <r>
           <rPr>
@@ -1380,7 +1380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M60" authorId="0" shapeId="0" xr:uid="{B6E51678-F58F-4EC5-BD36-ABB7926E4EB4}">
+    <comment ref="M60" authorId="0" shapeId="0" xr:uid="{0700576D-B558-412F-BB27-143C7D348A29}">
       <text>
         <r>
           <rPr>
@@ -1404,7 +1404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L63" authorId="0" shapeId="0" xr:uid="{DE335AB0-FD60-4A1F-B9ED-9B8389E834A2}">
+    <comment ref="L63" authorId="0" shapeId="0" xr:uid="{DCE16F0E-4B2F-4BC7-8A25-8FC1C481B112}">
       <text>
         <r>
           <rPr>
@@ -1428,7 +1428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S64" authorId="0" shapeId="0" xr:uid="{3546162E-8DE2-4590-A9AB-EAE25A00001E}">
+    <comment ref="S64" authorId="0" shapeId="0" xr:uid="{FEE8C6CB-83B7-4A68-A1E5-452D902CB7D0}">
       <text>
         <r>
           <rPr>
@@ -1452,7 +1452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M65" authorId="0" shapeId="0" xr:uid="{D693CB87-1C45-4839-A2FC-7AA291A33368}">
+    <comment ref="M65" authorId="0" shapeId="0" xr:uid="{8B728466-C03D-42AB-B275-DEA9EAB4F488}">
       <text>
         <r>
           <rPr>
@@ -1476,7 +1476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{66C697F9-137F-4F58-902C-90AB817B0F83}">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{B135192E-4998-4DEA-8B6D-B40023EEAF03}">
       <text>
         <r>
           <rPr>
@@ -1500,7 +1500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M70" authorId="0" shapeId="0" xr:uid="{DABE30CE-43BD-4C52-A81A-445BFC31152B}">
+    <comment ref="M70" authorId="0" shapeId="0" xr:uid="{EF3E1E24-6BE8-46DB-883B-1884DD1A24AE}">
       <text>
         <r>
           <rPr>
@@ -1524,7 +1524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X74" authorId="0" shapeId="0" xr:uid="{35953405-B476-47E8-A0D8-74E2329218AC}">
+    <comment ref="X74" authorId="0" shapeId="0" xr:uid="{177E5F48-EC67-4D90-B9BD-DC051FE1352F}">
       <text>
         <r>
           <rPr>
@@ -5144,7 +5144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5907,11 +5907,1623 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="340">
+  <dxfs count="528">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -14835,26 +16447,26 @@
     <mergeCell ref="AC2:AF2"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
-    <cfRule type="expression" dxfId="339" priority="4">
+    <cfRule type="expression" dxfId="527" priority="4">
       <formula>LEFT(E8,1)="N"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="338" priority="5">
+    <cfRule type="expression" dxfId="526" priority="5">
       <formula>LEFT(E8,1)="A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="337" priority="7">
+    <cfRule type="expression" dxfId="525" priority="7">
       <formula>LEFT(E8,1)="M"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="336" priority="8">
+    <cfRule type="expression" dxfId="524" priority="8">
       <formula>LEFT(E8,1)="D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42 E8:AI37 AK8:AN37">
-    <cfRule type="expression" dxfId="335" priority="3">
+    <cfRule type="expression" dxfId="523" priority="3">
       <formula>LEFT(E8,1)="O"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42">
-    <cfRule type="expression" dxfId="334" priority="1">
+    <cfRule type="expression" dxfId="522" priority="1">
       <formula>ISEVEN(ROW($E39))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15549,19 +17161,19 @@
         <v>219</v>
       </c>
       <c r="R8" s="128" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="S8" s="128" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="T8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="U8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="V8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="W8" s="128" t="s">
         <v>219</v>
@@ -15611,11 +17223,11 @@
       </c>
       <c r="AM8" s="93">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="93">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO8" s="93">
         <f t="shared" si="3"/>
@@ -16168,28 +17780,28 @@
         <v>253</v>
       </c>
       <c r="U13" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="V13" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="W13" s="49" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="X13" s="49" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="Y13" s="49" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="Z13" s="49" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AA13" s="49" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AB13" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="AC13" s="49" t="s">
         <v>219</v>
@@ -16222,19 +17834,19 @@
       </c>
       <c r="AM13" s="48">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN13" s="48">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO13" s="48">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP13" s="48">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16552,7 +18164,7 @@
         <v>218</v>
       </c>
       <c r="Z16" s="96" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="AA16" s="96" t="s">
         <v>219</v>
@@ -17269,7 +18881,7 @@
         <v>218</v>
       </c>
       <c r="S22" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="T22" s="96" t="s">
         <v>219</v>
@@ -17413,7 +19025,7 @@
         <v>218</v>
       </c>
       <c r="Z23" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="AA23" s="96" t="s">
         <v>219</v>
@@ -18019,22 +19631,22 @@
         <v>219</v>
       </c>
       <c r="W28" s="106" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="X28" s="106" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="Y28" s="106" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="Z28" s="106" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="AA28" s="125" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="AB28" s="106" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="AC28" s="106" t="s">
         <v>219</v>
@@ -18066,19 +19678,19 @@
       </c>
       <c r="AM28" s="48">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN28" s="48">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO28" s="48">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP28" s="48">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -18889,19 +20501,19 @@
         <v>194</v>
       </c>
       <c r="AB35" s="96" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="AC35" s="96" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="AD35" s="96" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AE35" s="96" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AF35" s="96" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="AG35" s="96" t="s">
         <v>219</v>
@@ -18921,19 +20533,19 @@
       </c>
       <c r="AM35" s="48">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN35" s="48">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO35" s="48">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AP35" s="48">
         <f t="shared" si="19"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -19432,52 +21044,52 @@
         <v>139</v>
       </c>
       <c r="D40" s="146"/>
-      <c r="F40" s="96" t="s">
+      <c r="F40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="96" t="s">
+      <c r="G40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="H40" s="96" t="s">
+      <c r="H40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="I40" s="96" t="s">
+      <c r="I40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="J40" s="96" t="s">
+      <c r="J40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="K40" s="96" t="s">
+      <c r="K40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="L40" s="96" t="s">
+      <c r="L40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="M40" s="96" t="s">
+      <c r="M40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="N40" s="96" t="s">
+      <c r="N40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="O40" s="96" t="s">
+      <c r="O40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="P40" s="96" t="s">
+      <c r="P40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="Q40" s="96" t="s">
+      <c r="Q40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="R40" s="96" t="s">
+      <c r="R40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="S40" s="96" t="s">
+      <c r="S40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="T40" s="96" t="s">
+      <c r="T40" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="U40" s="96" t="s">
+      <c r="U40" s="268" t="s">
         <v>255</v>
       </c>
       <c r="V40" s="96" t="s">
@@ -19746,10 +21358,10 @@
         <v>194</v>
       </c>
       <c r="AC42" s="96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD42" s="96" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="AE42" s="96" t="s">
         <v>218</v>
@@ -19775,7 +21387,7 @@
       </c>
       <c r="AM42" s="48">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN42" s="48">
         <f t="shared" si="17"/>
@@ -19783,7 +21395,7 @@
       </c>
       <c r="AO42" s="48">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP42" s="48">
         <f t="shared" si="19"/>
@@ -20329,7 +21941,7 @@
         <v>219</v>
       </c>
       <c r="T47" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="U47" s="96" t="s">
         <v>219</v>
@@ -20481,7 +22093,7 @@
         <v>194</v>
       </c>
       <c r="AD48" s="96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE48" s="96" t="s">
         <v>195</v>
@@ -20507,11 +22119,11 @@
       </c>
       <c r="AM48" s="48">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN48" s="48">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO48" s="48">
         <f t="shared" si="18"/>
@@ -22284,7 +23896,7 @@
         <v>195</v>
       </c>
       <c r="AE63" s="96" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="AF63" s="96" t="s">
         <v>218</v>
@@ -22311,7 +23923,7 @@
       </c>
       <c r="AN63" s="48">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO63" s="48">
         <f t="shared" si="18"/>
@@ -22739,7 +24351,7 @@
         <v>218</v>
       </c>
       <c r="T67" s="94" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="U67" s="94" t="s">
         <v>219</v>
@@ -22977,7 +24589,7 @@
         <v>242</v>
       </c>
       <c r="R69" s="95" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="S69" s="96" t="s">
         <v>194</v>
@@ -23102,7 +24714,7 @@
         <v>219</v>
       </c>
       <c r="S70" s="94" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="T70" s="94" t="s">
         <v>194</v>
@@ -23217,20 +24829,20 @@
       <c r="P71" s="96" t="s">
         <v>219</v>
       </c>
-      <c r="Q71" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="R71" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="S71" s="94" t="s">
-        <v>195</v>
-      </c>
-      <c r="T71" s="94" t="s">
-        <v>218</v>
-      </c>
-      <c r="U71" s="95" t="s">
-        <v>218</v>
+      <c r="Q71" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="R71" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="S71" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="T71" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="U71" s="267" t="s">
+        <v>255</v>
       </c>
       <c r="V71" s="96" t="s">
         <v>219</v>
@@ -23283,15 +24895,15 @@
       </c>
       <c r="AM71" s="48">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN71" s="48">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO71" s="48">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP71" s="48">
         <f t="shared" si="19"/>
@@ -23645,7 +25257,7 @@
       </c>
       <c r="AN75" s="48">
         <f t="shared" ref="AN75:AN86" si="22">COUNTIF($F63:$AJ63,"A*")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO75" s="48">
         <f t="shared" ref="AO75:AO86" si="23">COUNTIF($F63:$AJ63,"N*")</f>
@@ -23708,11 +25320,11 @@
       </c>
       <c r="Q76" s="37">
         <f t="shared" si="25"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R76" s="37">
         <f t="shared" si="25"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S76" s="37">
         <f t="shared" si="25"/>
@@ -23752,15 +25364,15 @@
       </c>
       <c r="AB76" s="37">
         <f t="shared" si="25"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC76" s="37">
         <f t="shared" si="25"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD76" s="37">
         <f t="shared" si="25"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE76" s="37">
         <f t="shared" si="25"/>
@@ -23867,7 +25479,7 @@
       </c>
       <c r="S77" s="37">
         <f t="shared" si="26"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T77" s="37">
         <f t="shared" si="26"/>
@@ -23915,7 +25527,7 @@
       </c>
       <c r="AE77" s="37">
         <f t="shared" si="26"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF77" s="37">
         <f t="shared" si="26"/>
@@ -24022,11 +25634,11 @@
       </c>
       <c r="T78" s="37">
         <f t="shared" si="27"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U78" s="37">
         <f t="shared" si="27"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V78" s="37">
         <f t="shared" si="27"/>
@@ -24066,7 +25678,7 @@
       </c>
       <c r="AE78" s="37">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF78" s="37">
         <f t="shared" si="27"/>
@@ -24221,7 +25833,7 @@
       </c>
       <c r="AF79" s="37">
         <f t="shared" si="28"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG79" s="37">
         <f t="shared" si="28"/>
@@ -24618,15 +26230,15 @@
       </c>
       <c r="R82" s="51">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S82" s="51">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T82" s="51">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U82" s="51">
         <f t="shared" si="31"/>
@@ -24754,15 +26366,15 @@
       </c>
       <c r="AM83" s="48">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN83" s="48">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO83" s="48">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP83" s="48">
         <f t="shared" si="24"/>
@@ -24821,23 +26433,23 @@
       </c>
       <c r="Q84" s="41">
         <f t="shared" si="32"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R84" s="41">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S84" s="41">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T84" s="41">
         <f t="shared" si="32"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U84" s="41">
         <f t="shared" si="32"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V84" s="41">
         <f t="shared" si="32"/>
@@ -24865,19 +26477,19 @@
       </c>
       <c r="AB84" s="41">
         <f t="shared" si="32"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC84" s="41">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD84" s="41">
         <f t="shared" si="32"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE84" s="41">
         <f t="shared" si="32"/>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF84" s="41">
         <f t="shared" si="32"/>
@@ -25091,23 +26703,23 @@
       </c>
       <c r="Q86" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R86" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S86" s="37">
         <f t="shared" si="33"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T86" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U86" s="37">
         <f t="shared" si="33"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V86" s="37">
         <f t="shared" si="33"/>
@@ -25135,23 +26747,23 @@
       </c>
       <c r="AB86" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AC86" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD86" s="37">
         <f t="shared" si="33"/>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AE86" s="37">
         <f t="shared" si="33"/>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AF86" s="37">
         <f t="shared" si="33"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG86" s="37">
         <f t="shared" si="33"/>
@@ -26410,19 +28022,19 @@
         <v>219</v>
       </c>
       <c r="R8" s="128" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="S8" s="128" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="T8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="U8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="V8" s="128" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="W8" s="128" t="s">
         <v>219</v>
@@ -26472,11 +28084,11 @@
       </c>
       <c r="AM8" s="48">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="48">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO8" s="48">
         <f t="shared" si="3"/>
@@ -26577,11 +28189,11 @@
       </c>
       <c r="R10" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" s="37">
         <f t="shared" si="5"/>
@@ -26716,15 +28328,15 @@
       </c>
       <c r="T11" s="37">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="37">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="37">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" s="37">
         <f t="shared" si="6"/>
@@ -27363,23 +28975,23 @@
       </c>
       <c r="R16" s="51">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="51">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" s="51">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V16" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W16" s="51">
         <f t="shared" si="11"/>
@@ -27530,23 +29142,23 @@
       </c>
       <c r="R18" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" s="41">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18" s="41">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" s="41">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18" s="41">
         <f t="shared" si="12"/>
@@ -27760,23 +29372,23 @@
       </c>
       <c r="R20" s="37">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20" s="37">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T20" s="37">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U20" s="37">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V20" s="37">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W20" s="37">
         <f t="shared" si="13"/>
@@ -27953,28 +29565,28 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
-    <cfRule type="containsText" dxfId="270" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="458" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="269" priority="2" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="457" priority="2" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="268" priority="3" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="456" priority="3" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="267" priority="4" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="455" priority="4" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="266" priority="5" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="454" priority="5" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="265" priority="7" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="453" priority="7" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="264" priority="10" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="452" priority="10" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="263" priority="11" operator="containsText" text="ME07">
+    <cfRule type="containsText" dxfId="451" priority="11" operator="containsText" text="ME07">
       <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28801,28 +30413,28 @@
         <v>253</v>
       </c>
       <c r="U9" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="V9" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="W9" s="49" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="X9" s="49" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="Y9" s="49" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="Z9" s="49" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AA9" s="49" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AB9" s="49" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="AC9" s="49" t="s">
         <v>219</v>
@@ -28855,19 +30467,19 @@
       </c>
       <c r="AM9" s="48">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN9" s="48">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO9" s="48">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP9" s="48">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -29102,11 +30714,11 @@
       </c>
       <c r="W12" s="37">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" s="37">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="37">
         <f t="shared" si="5"/>
@@ -29241,7 +30853,7 @@
       </c>
       <c r="Y13" s="37">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="37">
         <f t="shared" si="6"/>
@@ -29376,11 +30988,11 @@
       </c>
       <c r="Z14" s="37">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="37">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="37">
         <f t="shared" si="7"/>
@@ -29487,11 +31099,11 @@
       </c>
       <c r="U15" s="37">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15" s="37">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W15" s="37">
         <f t="shared" si="8"/>
@@ -29515,7 +31127,7 @@
       </c>
       <c r="AB15" s="37">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC15" s="37">
         <f t="shared" si="8"/>
@@ -30055,23 +31667,23 @@
       </c>
       <c r="W20" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X20" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="41">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB20" s="41">
         <f t="shared" si="12"/>
@@ -30277,35 +31889,35 @@
       </c>
       <c r="U22" s="37">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22" s="37">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22" s="37">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X22" s="37">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="37">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z22" s="37">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA22" s="37">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB22" s="37">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC22" s="37">
         <f t="shared" si="13"/>
@@ -30560,46 +32172,46 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
-    <cfRule type="containsText" dxfId="262" priority="1" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="450" priority="1" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="261" priority="2" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="449" priority="2" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="260" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="448" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="259" priority="4" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="447" priority="4" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="258" priority="5" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="446" priority="5" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="257" priority="6" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="445" priority="6" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="256" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="444" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="255" priority="8" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="443" priority="8" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="254" priority="9" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="442" priority="9" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="253" priority="10" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="441" priority="10" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="252" priority="11" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="440" priority="11" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="251" priority="12" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="439" priority="12" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="250" priority="13" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="438" priority="13" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="249" priority="14" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="437" priority="14" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31073,7 +32685,7 @@
         <v>218</v>
       </c>
       <c r="Z6" s="96" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="AA6" s="96" t="s">
         <v>219</v>
@@ -31784,7 +33396,7 @@
         <v>218</v>
       </c>
       <c r="S12" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="T12" s="96" t="s">
         <v>219</v>
@@ -31927,7 +33539,7 @@
         <v>218</v>
       </c>
       <c r="Z13" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="AA13" s="96" t="s">
         <v>219</v>
@@ -32528,22 +34140,22 @@
         <v>219</v>
       </c>
       <c r="W18" s="106" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="X18" s="106" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="Y18" s="106" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="Z18" s="106" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="AA18" s="125" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="AB18" s="106" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="AC18" s="106" t="s">
         <v>219</v>
@@ -32575,19 +34187,19 @@
       </c>
       <c r="AM18" s="48">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN18" s="48">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO18" s="48">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP18" s="48">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -32823,11 +34435,11 @@
       </c>
       <c r="W21" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X21" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="37">
         <f t="shared" si="5"/>
@@ -32962,7 +34574,7 @@
       </c>
       <c r="Y22" s="37">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="37">
         <f t="shared" si="6"/>
@@ -33097,11 +34709,11 @@
       </c>
       <c r="Z23" s="37">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA23" s="37">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="37">
         <f t="shared" si="7"/>
@@ -33236,7 +34848,7 @@
       </c>
       <c r="AB24" s="37">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24" s="37">
         <f t="shared" si="8"/>
@@ -33462,7 +35074,7 @@
       </c>
       <c r="S26" s="51">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="51">
         <f t="shared" si="10"/>
@@ -33645,23 +35257,23 @@
       </c>
       <c r="W28" s="41">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28" s="41">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28" s="41">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="41">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="41">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28" s="41">
         <f t="shared" si="11"/>
@@ -33875,27 +35487,27 @@
       </c>
       <c r="W30" s="37">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X30" s="37">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y30" s="37">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z30" s="37">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA30" s="37">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB30" s="37">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC30" s="37">
         <f t="shared" si="12"/>
@@ -34158,46 +35770,46 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
-    <cfRule type="containsText" dxfId="248" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="436" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="247" priority="2" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="435" priority="2" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="434" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="245" priority="5" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="433" priority="5" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="244" priority="6" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="432" priority="6" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="243" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="431" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="242" priority="8" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="430" priority="8" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="241" priority="9" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="429" priority="9" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="240" priority="11" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="428" priority="11" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="239" priority="12" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="427" priority="12" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="238" priority="13" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="426" priority="13" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="237" priority="18" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="425" priority="18" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="236" priority="19" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="424" priority="19" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="235" priority="21" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="423" priority="21" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35168,19 +36780,19 @@
         <v>194</v>
       </c>
       <c r="AB10" s="96" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="AC10" s="96" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="AD10" s="96" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AE10" s="96" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="AF10" s="96" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="AG10" s="96" t="s">
         <v>219</v>
@@ -35200,19 +36812,19 @@
       </c>
       <c r="AM10" s="48">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN10" s="48">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO10" s="48">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AP10" s="48">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -35711,52 +37323,52 @@
         <v>139</v>
       </c>
       <c r="D15" s="146"/>
-      <c r="F15" s="96" t="s">
+      <c r="F15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="G15" s="96" t="s">
+      <c r="G15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="H15" s="96" t="s">
+      <c r="H15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="I15" s="96" t="s">
+      <c r="I15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="J15" s="96" t="s">
+      <c r="J15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="K15" s="96" t="s">
+      <c r="K15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="L15" s="96" t="s">
+      <c r="L15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="M15" s="96" t="s">
+      <c r="M15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="N15" s="96" t="s">
+      <c r="N15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="O15" s="96" t="s">
+      <c r="O15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="P15" s="96" t="s">
+      <c r="P15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="Q15" s="96" t="s">
+      <c r="Q15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="R15" s="96" t="s">
+      <c r="R15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="S15" s="96" t="s">
+      <c r="S15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="T15" s="96" t="s">
+      <c r="T15" s="268" t="s">
         <v>255</v>
       </c>
-      <c r="U15" s="96" t="s">
+      <c r="U15" s="268" t="s">
         <v>255</v>
       </c>
       <c r="V15" s="96" t="s">
@@ -36025,10 +37637,10 @@
         <v>194</v>
       </c>
       <c r="AC17" s="96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD17" s="96" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="AE17" s="96" t="s">
         <v>218</v>
@@ -36054,7 +37666,7 @@
       </c>
       <c r="AM17" s="48">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN17" s="48">
         <f t="shared" si="2"/>
@@ -36062,7 +37674,7 @@
       </c>
       <c r="AO17" s="48">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP17" s="48">
         <f t="shared" si="4"/>
@@ -36608,7 +38220,7 @@
         <v>219</v>
       </c>
       <c r="T22" s="96" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="U22" s="96" t="s">
         <v>219</v>
@@ -36760,7 +38372,7 @@
         <v>194</v>
       </c>
       <c r="AD23" s="96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE23" s="96" t="s">
         <v>195</v>
@@ -36786,11 +38398,11 @@
       </c>
       <c r="AM23" s="48">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN23" s="48">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO23" s="48">
         <f t="shared" si="3"/>
@@ -38395,15 +40007,15 @@
       </c>
       <c r="AB37" s="37">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC37" s="37">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD37" s="37">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE37" s="37">
         <f t="shared" si="5"/>
@@ -38669,7 +40281,7 @@
       </c>
       <c r="AE39" s="37">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF39" s="37">
         <f t="shared" si="7"/>
@@ -38804,7 +40416,7 @@
       </c>
       <c r="AF40" s="37">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG40" s="37">
         <f t="shared" si="8"/>
@@ -39149,7 +40761,7 @@
       </c>
       <c r="T43" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" s="51">
         <f t="shared" si="11"/>
@@ -39348,19 +40960,19 @@
       </c>
       <c r="AB45" s="41">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC45" s="41">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD45" s="41">
         <f t="shared" si="12"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE45" s="41">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF45" s="41">
         <f t="shared" si="12"/>
@@ -39578,23 +41190,23 @@
       </c>
       <c r="AB47" s="37">
         <f t="shared" si="13"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC47" s="37">
         <f t="shared" si="13"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD47" s="37">
         <f t="shared" si="13"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE47" s="37">
         <f t="shared" si="13"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF47" s="37">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG47" s="37">
         <f t="shared" si="13"/>
@@ -39858,58 +41470,58 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ35">
-    <cfRule type="containsText" dxfId="234" priority="1" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="422" priority="1" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="233" priority="2" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="421" priority="2" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="232" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="420" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="231" priority="4" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="419" priority="4" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="230" priority="5" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="418" priority="5" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="229" priority="6" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="417" priority="6" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="228" priority="7" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="416" priority="7" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="227" priority="8" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="415" priority="8" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="226" priority="9" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="414" priority="9" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="225" priority="10" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="413" priority="10" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="224" priority="11" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="412" priority="11" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="223" priority="14" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="411" priority="14" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="15" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="410" priority="15" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="221" priority="16" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="409" priority="16" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="220" priority="17" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="408" priority="17" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="219" priority="18" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="407" priority="18" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="19" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="406" priority="19" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="23" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="405" priority="23" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40505,7 +42117,7 @@
         <v>195</v>
       </c>
       <c r="AE7" s="96" t="s">
-        <v>195</v>
+        <v>253</v>
       </c>
       <c r="AF7" s="96" t="s">
         <v>218</v>
@@ -40532,7 +42144,7 @@
       </c>
       <c r="AN7" s="22">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO7" s="22">
         <f t="shared" si="3"/>
@@ -40960,7 +42572,7 @@
         <v>218</v>
       </c>
       <c r="T11" s="94" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="U11" s="94" t="s">
         <v>219</v>
@@ -41198,7 +42810,7 @@
         <v>242</v>
       </c>
       <c r="R13" s="95" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="S13" s="96" t="s">
         <v>194</v>
@@ -41323,7 +42935,7 @@
         <v>219</v>
       </c>
       <c r="S14" s="94" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="T14" s="94" t="s">
         <v>194</v>
@@ -41438,20 +43050,20 @@
       <c r="P15" s="96" t="s">
         <v>219</v>
       </c>
-      <c r="Q15" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="R15" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="S15" s="94" t="s">
-        <v>195</v>
-      </c>
-      <c r="T15" s="94" t="s">
-        <v>218</v>
-      </c>
-      <c r="U15" s="95" t="s">
-        <v>218</v>
+      <c r="Q15" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="R15" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="S15" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="T15" s="266" t="s">
+        <v>255</v>
+      </c>
+      <c r="U15" s="267" t="s">
+        <v>255</v>
       </c>
       <c r="V15" s="96" t="s">
         <v>219</v>
@@ -41504,15 +43116,15 @@
       </c>
       <c r="AM15" s="22">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN15" s="22">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP15" s="22">
         <f t="shared" si="4"/>
@@ -41909,11 +43521,11 @@
       </c>
       <c r="Q20" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" s="37">
         <f t="shared" si="5"/>
@@ -42048,7 +43660,7 @@
       </c>
       <c r="S21" s="37">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" s="37">
         <f t="shared" si="6"/>
@@ -42096,7 +43708,7 @@
       </c>
       <c r="AE21" s="37">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="37">
         <f t="shared" si="6"/>
@@ -42183,11 +43795,11 @@
       </c>
       <c r="T22" s="37">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" s="37">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="37">
         <f t="shared" si="7"/>
@@ -42699,15 +44311,15 @@
       </c>
       <c r="R26" s="51">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" s="51">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="51">
         <f t="shared" si="11"/>
@@ -42862,23 +44474,23 @@
       </c>
       <c r="Q28" s="41">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R28" s="41">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S28" s="41">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28" s="41">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28" s="41">
         <f t="shared" si="12"/>
@@ -42918,7 +44530,7 @@
       </c>
       <c r="AE28" s="41">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF28" s="41">
         <f t="shared" si="12"/>
@@ -43093,23 +44705,23 @@
       </c>
       <c r="Q30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S30" s="37">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" s="37">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U30" s="37">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V30" s="37">
         <f t="shared" si="13"/>
@@ -43149,7 +44761,7 @@
       </c>
       <c r="AE30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30" s="37">
         <f t="shared" si="13"/>
@@ -43400,46 +45012,46 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ18">
-    <cfRule type="containsText" dxfId="216" priority="1" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="404" priority="1" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="2" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="403" priority="2" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="402" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="213" priority="4" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="401" priority="4" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="5" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="400" priority="5" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="6" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="399" priority="6" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="7" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="398" priority="7" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="209" priority="10" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="397" priority="10" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="208" priority="11" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="396" priority="11" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="207" priority="12" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="395" priority="12" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="206" priority="13" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="394" priority="13" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="14" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="393" priority="14" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="16" operator="containsText" text="NN13">
+    <cfRule type="containsText" dxfId="392" priority="16" operator="containsText" text="NN13">
       <formula>NOT(ISERROR(SEARCH("NN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="203" priority="20" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="391" priority="20" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46214,117 +47826,117 @@
     <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
-    <cfRule type="containsText" dxfId="202" priority="23" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="390" priority="23" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="201" priority="24" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="389" priority="24" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="25" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="388" priority="25" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="199" priority="26" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="387" priority="26" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="27" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="386" priority="27" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="197" priority="28" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="385" priority="28" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="196" priority="29" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="384" priority="29" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="195" priority="30" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="383" priority="30" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AH15">
-    <cfRule type="containsText" dxfId="194" priority="19" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="382" priority="19" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="193" priority="5" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="381" priority="5" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:AH15">
-    <cfRule type="containsText" dxfId="192" priority="16" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="380" priority="16" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="191" priority="17" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="379" priority="17" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="190" priority="18" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="378" priority="18" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="189" priority="6" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="377" priority="6" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="188" priority="7" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="376" priority="7" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="187" priority="8" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="375" priority="8" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="186" priority="9" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="374" priority="9" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="10" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="373" priority="10" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="184" priority="11" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="372" priority="11" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="183" priority="12" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="371" priority="12" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="182" priority="13" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="370" priority="13" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="181" priority="14" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="369" priority="14" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="180" priority="15" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="368" priority="15" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="179" priority="20" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="367" priority="20" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AI15">
-    <cfRule type="containsText" dxfId="178" priority="3" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="366" priority="3" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="177" priority="4" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="365" priority="4" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="176" priority="1" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="364" priority="1" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="175" priority="2" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="363" priority="2" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AH5 E6:AH10">
-    <cfRule type="containsText" dxfId="174" priority="31" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="362" priority="31" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="173" priority="32" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="361" priority="32" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="172" priority="33" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="360" priority="33" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="171" priority="34" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="359" priority="34" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="170" priority="35" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="358" priority="35" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="169" priority="36" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="357" priority="36" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="168" priority="37" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="356" priority="37" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
